--- a/ToDo.xlsx
+++ b/ToDo.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleckleinman/Documents/TheGrantScout/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71646602-351A-6946-B692-29BDD15A8B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4764223A-D0A9-234C-A808-D89EE6397066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19280" yWindow="500" windowWidth="18960" windowHeight="19200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="To Do This Week" sheetId="4" r:id="rId1"/>
-    <sheet name="Beta Leads" sheetId="7" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="8" state="hidden" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
+    <sheet name="To Do" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
+    <sheet name="Beta Leads" sheetId="7" state="hidden" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="8" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Beta Leads'!$B$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'To Do This Week'!$B$2:$H$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Beta Leads'!$B$3:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Do'!$B$2:$H$172</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="280">
   <si>
     <t>Task</t>
   </si>
@@ -445,31 +446,10 @@
     <t>BG2</t>
   </si>
   <si>
-    <t>Get a babysitter</t>
-  </si>
-  <si>
-    <t>Give Taylor stuff to list</t>
-  </si>
-  <si>
-    <t>Give Taylor csv file</t>
-  </si>
-  <si>
-    <t>Figure out when to pick up the stuff from Salt Lake</t>
-  </si>
-  <si>
-    <t>List something today</t>
-  </si>
-  <si>
-    <t>Mail Rent Check</t>
-  </si>
-  <si>
     <t>Check database import for completeness</t>
   </si>
   <si>
     <t>Enrich grants table recipient EINs</t>
-  </si>
-  <si>
-    <t>Track package</t>
   </si>
   <si>
     <t>11/12/2025 - He called back and said he was interested. I texted him the form but haven't heard back from him
@@ -752,45 +732,9 @@
     <t>Email Matt about payment</t>
   </si>
   <si>
-    <t>Write down notes from call with Margi</t>
-  </si>
-  <si>
     <t>Respond to Margi/Melissa's email</t>
   </si>
   <si>
-    <t>research CNE org</t>
-  </si>
-  <si>
-    <t>find orgs like CNE</t>
-  </si>
-  <si>
-    <t>Summarize sales efforts and results from last week</t>
-  </si>
-  <si>
-    <t>Update todos for each lead</t>
-  </si>
-  <si>
-    <t>Follow up call with PSMF</t>
-  </si>
-  <si>
-    <t>Follow up call with RHF</t>
-  </si>
-  <si>
-    <t>Follow up call with SNS</t>
-  </si>
-  <si>
-    <t>Follow up call with Horizons</t>
-  </si>
-  <si>
-    <t>Follow up call with Friendship Circle</t>
-  </si>
-  <si>
-    <t>Clean up calls CRM workbook (enrich leads, deduplicate etc)</t>
-  </si>
-  <si>
-    <t>Plan outreach strategy for this week</t>
-  </si>
-  <si>
     <t>Update CRM to show weekly stats and results</t>
   </si>
   <si>
@@ -812,18 +756,9 @@
     <t>Warm up  email addresses</t>
   </si>
   <si>
-    <t>Review last weeks accountability report</t>
-  </si>
-  <si>
     <t>Get additional 990 data for the database</t>
   </si>
   <si>
-    <t>Analyze Sales efforts from last week</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
     <t>Respond to Matts email</t>
   </si>
   <si>
@@ -845,42 +780,133 @@
     <t>Call with Matt and Terry</t>
   </si>
   <si>
-    <t>Get pipeline files all ready for Braden</t>
-  </si>
-  <si>
-    <t>Schedule linked posts for this week and next week</t>
-  </si>
-  <si>
-    <t>Show Braden report pipeline and build SNS report</t>
-  </si>
-  <si>
-    <t>Watch Braden build Horizons report</t>
-  </si>
-  <si>
-    <t>Build RHF and Friendship Circle reports together</t>
-  </si>
-  <si>
     <t>Write up report for last week - Jonathan, Bishop, Grammy</t>
-  </si>
-  <si>
-    <t>Finish PSMF report</t>
   </si>
   <si>
     <t>Prep for call with Matt and Terry
 - Moneyball 
+- Send teams link
 - List of deliverables in a report
 - List of similar nonprofits
 - List of target funders</t>
+  </si>
+  <si>
+    <t>Direct Sales</t>
+  </si>
+  <si>
+    <t>Send 5 Beta reports</t>
+  </si>
+  <si>
+    <t>Build pipeline test harness</t>
+  </si>
+  <si>
+    <t>Call foundation leads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call 100 nonprofit prospects </t>
+  </si>
+  <si>
+    <t>Migrate database to supabase</t>
+  </si>
+  <si>
+    <t>Consolidate report generation scripts/prompting</t>
+  </si>
+  <si>
+    <t>Generate and send 5 more beta reports</t>
+  </si>
+  <si>
+    <t>Send VetsBoats their first report</t>
+  </si>
+  <si>
+    <t>Call foundation leads back.</t>
+  </si>
+  <si>
+    <t>Call 100 nonprofit prospects directly</t>
+  </si>
+  <si>
+    <t>Migrate database to Supabase (for easier report generation)</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>Goals</t>
+  </si>
+  <si>
+    <t>Plans</t>
+  </si>
+  <si>
+    <t>Build Test Harness</t>
+  </si>
+  <si>
+    <t>Run test harness</t>
+  </si>
+  <si>
+    <t>Finish Phase 4 for easy reports</t>
+  </si>
+  <si>
+    <t>Make supabase able to handle more data</t>
+  </si>
+  <si>
+    <t>Rerun import script (piece by piece version)</t>
+  </si>
+  <si>
+    <t>Identify additional f990 data to import</t>
+  </si>
+  <si>
+    <t>Run pipeline on 100 test nonprofits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make pipeline V4 </t>
+  </si>
+  <si>
+    <t>Identify nonprofits to test on and call (from the foundation who said no)</t>
+  </si>
+  <si>
+    <t>Call 20 nonprofits</t>
+  </si>
+  <si>
+    <t>Call 30 nonprofits</t>
+  </si>
+  <si>
+    <t>Write up report on last nights run</t>
+  </si>
+  <si>
+    <t>Analyze run and find identify matches for all 5 beta groups</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>Retirement Housing Foundation</t>
+  </si>
+  <si>
+    <t>SNS</t>
+  </si>
+  <si>
+    <t>Horizons National Student Enrichment Program Inc.</t>
+  </si>
+  <si>
+    <t>Friendship Circle SD INC</t>
+  </si>
+  <si>
+    <t>PSMF</t>
+  </si>
+  <si>
+    <t>RHF</t>
+  </si>
+  <si>
+    <t>HN</t>
+  </si>
+  <si>
+    <t>FC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="[$-409]h:mm\ AM/PM;@"/>
-  </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -927,6 +953,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -936,7 +983,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1091,16 +1138,7 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="dotted">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -1111,10 +1149,105 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="dotted">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1122,7 +1255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1148,9 +1281,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1172,43 +1302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1260,16 +1354,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1283,9 +1368,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1303,115 +1385,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF9999FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB7C3FD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9966"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill>
@@ -1458,6 +1493,48 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB7C3FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9966"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1746,47 +1823,300 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A518F1-E8D1-4EDA-B8FC-EAEFD9F39116}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="B1:T161"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFAB370-5E5C-46A0-8279-06017109B5E9}">
+  <dimension ref="B2:E27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="23.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="71" customWidth="1"/>
-    <col min="5" max="5" width="49.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" style="78" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="23.5" style="2" customWidth="1"/>
-    <col min="9" max="14" width="23.5" customWidth="1"/>
-    <col min="15" max="20" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="57.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1"/>
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" s="63">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C5" s="58" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="59">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C6" s="58" t="s">
+        <v>252</v>
+      </c>
+      <c r="D6" s="59">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C7" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" s="59">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C8" s="58" t="s">
+        <v>254</v>
+      </c>
+      <c r="D8" s="59">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="61">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+    </row>
+    <row r="11" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:5" ht="30" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C12" s="66"/>
+      <c r="D12" s="67" t="s">
+        <v>257</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C13" s="62" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" s="69" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="73">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C14" s="58" t="s">
+        <v>250</v>
+      </c>
+      <c r="D14" s="64" t="s">
+        <v>270</v>
+      </c>
+      <c r="E14" s="71">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C15" s="58" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>258</v>
+      </c>
+      <c r="E15" s="71">
+        <v>46043</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C16" s="58" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="E16" s="71">
+        <v>46043</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C17" s="58" t="s">
+        <v>250</v>
+      </c>
+      <c r="D17" s="64" t="s">
+        <v>260</v>
+      </c>
+      <c r="E17" s="71">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C18" s="58" t="s">
+        <v>254</v>
+      </c>
+      <c r="D18" s="64" t="s">
+        <v>261</v>
+      </c>
+      <c r="E18" s="71">
+        <v>46043</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C19" s="58" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="74">
+        <v>46043</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C20" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>263</v>
+      </c>
+      <c r="E20" s="71">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C21" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="D21" s="64" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="71">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C22" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" s="71">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C23" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="D23" s="64" t="s">
+        <v>266</v>
+      </c>
+      <c r="E23" s="71">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C24" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>267</v>
+      </c>
+      <c r="E24" s="71">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C25" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="D25" s="64" t="s">
+        <v>268</v>
+      </c>
+      <c r="E25" s="71">
+        <v>46043</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C26" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>267</v>
+      </c>
+      <c r="E26" s="71">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="60" t="s">
+        <v>253</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>268</v>
+      </c>
+      <c r="E27" s="72">
+        <v>46045</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A518F1-E8D1-4EDA-B8FC-EAEFD9F39116}">
+  <dimension ref="B1:S172"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="23.5" style="76" customWidth="1"/>
+    <col min="3" max="3" width="23.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" style="54" customWidth="1"/>
+    <col min="5" max="5" width="34.1640625" style="77" customWidth="1"/>
+    <col min="6" max="6" width="49.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" style="2" customWidth="1"/>
+    <col min="9" max="13" width="23.5" customWidth="1"/>
+    <col min="14" max="19" width="13.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="56"/>
       <c r="C1"/>
-      <c r="D1" s="67"/>
-      <c r="E1"/>
-      <c r="F1" s="72"/>
+      <c r="D1" s="50"/>
+      <c r="F1"/>
       <c r="H1"/>
     </row>
-    <row r="2" spans="2:20" s="2" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="2:19" s="2" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="11" t="s">
+      <c r="G2" s="43"/>
+      <c r="H2" s="10" t="s">
         <v>3</v>
       </c>
       <c r="I2" s="1"/>
@@ -1800,27 +2130,26 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="17">
+    </row>
+    <row r="3" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B3" s="79">
         <v>45992</v>
       </c>
-      <c r="C3" s="18" t="str">
-        <f t="shared" ref="C3:C11" si="0">TEXT(B3, "dddd")</f>
+      <c r="C3" s="80" t="str">
+        <f>TEXT(B3, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="81">
         <v>1</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="82"/>
+      <c r="F3" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" s="20">
+      <c r="G3" s="83" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="84">
         <v>45992</v>
       </c>
       <c r="I3" s="3"/>
@@ -1828,33 +2157,32 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="5"/>
-    </row>
-    <row r="4" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="14">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="5"/>
+    </row>
+    <row r="4" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="13">
         <v>45992</v>
       </c>
-      <c r="C4" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="C4" s="14" t="str">
+        <f>TEXT(B4, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>1</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="85"/>
+      <c r="F4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" s="21">
+      <c r="G4" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="16">
         <v>45992</v>
       </c>
       <c r="I4" s="5"/>
@@ -1866,29 +2194,28 @@
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="5"/>
-    </row>
-    <row r="5" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="14">
+      <c r="R4" s="4"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="13">
         <v>45992</v>
       </c>
-      <c r="C5" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="C5" s="14" t="str">
+        <f>TEXT(B5, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="85"/>
+      <c r="F5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H5" s="21">
+      <c r="G5" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" s="16">
         <v>45992</v>
       </c>
       <c r="I5" s="5"/>
@@ -1898,31 +2225,30 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="5"/>
-    </row>
-    <row r="6" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="22">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="13">
         <v>45992</v>
       </c>
-      <c r="C6" s="23" t="str">
-        <f t="shared" si="0"/>
+      <c r="C6" s="14" t="str">
+        <f>TEXT(B6, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="15">
         <v>2</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="85"/>
+      <c r="F6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="24"/>
-      <c r="G6" s="59" t="s">
-        <v>146</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="16">
         <v>45992</v>
       </c>
       <c r="I6" s="5"/>
@@ -1934,29 +2260,28 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="5"/>
-    </row>
-    <row r="7" spans="2:20" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="26">
+      <c r="R6" s="4"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="13">
         <v>45992</v>
       </c>
-      <c r="C7" s="27" t="str">
-        <f t="shared" si="0"/>
+      <c r="C7" s="14" t="str">
+        <f>TEXT(B7, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="15">
         <v>3</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="85"/>
+      <c r="F7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="29">
+      <c r="G7" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="16">
         <v>45992</v>
       </c>
       <c r="I7" s="5"/>
@@ -1966,31 +2291,30 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="5"/>
-    </row>
-    <row r="8" spans="2:20" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="17">
+      <c r="P7" s="4"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="2:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="B8" s="13">
         <v>45992</v>
       </c>
-      <c r="C8" s="18" t="str">
-        <f t="shared" si="0"/>
+      <c r="C8" s="14" t="str">
+        <f>TEXT(B8, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="15">
         <v>4</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="85"/>
+      <c r="F8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="20">
+      <c r="G8" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H8" s="16">
         <v>45992</v>
       </c>
       <c r="I8" s="5"/>
@@ -2002,29 +2326,28 @@
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="5"/>
-    </row>
-    <row r="9" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="14">
+      <c r="R8" s="4"/>
+      <c r="S8" s="5"/>
+    </row>
+    <row r="9" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="13">
         <v>45992</v>
       </c>
-      <c r="C9" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="C9" s="14" t="str">
+        <f>TEXT(B9, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>5</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="85"/>
+      <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="H9" s="21">
+      <c r="G9" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H9" s="16">
         <v>45992</v>
       </c>
       <c r="I9" s="3"/>
@@ -2032,33 +2355,32 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="5"/>
-    </row>
-    <row r="10" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="14">
+      <c r="N9" s="4"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="5"/>
+    </row>
+    <row r="10" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="13">
         <v>45992</v>
       </c>
-      <c r="C10" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="C10" s="14" t="str">
+        <f>TEXT(B10, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <v>5</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="85"/>
+      <c r="F10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="H10" s="21">
+      <c r="G10" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="16">
         <v>45992</v>
       </c>
       <c r="I10" s="5"/>
@@ -2070,29 +2392,28 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="5"/>
-    </row>
-    <row r="11" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="14">
+      <c r="R10" s="4"/>
+      <c r="S10" s="5"/>
+    </row>
+    <row r="11" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="13">
         <v>45992</v>
       </c>
-      <c r="C11" s="15" t="str">
-        <f t="shared" si="0"/>
+      <c r="C11" s="14" t="str">
+        <f>TEXT(B11, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>6</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="85"/>
+      <c r="F11" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H11" s="21">
+      <c r="G11" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H11" s="16">
         <v>45992</v>
       </c>
       <c r="I11" s="5"/>
@@ -2104,29 +2425,28 @@
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="5"/>
-    </row>
-    <row r="12" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="14">
+      <c r="R11" s="4"/>
+      <c r="S11" s="5"/>
+    </row>
+    <row r="12" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="13">
         <v>45992</v>
       </c>
-      <c r="C12" s="16" t="str">
-        <f t="shared" ref="C12:C32" si="1">IF(ISBLANK(B12),"",TEXT(B12, "dddd"))</f>
+      <c r="C12" s="15" t="str">
+        <f>IF(ISBLANK(B12),"",TEXT(B12, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>6</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="85"/>
+      <c r="F12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H12" s="21">
+      <c r="G12" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="16">
         <v>45992</v>
       </c>
       <c r="I12" s="5"/>
@@ -2138,29 +2458,28 @@
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="5"/>
-    </row>
-    <row r="13" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="14">
+      <c r="R12" s="4"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="13">
         <v>45994</v>
       </c>
-      <c r="C13" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C13" s="15" t="str">
+        <f>IF(ISBLANK(B13),"",TEXT(B13, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <v>1</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="85"/>
+      <c r="F13" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="H13" s="21">
+      <c r="G13" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" s="16">
         <v>45994</v>
       </c>
       <c r="I13" s="5"/>
@@ -2172,29 +2491,28 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="5"/>
-    </row>
-    <row r="14" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="14">
+      <c r="R13" s="4"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="13">
         <v>45994</v>
       </c>
-      <c r="C14" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C14" s="15" t="str">
+        <f>IF(ISBLANK(B14),"",TEXT(B14, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="15">
         <v>1.5</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="85"/>
+      <c r="F14" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="H14" s="21">
+      <c r="G14" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" s="16">
         <v>45994</v>
       </c>
       <c r="I14" s="5"/>
@@ -2204,31 +2522,30 @@
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="5"/>
-    </row>
-    <row r="15" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="52">
+      <c r="P14" s="4"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="5"/>
+    </row>
+    <row r="15" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="39">
         <v>45994</v>
       </c>
-      <c r="C15" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C15" s="15" t="str">
+        <f>IF(ISBLANK(B15),"",TEXT(B15, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="38">
         <v>2</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="E15" s="86"/>
+      <c r="F15" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="H15" s="53">
+      <c r="G15" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="40">
         <v>45994</v>
       </c>
       <c r="I15" s="5"/>
@@ -2238,31 +2555,30 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="5"/>
-    </row>
-    <row r="16" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="14">
+      <c r="P15" s="4"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="5"/>
+    </row>
+    <row r="16" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="13">
         <v>45994</v>
       </c>
-      <c r="C16" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C16" s="15" t="str">
+        <f>IF(ISBLANK(B16),"",TEXT(B16, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="H16" s="21">
+      <c r="E16" s="85"/>
+      <c r="F16" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="16">
         <v>45994</v>
       </c>
       <c r="I16" s="5"/>
@@ -2272,31 +2588,30 @@
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="5"/>
-    </row>
-    <row r="17" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="14">
+      <c r="P16" s="4"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="5"/>
+    </row>
+    <row r="17" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="13">
         <v>45994</v>
       </c>
-      <c r="C17" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C17" s="15" t="str">
+        <f>IF(ISBLANK(B17),"",TEXT(B17, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="15">
         <v>3</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="85"/>
+      <c r="F17" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H17" s="21">
+      <c r="G17" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H17" s="16">
         <v>45994</v>
       </c>
       <c r="I17" s="5"/>
@@ -2306,31 +2621,30 @@
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="5"/>
-    </row>
-    <row r="18" spans="2:20" s="55" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="14">
+      <c r="P17" s="4"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="5"/>
+    </row>
+    <row r="18" spans="2:19" s="42" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="13">
         <v>45994</v>
       </c>
-      <c r="C18" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C18" s="15" t="str">
+        <f>IF(ISBLANK(B18),"",TEXT(B18, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="85"/>
+      <c r="F18" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="21">
+      <c r="G18" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" s="16">
         <v>45994</v>
       </c>
       <c r="I18" s="3"/>
@@ -2342,29 +2656,28 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="3"/>
-    </row>
-    <row r="19" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="14">
+      <c r="R18" s="41"/>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="13">
         <v>45994</v>
       </c>
-      <c r="C19" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C19" s="15" t="str">
+        <f>IF(ISBLANK(B19),"",TEXT(B19, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>4</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="85"/>
+      <c r="F19" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H19" s="21">
+      <c r="G19" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H19" s="16">
         <v>45994</v>
       </c>
       <c r="I19" s="5"/>
@@ -2376,29 +2689,28 @@
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="5"/>
-    </row>
-    <row r="20" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="14">
+      <c r="R19" s="4"/>
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="13">
         <v>45994</v>
       </c>
-      <c r="C20" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C20" s="15" t="str">
+        <f>IF(ISBLANK(B20),"",TEXT(B20, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>5</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="85"/>
+      <c r="F20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H20" s="21">
+      <c r="G20" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" s="16">
         <v>45994</v>
       </c>
       <c r="I20" s="5"/>
@@ -2410,29 +2722,28 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="5"/>
-    </row>
-    <row r="21" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="14">
+      <c r="R20" s="4"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B21" s="13">
         <v>45995</v>
       </c>
-      <c r="C21" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C21" s="15" t="str">
+        <f>IF(ISBLANK(B21),"",TEXT(B21, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="15">
         <v>1</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="85"/>
+      <c r="F21" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="21">
+      <c r="G21" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21" s="16">
         <v>45995</v>
       </c>
       <c r="I21" s="5"/>
@@ -2444,29 +2755,28 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="5"/>
-    </row>
-    <row r="22" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="14">
+      <c r="R21" s="4"/>
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" s="13">
         <v>45995</v>
       </c>
-      <c r="C22" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C22" s="15" t="str">
+        <f>IF(ISBLANK(B22),"",TEXT(B22, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="15">
         <v>1.5</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="85"/>
+      <c r="F22" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H22" s="21">
+      <c r="G22" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H22" s="16">
         <v>45995</v>
       </c>
       <c r="I22" s="5"/>
@@ -2476,31 +2786,30 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="5"/>
-    </row>
-    <row r="23" spans="2:20" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="21">
+      <c r="P22" s="4"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="5"/>
+    </row>
+    <row r="23" spans="2:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="B23" s="13">
         <v>45995</v>
       </c>
-      <c r="C23" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C23" s="15" t="str">
+        <f>IF(ISBLANK(B23),"",TEXT(B23, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="15">
         <v>2</v>
       </c>
-      <c r="E23" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="H23" s="21">
+      <c r="E23" s="85"/>
+      <c r="F23" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H23" s="16">
         <v>45995</v>
       </c>
       <c r="I23" s="5"/>
@@ -2510,31 +2819,30 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="5"/>
-    </row>
-    <row r="24" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="21">
+      <c r="P23" s="4"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="5"/>
+    </row>
+    <row r="24" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B24" s="13">
         <v>45995</v>
       </c>
-      <c r="C24" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C24" s="15" t="str">
+        <f>IF(ISBLANK(B24),"",TEXT(B24, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
         <v>4</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="85"/>
+      <c r="F24" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H24" s="21">
+      <c r="H24" s="16">
         <v>45995</v>
       </c>
       <c r="I24" s="5"/>
@@ -2544,31 +2852,30 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="5"/>
-    </row>
-    <row r="25" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="14">
+      <c r="P24" s="4"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="5"/>
+    </row>
+    <row r="25" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="13">
         <v>45995</v>
       </c>
-      <c r="C25" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C25" s="15" t="str">
+        <f>IF(ISBLANK(B25),"",TEXT(B25, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="15">
         <v>5</v>
       </c>
-      <c r="E25" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H25" s="21">
+      <c r="E25" s="85"/>
+      <c r="F25" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" s="16">
         <v>45995</v>
       </c>
       <c r="I25" s="5"/>
@@ -2580,29 +2887,28 @@
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="5"/>
-    </row>
-    <row r="26" spans="2:20" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="14">
+      <c r="R25" s="4"/>
+      <c r="S25" s="5"/>
+    </row>
+    <row r="26" spans="2:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="B26" s="13">
         <v>45995</v>
       </c>
-      <c r="C26" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C26" s="15" t="str">
+        <f>IF(ISBLANK(B26),"",TEXT(B26, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="15">
         <v>6</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="85"/>
+      <c r="F26" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" s="21">
+      <c r="G26" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" s="16">
         <v>45995</v>
       </c>
       <c r="I26" s="5"/>
@@ -2614,25 +2920,24 @@
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="5"/>
-    </row>
-    <row r="27" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="14">
+      <c r="R26" s="4"/>
+      <c r="S26" s="5"/>
+    </row>
+    <row r="27" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="13">
         <v>45995</v>
       </c>
-      <c r="C27" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C27" s="15" t="str">
+        <f>IF(ISBLANK(B27),"",TEXT(B27, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="21">
+      <c r="D27" s="15"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" s="44"/>
+      <c r="H27" s="16">
         <v>45995</v>
       </c>
       <c r="I27" s="3"/>
@@ -2640,33 +2945,32 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="5"/>
-    </row>
-    <row r="28" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="14">
+      <c r="N27" s="4"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="5"/>
+    </row>
+    <row r="28" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B28" s="13">
         <v>45996</v>
       </c>
-      <c r="C28" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C28" s="15" t="str">
+        <f>IF(ISBLANK(B28),"",TEXT(B28, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" s="21">
+      <c r="E28" s="85"/>
+      <c r="F28" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" s="16">
         <v>45996</v>
       </c>
       <c r="I28" s="3"/>
@@ -2674,33 +2978,32 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="5"/>
-    </row>
-    <row r="29" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="14">
+      <c r="N28" s="4"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="5"/>
+    </row>
+    <row r="29" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="13">
         <v>45996</v>
       </c>
-      <c r="C29" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C29" s="15" t="str">
+        <f>IF(ISBLANK(B29),"",TEXT(B29, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="15">
         <v>1</v>
       </c>
-      <c r="E29" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="58" t="s">
+      <c r="E29" s="85"/>
+      <c r="F29" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H29" s="21">
+      <c r="G29" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H29" s="16">
         <v>46000</v>
       </c>
       <c r="I29" s="5"/>
@@ -2710,31 +3013,30 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="5"/>
-    </row>
-    <row r="30" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="14">
+      <c r="P29" s="4"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="5"/>
+    </row>
+    <row r="30" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="13">
         <v>45996</v>
       </c>
-      <c r="C30" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C30" s="15" t="str">
+        <f>IF(ISBLANK(B30),"",TEXT(B30, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="15">
         <v>1</v>
       </c>
-      <c r="E30" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H30" s="21">
+      <c r="E30" s="85"/>
+      <c r="F30" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H30" s="16">
         <v>46000</v>
       </c>
       <c r="I30" s="5"/>
@@ -2744,31 +3046,30 @@
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="5"/>
-    </row>
-    <row r="31" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="14">
+      <c r="P30" s="4"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="5"/>
+    </row>
+    <row r="31" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" s="13">
         <v>45996</v>
       </c>
-      <c r="C31" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C31" s="15" t="str">
+        <f>IF(ISBLANK(B31),"",TEXT(B31, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="15">
         <v>1.5</v>
       </c>
-      <c r="E31" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H31" s="21">
+      <c r="E31" s="85"/>
+      <c r="F31" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H31" s="16">
         <v>46000</v>
       </c>
       <c r="I31" s="5"/>
@@ -2778,29 +3079,28 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="5"/>
-    </row>
-    <row r="32" spans="2:20" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="14">
+      <c r="P31" s="4"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="5"/>
+    </row>
+    <row r="32" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="13">
         <v>45996</v>
       </c>
-      <c r="C32" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C32" s="15" t="str">
+        <f>IF(ISBLANK(B32),"",TEXT(B32, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H32" s="21">
+      <c r="D32" s="15"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H32" s="16">
         <v>45996</v>
       </c>
       <c r="I32" s="5"/>
@@ -2812,2425 +3112,2521 @@
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="5"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="5"/>
     </row>
     <row r="33" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B33" s="14">
+      <c r="B33" s="13">
         <v>45999</v>
       </c>
-      <c r="C33" s="16" t="str">
+      <c r="C33" s="15" t="str">
         <f>IF(ISBLANK(B33),"",TEXT(B33, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D33" s="69">
+      <c r="D33" s="52">
         <v>3</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="44"/>
+      <c r="F33" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F33" s="74"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="30"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B34" s="14">
+      <c r="B34" s="13">
         <v>45999</v>
       </c>
-      <c r="C34" s="16" t="str">
+      <c r="C34" s="15" t="str">
         <f>IF(ISBLANK(B34),"",TEXT(B34, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D34" s="69">
+      <c r="D34" s="52">
         <v>3</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="44"/>
+      <c r="F34" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="74"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="30"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B35" s="14">
+      <c r="B35" s="13">
         <v>45999</v>
       </c>
-      <c r="C35" s="16" t="str">
+      <c r="C35" s="15" t="str">
         <f>IF(ISBLANK(B35),"",TEXT(B35, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D35" s="69">
+      <c r="D35" s="52">
         <v>4</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="44"/>
+      <c r="F35" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="74"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="30"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="2:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="B36" s="14">
+      <c r="B36" s="13">
         <v>45999</v>
       </c>
-      <c r="C36" s="16" t="str">
+      <c r="C36" s="15" t="str">
         <f>IF(ISBLANK(B36),"",TEXT(B36, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D36" s="69">
+      <c r="D36" s="52">
         <v>5</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="44"/>
+      <c r="F36" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F36" s="74"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="30"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="17"/>
     </row>
     <row r="37" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B37" s="14">
+      <c r="B37" s="13">
         <v>46000</v>
       </c>
-      <c r="C37" s="16" t="str">
+      <c r="C37" s="15" t="str">
         <f>IF(ISBLANK(B37),"",TEXT(B37, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D37" s="69"/>
-      <c r="E37" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="F37" s="74"/>
-      <c r="G37" s="58" t="s">
+      <c r="D37" s="52"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="H37" s="21">
+      <c r="G37" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H37" s="16">
         <v>46000</v>
       </c>
     </row>
     <row r="38" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B38" s="14">
+      <c r="B38" s="13">
         <v>46001</v>
       </c>
-      <c r="C38" s="16" t="str">
+      <c r="C38" s="15" t="str">
         <f>IF(ISBLANK(B38),"",TEXT(B38, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D38" s="69">
+      <c r="D38" s="52">
         <v>1</v>
       </c>
-      <c r="E38" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="F38" s="74"/>
-      <c r="G38" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H38" s="21">
+      <c r="E38" s="85"/>
+      <c r="F38" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H38" s="16">
         <v>46001</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B39" s="14">
+      <c r="B39" s="13">
         <v>46001</v>
       </c>
-      <c r="C39" s="16" t="str">
+      <c r="C39" s="15" t="str">
         <f>IF(ISBLANK(B39),"",TEXT(B39, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D39" s="69">
+      <c r="D39" s="52">
         <v>2</v>
       </c>
-      <c r="E39" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="F39" s="74"/>
-      <c r="G39" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H39" s="21">
+      <c r="E39" s="85"/>
+      <c r="F39" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H39" s="16">
         <v>46001</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B40" s="14">
+      <c r="B40" s="13">
         <v>46001</v>
       </c>
-      <c r="C40" s="16" t="str">
+      <c r="C40" s="15" t="str">
         <f>IF(ISBLANK(B40),"",TEXT(B40, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D40" s="69">
+      <c r="D40" s="52">
         <v>2.1</v>
       </c>
-      <c r="E40" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="F40" s="74"/>
-      <c r="G40" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H40" s="21">
+      <c r="E40" s="85"/>
+      <c r="F40" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H40" s="16">
         <v>46001</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B41" s="14">
+      <c r="B41" s="13">
         <v>46001</v>
       </c>
-      <c r="C41" s="16" t="str">
+      <c r="C41" s="15" t="str">
         <f>IF(ISBLANK(B41),"",TEXT(B41, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D41" s="69">
+      <c r="D41" s="52">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E41" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="F41" s="74"/>
-      <c r="G41" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H41" s="21">
+      <c r="E41" s="85"/>
+      <c r="F41" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H41" s="16">
         <v>46001</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B42" s="14">
+      <c r="B42" s="13">
         <v>46001</v>
       </c>
-      <c r="C42" s="16" t="str">
+      <c r="C42" s="15" t="str">
         <f>IF(ISBLANK(B42),"",TEXT(B42, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D42" s="69">
+      <c r="D42" s="52">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E42" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="F42" s="74"/>
-      <c r="G42" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H42" s="21">
+      <c r="E42" s="85"/>
+      <c r="F42" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H42" s="16">
         <v>46002</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B43" s="14">
+      <c r="B43" s="13">
         <v>46001</v>
       </c>
-      <c r="C43" s="16" t="str">
+      <c r="C43" s="15" t="str">
         <f>IF(ISBLANK(B43),"",TEXT(B43, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D43" s="69">
+      <c r="D43" s="52">
         <v>2.4</v>
       </c>
-      <c r="E43" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="F43" s="74"/>
-      <c r="G43" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H43" s="21">
+      <c r="E43" s="85"/>
+      <c r="F43" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H43" s="16">
         <v>46002</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B44" s="14">
+      <c r="B44" s="13">
         <v>46001</v>
       </c>
-      <c r="C44" s="16" t="str">
+      <c r="C44" s="15" t="str">
         <f>IF(ISBLANK(B44),"",TEXT(B44, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D44" s="69">
+      <c r="D44" s="52">
         <v>2.4500000000000002</v>
       </c>
-      <c r="E44" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F44" s="74"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="21"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="G44" s="44"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B45" s="14">
+      <c r="B45" s="13">
         <v>46001</v>
       </c>
-      <c r="C45" s="16" t="str">
+      <c r="C45" s="15" t="str">
         <f>IF(ISBLANK(B45),"",TEXT(B45, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D45" s="69">
+      <c r="D45" s="52">
         <v>2.5</v>
       </c>
-      <c r="E45" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="F45" s="74"/>
-      <c r="G45" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H45" s="21"/>
+      <c r="E45" s="85"/>
+      <c r="F45" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="G45" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B46" s="14">
+      <c r="B46" s="13">
         <v>46001</v>
       </c>
-      <c r="C46" s="16" t="str">
+      <c r="C46" s="15" t="str">
         <f>IF(ISBLANK(B46),"",TEXT(B46, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D46" s="69">
+      <c r="D46" s="52">
         <v>2.6</v>
       </c>
-      <c r="E46" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F46" s="74"/>
-      <c r="G46" s="58" t="s">
+      <c r="E46" s="44"/>
+      <c r="F46" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="G46" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="H46" s="30"/>
+      <c r="H46" s="17"/>
     </row>
     <row r="47" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B47" s="14">
+      <c r="B47" s="13">
         <v>46001</v>
       </c>
-      <c r="C47" s="16" t="str">
+      <c r="C47" s="15" t="str">
         <f>IF(ISBLANK(B47),"",TEXT(B47, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D47" s="69">
+      <c r="D47" s="52">
         <v>8</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="85"/>
+      <c r="F47" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="F47" s="74"/>
-      <c r="G47" s="58" t="s">
-        <v>164</v>
-      </c>
-      <c r="H47" s="21">
+      <c r="H47" s="16">
         <v>46001</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B48" s="14">
+      <c r="B48" s="13">
         <v>46002</v>
       </c>
-      <c r="C48" s="16" t="str">
+      <c r="C48" s="15" t="str">
         <f>IF(ISBLANK(B48),"",TEXT(B48, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D48" s="69">
+      <c r="D48" s="52">
         <v>1</v>
       </c>
-      <c r="E48" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="F48" s="74"/>
-      <c r="G48" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="H48" s="30"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G48" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" s="17"/>
     </row>
     <row r="49" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B49" s="14">
+      <c r="B49" s="13">
         <v>46003</v>
       </c>
-      <c r="C49" s="16" t="str">
+      <c r="C49" s="15" t="str">
         <f>IF(ISBLANK(B49),"",TEXT(B49, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D49" s="69">
+      <c r="D49" s="52">
         <v>1</v>
       </c>
-      <c r="E49" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="F49" s="74"/>
-      <c r="G49" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H49" s="21">
+      <c r="E49" s="85"/>
+      <c r="F49" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H49" s="16">
         <v>46003</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B50" s="14">
+      <c r="B50" s="13">
         <v>46006</v>
       </c>
-      <c r="C50" s="16" t="str">
+      <c r="C50" s="15" t="str">
         <f>IF(ISBLANK(B50),"",TEXT(B50, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D50" s="69">
+      <c r="D50" s="52">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E50" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="F50" s="74"/>
-      <c r="G50" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H50" s="21">
+      <c r="E50" s="85"/>
+      <c r="F50" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G50" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H50" s="16">
         <v>46003</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B51" s="14">
+      <c r="B51" s="13">
         <v>46006</v>
       </c>
-      <c r="C51" s="16" t="str">
+      <c r="C51" s="15" t="str">
         <f>IF(ISBLANK(B51),"",TEXT(B51, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D51" s="69">
+      <c r="D51" s="52">
         <v>1.2</v>
       </c>
-      <c r="E51" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="F51" s="74"/>
-      <c r="G51" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H51" s="21">
+      <c r="E51" s="85"/>
+      <c r="F51" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H51" s="16">
         <v>46003</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B52" s="14">
+      <c r="B52" s="13">
         <v>46006</v>
       </c>
-      <c r="C52" s="16" t="str">
+      <c r="C52" s="15" t="str">
         <f>IF(ISBLANK(B52),"",TEXT(B52, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D52" s="69">
+      <c r="D52" s="52">
         <v>2.1</v>
       </c>
-      <c r="E52" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="F52" s="74"/>
-      <c r="G52" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="H52" s="21">
+      <c r="E52" s="85"/>
+      <c r="F52" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="H52" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B53" s="14">
+      <c r="B53" s="13">
         <v>46006</v>
       </c>
-      <c r="C53" s="16" t="str">
+      <c r="C53" s="15" t="str">
         <f>IF(ISBLANK(B53),"",TEXT(B53, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D53" s="69">
+      <c r="D53" s="52">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="85"/>
+      <c r="F53" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="G53" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="F53" s="74"/>
-      <c r="G53" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="H53" s="21">
+      <c r="H53" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B54" s="14">
+      <c r="B54" s="13">
         <v>46006</v>
       </c>
-      <c r="C54" s="16" t="str">
+      <c r="C54" s="15" t="str">
         <f>IF(ISBLANK(B54),"",TEXT(B54, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D54" s="69">
+      <c r="D54" s="52">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E54" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="F54" s="74"/>
-      <c r="G54" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="H54" s="21">
+      <c r="E54" s="85"/>
+      <c r="F54" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="G54" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="H54" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B55" s="14">
+      <c r="B55" s="13">
         <v>46006</v>
       </c>
-      <c r="C55" s="16" t="str">
+      <c r="C55" s="15" t="str">
         <f>IF(ISBLANK(B55),"",TEXT(B55, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D55" s="69">
+      <c r="D55" s="52">
         <v>3.1</v>
       </c>
-      <c r="E55" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="F55" s="74"/>
-      <c r="G55" s="58" t="s">
-        <v>178</v>
-      </c>
-      <c r="H55" s="21">
+      <c r="E55" s="85"/>
+      <c r="F55" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="G55" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="H55" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="56" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B56" s="14">
+      <c r="B56" s="13">
         <v>46006</v>
       </c>
-      <c r="C56" s="16" t="str">
+      <c r="C56" s="15" t="str">
         <f>IF(ISBLANK(B56),"",TEXT(B56, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D56" s="69">
+      <c r="D56" s="52">
         <v>3.2</v>
       </c>
-      <c r="E56" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="F56" s="74"/>
-      <c r="G56" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H56" s="21">
+      <c r="E56" s="85"/>
+      <c r="F56" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="G56" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H56" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B57" s="14">
+      <c r="B57" s="13">
         <v>46006</v>
       </c>
-      <c r="C57" s="16" t="str">
+      <c r="C57" s="15" t="str">
         <f>IF(ISBLANK(B57),"",TEXT(B57, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D57" s="69">
+      <c r="D57" s="52">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E57" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="F57" s="74"/>
-      <c r="G57" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H57" s="21">
+      <c r="E57" s="85"/>
+      <c r="F57" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="G57" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H57" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="58" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B58" s="14">
+      <c r="B58" s="13">
         <v>46006</v>
       </c>
-      <c r="C58" s="16" t="str">
+      <c r="C58" s="15" t="str">
         <f>IF(ISBLANK(B58),"",TEXT(B58, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D58" s="69">
+      <c r="D58" s="52">
         <v>4.2</v>
       </c>
-      <c r="E58" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="F58" s="74"/>
-      <c r="G58" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H58" s="21">
+      <c r="E58" s="85"/>
+      <c r="F58" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="G58" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H58" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="59" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B59" s="14">
+      <c r="B59" s="13">
         <v>46006</v>
       </c>
-      <c r="C59" s="16" t="str">
+      <c r="C59" s="15" t="str">
         <f>IF(ISBLANK(B59),"",TEXT(B59, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D59" s="69">
+      <c r="D59" s="52">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E59" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F59" s="74"/>
-      <c r="G59" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H59" s="21">
+      <c r="E59" s="85"/>
+      <c r="F59" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="G59" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H59" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B60" s="14">
+      <c r="B60" s="13">
         <v>46006</v>
       </c>
-      <c r="C60" s="16" t="str">
+      <c r="C60" s="15" t="str">
         <f>IF(ISBLANK(B60),"",TEXT(B60, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D60" s="69">
+      <c r="D60" s="52">
         <v>5.2</v>
       </c>
-      <c r="E60" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="F60" s="74"/>
-      <c r="G60" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H60" s="21">
+      <c r="E60" s="85"/>
+      <c r="F60" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="G60" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H60" s="16">
         <v>46006</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B61" s="14">
+      <c r="B61" s="13">
         <v>46007</v>
       </c>
-      <c r="C61" s="16" t="str">
+      <c r="C61" s="15" t="str">
         <f>IF(ISBLANK(B61),"",TEXT(B61, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D61" s="69">
+      <c r="D61" s="52">
         <v>4.3</v>
       </c>
-      <c r="E61" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="F61" s="74"/>
-      <c r="G61" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H61" s="21">
+      <c r="E61" s="85"/>
+      <c r="F61" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="G61" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H61" s="16">
         <v>46007</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B62" s="14">
+      <c r="B62" s="13">
         <v>46007</v>
       </c>
-      <c r="C62" s="16" t="str">
+      <c r="C62" s="15" t="str">
         <f>IF(ISBLANK(B62),"",TEXT(B62, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D62" s="69">
+      <c r="D62" s="52">
         <v>4.5</v>
       </c>
-      <c r="E62" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="F62" s="74"/>
-      <c r="G62" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H62" s="21">
+      <c r="E62" s="85"/>
+      <c r="F62" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="G62" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H62" s="16">
         <v>46007</v>
       </c>
     </row>
     <row r="63" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B63" s="14">
+      <c r="B63" s="13">
         <v>46007</v>
       </c>
-      <c r="C63" s="16" t="str">
+      <c r="C63" s="15" t="str">
         <f>IF(ISBLANK(B63),"",TEXT(B63, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D63" s="69">
+      <c r="D63" s="52">
         <v>5.3</v>
       </c>
-      <c r="E63" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="F63" s="74"/>
-      <c r="G63" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H63" s="21">
+      <c r="E63" s="85"/>
+      <c r="F63" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="G63" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H63" s="16">
         <v>46007</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B64" s="14">
+      <c r="B64" s="13">
         <v>46007</v>
       </c>
-      <c r="C64" s="16" t="str">
+      <c r="C64" s="15" t="str">
         <f>IF(ISBLANK(B64),"",TEXT(B64, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D64" s="69">
+      <c r="D64" s="52">
         <v>5.4</v>
       </c>
-      <c r="E64" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="F64" s="74"/>
-      <c r="G64" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H64" s="21">
+      <c r="E64" s="85"/>
+      <c r="F64" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="G64" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H64" s="16">
         <v>46007</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B65" s="14">
+      <c r="B65" s="13">
         <v>46008</v>
       </c>
-      <c r="C65" s="16" t="str">
+      <c r="C65" s="15" t="str">
         <f>IF(ISBLANK(B65),"",TEXT(B65, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D65" s="69">
+      <c r="D65" s="52">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E65" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="F65" s="74"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="21">
+      <c r="E65" s="85"/>
+      <c r="F65" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="G65" s="44"/>
+      <c r="H65" s="16">
         <v>46008</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B66" s="14">
+      <c r="B66" s="13">
         <v>46008</v>
       </c>
-      <c r="C66" s="16" t="str">
+      <c r="C66" s="15" t="str">
         <f>IF(ISBLANK(B66),"",TEXT(B66, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D66" s="69">
+      <c r="D66" s="52">
         <v>1.2</v>
       </c>
-      <c r="E66" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="F66" s="74"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="21">
+      <c r="E66" s="85"/>
+      <c r="F66" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="G66" s="44"/>
+      <c r="H66" s="16">
         <v>46008</v>
       </c>
     </row>
     <row r="67" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B67" s="14">
+      <c r="B67" s="13">
         <v>46008</v>
       </c>
-      <c r="C67" s="16" t="str">
+      <c r="C67" s="15" t="str">
         <f>IF(ISBLANK(B67),"",TEXT(B67, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D67" s="69">
+      <c r="D67" s="52">
         <v>5.3</v>
       </c>
-      <c r="E67" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F67" s="74"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="21"/>
+      <c r="E67" s="85"/>
+      <c r="F67" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="G67" s="44"/>
+      <c r="H67" s="16"/>
     </row>
     <row r="68" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B68" s="14">
+      <c r="B68" s="13">
         <v>46008</v>
       </c>
-      <c r="C68" s="16" t="str">
+      <c r="C68" s="15" t="str">
         <f>IF(ISBLANK(B68),"",TEXT(B68, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D68" s="69">
+      <c r="D68" s="52">
         <v>5.6</v>
       </c>
-      <c r="E68" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="F68" s="74"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="21">
+      <c r="E68" s="85"/>
+      <c r="F68" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G68" s="44"/>
+      <c r="H68" s="16">
         <v>46015</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B69" s="14">
+      <c r="B69" s="13">
         <v>46009</v>
       </c>
-      <c r="C69" s="16" t="str">
+      <c r="C69" s="15" t="str">
         <f>IF(ISBLANK(B69),"",TEXT(B69, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D69" s="69">
+      <c r="D69" s="52">
         <v>5.4</v>
       </c>
-      <c r="E69" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F69" s="74"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="21">
+      <c r="E69" s="85"/>
+      <c r="F69" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="G69" s="44"/>
+      <c r="H69" s="16">
         <v>46022</v>
       </c>
     </row>
     <row r="70" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B70" s="14">
+      <c r="B70" s="13">
         <v>46009</v>
       </c>
-      <c r="C70" s="16" t="str">
+      <c r="C70" s="15" t="str">
         <f>IF(ISBLANK(B70),"",TEXT(B70, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="F70" s="74"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="21">
+      <c r="D70" s="52"/>
+      <c r="E70" s="85"/>
+      <c r="F70" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="G70" s="44"/>
+      <c r="H70" s="16">
         <v>46009</v>
       </c>
     </row>
     <row r="71" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B71" s="21">
+      <c r="B71" s="13">
         <v>46015</v>
       </c>
-      <c r="C71" s="16" t="str">
+      <c r="C71" s="15" t="str">
         <f>IF(ISBLANK(B71),"",TEXT(B71, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D71" s="69">
+      <c r="D71" s="52">
         <v>2.1</v>
       </c>
-      <c r="E71" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="F71" s="74"/>
-      <c r="G71" s="58"/>
-      <c r="H71" s="21">
+      <c r="E71" s="85"/>
+      <c r="F71" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="G71" s="44"/>
+      <c r="H71" s="16">
         <v>46015</v>
       </c>
     </row>
     <row r="72" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B72" s="21">
+      <c r="B72" s="13">
         <v>46015</v>
       </c>
-      <c r="C72" s="16" t="str">
+      <c r="C72" s="15" t="str">
         <f>IF(ISBLANK(B72),"",TEXT(B72, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D72" s="69">
+      <c r="D72" s="52">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E72" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="F72" s="74"/>
-      <c r="G72" s="58"/>
-      <c r="H72" s="21">
+      <c r="E72" s="85"/>
+      <c r="F72" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="G72" s="44"/>
+      <c r="H72" s="16">
         <v>46015</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B73" s="21">
+      <c r="B73" s="13">
         <v>46015</v>
       </c>
-      <c r="C73" s="16" t="str">
+      <c r="C73" s="15" t="str">
         <f>IF(ISBLANK(B73),"",TEXT(B73, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="F73" s="74"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="21">
+      <c r="D73" s="52"/>
+      <c r="E73" s="85"/>
+      <c r="F73" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" s="44"/>
+      <c r="H73" s="16">
         <v>46015</v>
       </c>
     </row>
     <row r="74" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B74" s="21">
+      <c r="B74" s="13">
         <v>46015</v>
       </c>
-      <c r="C74" s="16" t="str">
+      <c r="C74" s="15" t="str">
         <f>IF(ISBLANK(B74),"",TEXT(B74, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="F74" s="74"/>
-      <c r="G74" s="58"/>
-      <c r="H74" s="21">
+      <c r="D74" s="52"/>
+      <c r="E74" s="85"/>
+      <c r="F74" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="G74" s="44"/>
+      <c r="H74" s="16">
         <v>46015</v>
       </c>
     </row>
     <row r="75" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B75" s="14">
+      <c r="B75" s="13">
         <v>46015</v>
       </c>
-      <c r="C75" s="16" t="str">
+      <c r="C75" s="15" t="str">
         <f>IF(ISBLANK(B75),"",TEXT(B75, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="F75" s="74"/>
-      <c r="G75" s="58"/>
-      <c r="H75" s="21">
+      <c r="D75" s="52"/>
+      <c r="E75" s="85"/>
+      <c r="F75" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="G75" s="44"/>
+      <c r="H75" s="16">
         <v>46015</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B76" s="14">
+      <c r="B76" s="13">
         <v>46022</v>
       </c>
-      <c r="C76" s="16" t="str">
+      <c r="C76" s="15" t="str">
         <f>IF(ISBLANK(B76),"",TEXT(B76, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="F76" s="74"/>
-      <c r="G76" s="58"/>
-      <c r="H76" s="21">
+      <c r="D76" s="52"/>
+      <c r="E76" s="85"/>
+      <c r="F76" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="G76" s="44"/>
+      <c r="H76" s="16">
         <v>46022</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B77" s="14">
+      <c r="B77" s="13">
         <v>46022</v>
       </c>
-      <c r="C77" s="16" t="str">
+      <c r="C77" s="15" t="str">
         <f>IF(ISBLANK(B77),"",TEXT(B77, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D77" s="69"/>
-      <c r="E77" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="F77" s="74"/>
-      <c r="G77" s="58"/>
-      <c r="H77" s="21">
+      <c r="D77" s="52"/>
+      <c r="E77" s="85"/>
+      <c r="F77" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="G77" s="44"/>
+      <c r="H77" s="16">
         <v>46022</v>
       </c>
     </row>
     <row r="78" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B78" s="14">
+      <c r="B78" s="13">
         <v>46022</v>
       </c>
-      <c r="C78" s="16" t="str">
+      <c r="C78" s="15" t="str">
         <f>IF(ISBLANK(B78),"",TEXT(B78, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D78" s="69"/>
-      <c r="E78" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="F78" s="74"/>
-      <c r="G78" s="58"/>
-      <c r="H78" s="21">
+      <c r="D78" s="52"/>
+      <c r="E78" s="85"/>
+      <c r="F78" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G78" s="44"/>
+      <c r="H78" s="16">
         <v>46022</v>
       </c>
     </row>
     <row r="79" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B79" s="21">
+      <c r="B79" s="13">
         <v>46024</v>
       </c>
-      <c r="C79" s="16" t="str">
+      <c r="C79" s="15" t="str">
         <f>IF(ISBLANK(B79),"",TEXT(B79, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D79" s="69">
+      <c r="D79" s="52">
         <v>0.1</v>
       </c>
-      <c r="E79" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="F79" s="74"/>
-      <c r="G79" s="58"/>
-      <c r="H79" s="21">
+      <c r="E79" s="85"/>
+      <c r="F79" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G79" s="44"/>
+      <c r="H79" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="80" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B80" s="21">
+      <c r="B80" s="13">
         <v>46024</v>
       </c>
-      <c r="C80" s="16" t="str">
+      <c r="C80" s="15" t="str">
         <f>IF(ISBLANK(B80),"",TEXT(B80, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D80" s="69">
+      <c r="D80" s="52">
         <v>0.15</v>
       </c>
-      <c r="E80" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F80" s="74"/>
-      <c r="G80" s="58"/>
-      <c r="H80" s="21">
+      <c r="E80" s="85"/>
+      <c r="F80" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G80" s="44"/>
+      <c r="H80" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B81" s="21">
+      <c r="B81" s="13">
         <v>46024</v>
       </c>
-      <c r="C81" s="16" t="str">
+      <c r="C81" s="15" t="str">
         <f>IF(ISBLANK(B81),"",TEXT(B81, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D81" s="69">
+      <c r="D81" s="52">
         <v>0.2</v>
       </c>
-      <c r="E81" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="F81" s="74"/>
-      <c r="G81" s="58"/>
-      <c r="H81" s="21">
+      <c r="E81" s="85"/>
+      <c r="F81" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G81" s="44"/>
+      <c r="H81" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="82" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B82" s="21">
+      <c r="B82" s="13">
         <v>46024</v>
       </c>
-      <c r="C82" s="16" t="str">
+      <c r="C82" s="15" t="str">
         <f>IF(ISBLANK(B82),"",TEXT(B82, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D82" s="69">
+      <c r="D82" s="52">
         <v>0.3</v>
       </c>
-      <c r="E82" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="F82" s="74"/>
-      <c r="G82" s="58"/>
-      <c r="H82" s="21">
+      <c r="E82" s="85"/>
+      <c r="F82" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="G82" s="44"/>
+      <c r="H82" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B83" s="21">
+      <c r="B83" s="13">
         <v>46024</v>
       </c>
-      <c r="C83" s="16" t="str">
+      <c r="C83" s="15" t="str">
         <f>IF(ISBLANK(B83),"",TEXT(B83, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D83" s="69">
+      <c r="D83" s="52">
         <v>0.4</v>
       </c>
-      <c r="E83" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="F83" s="74"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="21">
+      <c r="E83" s="85"/>
+      <c r="F83" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="G83" s="44"/>
+      <c r="H83" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="84" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B84" s="21">
+      <c r="B84" s="13">
         <v>46024</v>
       </c>
-      <c r="C84" s="16" t="str">
+      <c r="C84" s="15" t="str">
         <f>IF(ISBLANK(B84),"",TEXT(B84, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D84" s="69">
+      <c r="D84" s="52">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E84" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="F84" s="74"/>
-      <c r="G84" s="58"/>
-      <c r="H84" s="21">
+      <c r="E84" s="85"/>
+      <c r="F84" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="G84" s="44"/>
+      <c r="H84" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="85" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B85" s="14">
+      <c r="B85" s="13">
         <v>46024</v>
       </c>
-      <c r="C85" s="16" t="str">
+      <c r="C85" s="15" t="str">
         <f>IF(ISBLANK(B85),"",TEXT(B85, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D85" s="69">
+      <c r="D85" s="52">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E85" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="F85" s="74"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="21">
+      <c r="E85" s="85"/>
+      <c r="F85" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="G85" s="44"/>
+      <c r="H85" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B86" s="14">
+      <c r="B86" s="13">
         <v>46024</v>
       </c>
-      <c r="C86" s="16" t="str">
+      <c r="C86" s="15" t="str">
         <f>IF(ISBLANK(B86),"",TEXT(B86, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D86" s="69">
+      <c r="D86" s="52">
         <v>1.1299999999999999</v>
       </c>
-      <c r="E86" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="F86" s="74"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="21"/>
+      <c r="E86" s="85"/>
+      <c r="F86" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="G86" s="44"/>
+      <c r="H86" s="16"/>
     </row>
     <row r="87" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B87" s="14">
+      <c r="B87" s="13">
         <v>46024</v>
       </c>
-      <c r="C87" s="16" t="str">
+      <c r="C87" s="15" t="str">
         <f>IF(ISBLANK(B87),"",TEXT(B87, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D87" s="69">
+      <c r="D87" s="52">
         <v>1.2</v>
       </c>
-      <c r="E87" s="16" t="s">
+      <c r="E87" s="85"/>
+      <c r="F87" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F87" s="74"/>
-      <c r="G87" s="58"/>
-      <c r="H87" s="21">
+      <c r="G87" s="44"/>
+      <c r="H87" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B88" s="14">
+      <c r="B88" s="13">
         <v>46024</v>
       </c>
-      <c r="C88" s="16" t="str">
+      <c r="C88" s="15" t="str">
         <f>IF(ISBLANK(B88),"",TEXT(B88, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D88" s="69">
+      <c r="D88" s="52">
         <v>1.3</v>
       </c>
-      <c r="E88" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="F88" s="74"/>
-      <c r="G88" s="58"/>
-      <c r="H88" s="21"/>
+      <c r="E88" s="85"/>
+      <c r="F88" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="G88" s="44"/>
+      <c r="H88" s="16"/>
     </row>
     <row r="89" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B89" s="14">
+      <c r="B89" s="13">
         <v>46024</v>
       </c>
-      <c r="C89" s="16" t="str">
+      <c r="C89" s="15" t="str">
         <f>IF(ISBLANK(B89),"",TEXT(B89, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D89" s="69">
+      <c r="D89" s="52">
         <v>2.1</v>
       </c>
-      <c r="E89" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="F89" s="74"/>
-      <c r="G89" s="58"/>
-      <c r="H89" s="21">
+      <c r="E89" s="85"/>
+      <c r="F89" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="G89" s="44"/>
+      <c r="H89" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B90" s="14">
+      <c r="B90" s="13">
         <v>46024</v>
       </c>
-      <c r="C90" s="16" t="str">
+      <c r="C90" s="15" t="str">
         <f>IF(ISBLANK(B90),"",TEXT(B90, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D90" s="69">
+      <c r="D90" s="52">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E90" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="F90" s="74"/>
-      <c r="G90" s="58"/>
-      <c r="H90" s="21">
+      <c r="E90" s="85"/>
+      <c r="F90" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="G90" s="44"/>
+      <c r="H90" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B91" s="14">
+      <c r="B91" s="13">
         <v>46024</v>
       </c>
-      <c r="C91" s="16" t="str">
+      <c r="C91" s="15" t="str">
         <f>IF(ISBLANK(B91),"",TEXT(B91, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D91" s="69">
+      <c r="D91" s="52">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E91" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="F91" s="74"/>
-      <c r="G91" s="58"/>
-      <c r="H91" s="21">
+      <c r="E91" s="85"/>
+      <c r="F91" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="G91" s="44"/>
+      <c r="H91" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="92" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B92" s="14">
+      <c r="B92" s="13">
         <v>46024</v>
       </c>
-      <c r="C92" s="16" t="str">
+      <c r="C92" s="15" t="str">
         <f>IF(ISBLANK(B92),"",TEXT(B92, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D92" s="69">
+      <c r="D92" s="52">
         <v>3.1</v>
       </c>
-      <c r="E92" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="F92" s="74"/>
-      <c r="G92" s="58"/>
-      <c r="H92" s="21">
+      <c r="E92" s="85"/>
+      <c r="F92" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G92" s="44"/>
+      <c r="H92" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B93" s="14">
+      <c r="B93" s="13">
         <v>46024</v>
       </c>
-      <c r="C93" s="16" t="str">
+      <c r="C93" s="15" t="str">
         <f>IF(ISBLANK(B93),"",TEXT(B93, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D93" s="69">
+      <c r="D93" s="52">
         <v>3.2</v>
       </c>
-      <c r="E93" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="F93" s="74"/>
-      <c r="G93" s="58"/>
-      <c r="H93" s="21">
+      <c r="E93" s="85"/>
+      <c r="F93" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G93" s="44"/>
+      <c r="H93" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="94" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B94" s="14">
+      <c r="B94" s="13">
         <v>46024</v>
       </c>
-      <c r="C94" s="16" t="str">
+      <c r="C94" s="15" t="str">
         <f>IF(ISBLANK(B94),"",TEXT(B94, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D94" s="69">
+      <c r="D94" s="52">
         <v>3.3</v>
       </c>
-      <c r="E94" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="F94" s="74"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="21">
+      <c r="E94" s="85"/>
+      <c r="F94" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="G94" s="44"/>
+      <c r="H94" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B95" s="14">
+      <c r="B95" s="13">
         <v>46024</v>
       </c>
-      <c r="C95" s="16" t="str">
+      <c r="C95" s="15" t="str">
         <f>IF(ISBLANK(B95),"",TEXT(B95, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D95" s="69">
+      <c r="D95" s="52">
         <v>3.4</v>
       </c>
-      <c r="E95" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="F95" s="74"/>
-      <c r="G95" s="58"/>
-      <c r="H95" s="21">
+      <c r="E95" s="85"/>
+      <c r="F95" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="G95" s="44"/>
+      <c r="H95" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="96" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B96" s="14">
+      <c r="B96" s="13">
         <v>46024</v>
       </c>
-      <c r="C96" s="16" t="str">
+      <c r="C96" s="15" t="str">
         <f>IF(ISBLANK(B96),"",TEXT(B96, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D96" s="69">
+      <c r="D96" s="52">
         <v>3.6</v>
       </c>
-      <c r="E96" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="F96" s="74"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="21">
+      <c r="E96" s="85"/>
+      <c r="F96" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="G96" s="44"/>
+      <c r="H96" s="16">
         <v>46024</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B97" s="14">
+      <c r="B97" s="13">
         <v>46024</v>
       </c>
-      <c r="C97" s="16" t="str">
+      <c r="C97" s="15" t="str">
         <f>IF(ISBLANK(B97),"",TEXT(B97, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D97" s="69">
+      <c r="D97" s="52">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E97" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="F97" s="74"/>
-      <c r="G97" s="58"/>
-      <c r="H97" s="30"/>
+      <c r="E97" s="44"/>
+      <c r="F97" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="G97" s="44"/>
+      <c r="H97" s="17"/>
     </row>
     <row r="98" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B98" s="14">
+      <c r="B98" s="13">
         <v>46024</v>
       </c>
-      <c r="C98" s="16" t="str">
+      <c r="C98" s="15" t="str">
         <f>IF(ISBLANK(B98),"",TEXT(B98, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D98" s="69">
+      <c r="D98" s="52">
         <v>4.2</v>
       </c>
-      <c r="E98" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="F98" s="74"/>
-      <c r="G98" s="58"/>
-      <c r="H98" s="30"/>
+      <c r="E98" s="44"/>
+      <c r="F98" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="G98" s="44"/>
+      <c r="H98" s="17"/>
     </row>
     <row r="99" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B99" s="14">
+      <c r="B99" s="13">
         <v>46024</v>
       </c>
-      <c r="C99" s="16" t="str">
+      <c r="C99" s="15" t="str">
         <f>IF(ISBLANK(B99),"",TEXT(B99, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D99" s="69">
+      <c r="D99" s="52">
         <v>4.3</v>
       </c>
-      <c r="E99" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="F99" s="74"/>
-      <c r="G99" s="58"/>
-      <c r="H99" s="30"/>
+      <c r="E99" s="44"/>
+      <c r="F99" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="G99" s="44"/>
+      <c r="H99" s="17"/>
     </row>
     <row r="100" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B100" s="14">
+      <c r="B100" s="13">
         <v>46027</v>
       </c>
-      <c r="C100" s="16" t="str">
+      <c r="C100" s="15" t="str">
         <f>IF(ISBLANK(B100),"",TEXT(B100, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D100" s="69"/>
-      <c r="E100" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="F100" s="74"/>
-      <c r="G100" s="58"/>
-      <c r="H100" s="21">
+      <c r="D100" s="52"/>
+      <c r="E100" s="85"/>
+      <c r="F100" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="G100" s="44"/>
+      <c r="H100" s="16">
         <v>46027</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B101" s="14">
+      <c r="B101" s="13">
         <v>46028</v>
       </c>
-      <c r="C101" s="16" t="str">
+      <c r="C101" s="15" t="str">
         <f>IF(ISBLANK(B101),"",TEXT(B101, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D101" s="69"/>
-      <c r="E101" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F101" s="75"/>
-      <c r="G101" s="58"/>
-      <c r="H101" s="21">
+      <c r="D101" s="52"/>
+      <c r="E101" s="85"/>
+      <c r="F101" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G101" s="44"/>
+      <c r="H101" s="16">
         <v>46027</v>
       </c>
     </row>
     <row r="102" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B102" s="14">
+      <c r="B102" s="13">
         <v>46028</v>
       </c>
-      <c r="C102" s="16" t="str">
+      <c r="C102" s="15" t="str">
         <f>IF(ISBLANK(B102),"",TEXT(B102, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D102" s="69"/>
-      <c r="E102" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="F102" s="74"/>
-      <c r="G102" s="58"/>
-      <c r="H102" s="30"/>
+      <c r="D102" s="52"/>
+      <c r="E102" s="44"/>
+      <c r="F102" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="G102" s="44"/>
+      <c r="H102" s="17"/>
     </row>
     <row r="103" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B103" s="14">
+      <c r="B103" s="13">
         <v>46028</v>
       </c>
-      <c r="C103" s="16" t="str">
+      <c r="C103" s="15" t="str">
         <f>IF(ISBLANK(B103),"",TEXT(B103, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D103" s="69"/>
-      <c r="E103" s="65" t="s">
-        <v>227</v>
-      </c>
-      <c r="F103" s="76"/>
-      <c r="G103" s="58"/>
-      <c r="H103" s="30"/>
+      <c r="D103" s="52"/>
+      <c r="E103" s="44"/>
+      <c r="F103" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="G103" s="44"/>
+      <c r="H103" s="17"/>
     </row>
     <row r="104" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B104" s="14">
+      <c r="B104" s="13">
         <v>46030</v>
       </c>
-      <c r="C104" s="16" t="str">
+      <c r="C104" s="15" t="str">
         <f>IF(ISBLANK(B104),"",TEXT(B104, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D104" s="69"/>
-      <c r="E104" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="F104" s="74"/>
-      <c r="G104" s="58" t="s">
-        <v>246</v>
-      </c>
-      <c r="H104" s="21">
+      <c r="D104" s="52"/>
+      <c r="E104" s="85"/>
+      <c r="F104" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="G104" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="H104" s="16">
         <v>46027</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B105" s="14">
+      <c r="B105" s="13">
         <v>46030</v>
       </c>
-      <c r="C105" s="16" t="str">
+      <c r="C105" s="15" t="str">
         <f>IF(ISBLANK(B105),"",TEXT(B105, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D105" s="69"/>
-      <c r="E105" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="F105" s="74"/>
-      <c r="G105" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H105" s="21">
+      <c r="D105" s="52"/>
+      <c r="E105" s="85"/>
+      <c r="F105" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="G105" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H105" s="16">
         <v>46030</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B106" s="14">
+      <c r="B106" s="13">
         <v>46034</v>
       </c>
-      <c r="C106" s="16" t="str">
+      <c r="C106" s="15" t="str">
         <f>IF(ISBLANK(B106),"",TEXT(B106, "dddd"))</f>
         <v>Monday</v>
       </c>
-      <c r="D106" s="69"/>
-      <c r="E106" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="F106" s="74"/>
-      <c r="G106" s="58" t="s">
-        <v>247</v>
-      </c>
-      <c r="H106" s="21">
+      <c r="D106" s="52"/>
+      <c r="E106" s="85"/>
+      <c r="F106" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="G106" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="H106" s="16">
         <v>46034</v>
       </c>
     </row>
     <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B107" s="14">
+      <c r="B107" s="13">
         <v>46035</v>
       </c>
-      <c r="C107" s="16" t="str">
+      <c r="C107" s="15" t="str">
         <f>IF(ISBLANK(B107),"",TEXT(B107, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D107" s="69">
+      <c r="D107" s="52">
         <v>3.2</v>
       </c>
-      <c r="E107" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="F107" s="74"/>
-      <c r="G107" s="58"/>
-      <c r="H107" s="21">
+      <c r="E107" s="85"/>
+      <c r="F107" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="G107" s="44"/>
+      <c r="H107" s="16">
         <v>46035</v>
       </c>
     </row>
     <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B108" s="14">
+      <c r="B108" s="13">
         <v>46035</v>
       </c>
-      <c r="C108" s="16" t="str">
+      <c r="C108" s="15" t="str">
         <f>IF(ISBLANK(B108),"",TEXT(B108, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D108" s="69">
+      <c r="D108" s="52">
         <v>3.3</v>
       </c>
-      <c r="E108" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="F108" s="74"/>
-      <c r="G108" s="58"/>
-      <c r="H108" s="21">
+      <c r="E108" s="85"/>
+      <c r="F108" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="G108" s="44"/>
+      <c r="H108" s="16">
         <v>46035</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B109" s="14">
+      <c r="B109" s="13">
         <v>46036</v>
       </c>
-      <c r="C109" s="16" t="str">
+      <c r="C109" s="15" t="str">
         <f>IF(ISBLANK(B109),"",TEXT(B109, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D109" s="69"/>
-      <c r="E109" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="F109" s="74"/>
-      <c r="G109" s="58"/>
-      <c r="H109" s="21">
+      <c r="D109" s="52"/>
+      <c r="E109" s="85"/>
+      <c r="F109" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="G109" s="44"/>
+      <c r="H109" s="16">
         <v>46036</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B110" s="14">
+      <c r="B110" s="13">
         <v>46036</v>
       </c>
-      <c r="C110" s="16" t="str">
+      <c r="C110" s="15" t="str">
         <f>IF(ISBLANK(B110),"",TEXT(B110, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D110" s="69"/>
-      <c r="E110" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="F110" s="74"/>
-      <c r="G110" s="58"/>
-      <c r="H110" s="21">
+      <c r="D110" s="52"/>
+      <c r="E110" s="85"/>
+      <c r="F110" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="G110" s="44"/>
+      <c r="H110" s="16">
         <v>46036</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B111" s="14">
+      <c r="B111" s="13">
         <v>46036</v>
       </c>
-      <c r="C111" s="16" t="str">
+      <c r="C111" s="15" t="str">
         <f>IF(ISBLANK(B111),"",TEXT(B111, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D111" s="69"/>
-      <c r="E111" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="F111" s="74"/>
-      <c r="G111" s="58"/>
-      <c r="H111" s="21">
+      <c r="D111" s="52"/>
+      <c r="E111" s="85"/>
+      <c r="F111" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="G111" s="44"/>
+      <c r="H111" s="16">
         <v>46036</v>
       </c>
     </row>
     <row r="112" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B112" s="14">
+      <c r="B112" s="13">
         <v>46036</v>
       </c>
-      <c r="C112" s="16" t="str">
+      <c r="C112" s="15" t="str">
         <f>IF(ISBLANK(B112),"",TEXT(B112, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D112" s="69"/>
-      <c r="E112" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="F112" s="74"/>
-      <c r="G112" s="58"/>
-      <c r="H112" s="21">
+      <c r="D112" s="52"/>
+      <c r="E112" s="85"/>
+      <c r="F112" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="G112" s="44"/>
+      <c r="H112" s="16">
         <v>46036</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B113" s="14">
+      <c r="B113" s="13">
         <v>46037</v>
       </c>
-      <c r="C113" s="16" t="str">
+      <c r="C113" s="15" t="str">
         <f>IF(ISBLANK(B113),"",TEXT(B113, "dddd"))</f>
         <v>Thursday</v>
       </c>
-      <c r="D113" s="69"/>
-      <c r="E113" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="F113" s="74"/>
-      <c r="G113" s="58"/>
-      <c r="H113" s="21">
+      <c r="D113" s="52"/>
+      <c r="E113" s="85"/>
+      <c r="F113" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="G113" s="44"/>
+      <c r="H113" s="16">
         <v>46037</v>
       </c>
     </row>
-    <row r="114" spans="2:8" ht="80" x14ac:dyDescent="0.2">
-      <c r="B114" s="14">
+    <row r="114" spans="2:8" ht="96" x14ac:dyDescent="0.2">
+      <c r="B114" s="13">
         <v>46038</v>
       </c>
-      <c r="C114" s="16" t="str">
+      <c r="C114" s="15" t="str">
         <f>IF(ISBLANK(B114),"",TEXT(B114, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D114" s="69">
+      <c r="D114" s="52">
         <v>0.01</v>
       </c>
-      <c r="E114" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="F114" s="74"/>
-      <c r="G114" s="58"/>
-      <c r="H114" s="21"/>
+      <c r="E114" s="85"/>
+      <c r="F114" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="G114" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H114" s="16">
+        <v>46038</v>
+      </c>
     </row>
     <row r="115" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B115" s="14">
+      <c r="B115" s="13">
         <v>46038</v>
       </c>
-      <c r="C115" s="16" t="str">
+      <c r="C115" s="15" t="str">
         <f>IF(ISBLANK(B115),"",TEXT(B115, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D115" s="69">
+      <c r="D115" s="52">
         <v>0.1</v>
       </c>
-      <c r="E115" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="F115" s="74"/>
-      <c r="G115" s="58"/>
-      <c r="H115" s="21"/>
+      <c r="E115" s="85"/>
+      <c r="F115" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="G115" s="44" t="s">
+        <v>243</v>
+      </c>
+      <c r="H115" s="16">
+        <v>46038</v>
+      </c>
     </row>
     <row r="116" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B116" s="14">
+      <c r="B116" s="13">
         <v>46038</v>
       </c>
-      <c r="C116" s="16" t="str">
+      <c r="C116" s="15" t="str">
         <f>IF(ISBLANK(B116),"",TEXT(B116, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D116" s="69">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E116" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="F116" s="74">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="G116" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="H116" s="21"/>
+      <c r="D116" s="52">
+        <v>3.3</v>
+      </c>
+      <c r="E116" s="85"/>
+      <c r="F116" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="G116" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="H116" s="16">
+        <v>46375</v>
+      </c>
     </row>
     <row r="117" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B117" s="14">
+      <c r="B117" s="13">
         <v>46038</v>
       </c>
-      <c r="C117" s="16" t="str">
+      <c r="C117" s="15" t="str">
         <f>IF(ISBLANK(B117),"",TEXT(B117, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D117" s="69">
-        <v>1.2</v>
-      </c>
-      <c r="E117" s="16" t="s">
+      <c r="D117" s="52"/>
+      <c r="E117" s="85"/>
+      <c r="F117" s="15"/>
+      <c r="G117" s="44"/>
+      <c r="H117" s="16"/>
+    </row>
+    <row r="118" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B118" s="78">
+        <v>46042</v>
+      </c>
+      <c r="C118" s="15" t="str">
+        <f>IF(ISBLANK(B118),"",TEXT(B118, "dddd"))</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="D118" s="52"/>
+      <c r="E118" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="F118" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="G118" s="44"/>
+      <c r="H118" s="16">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B119" s="78">
+        <v>46042</v>
+      </c>
+      <c r="C119" s="15" t="str">
+        <f>IF(ISBLANK(B119),"",TEXT(B119, "dddd"))</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="D119" s="52"/>
+      <c r="E119" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="F119" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="G119" s="44"/>
+      <c r="H119" s="16">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B120" s="78">
+        <v>46042</v>
+      </c>
+      <c r="C120" s="15" t="str">
+        <f>IF(ISBLANK(B120),"",TEXT(B120, "dddd"))</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="D120" s="52"/>
+      <c r="E120" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G120" s="44"/>
+      <c r="H120" s="16"/>
+    </row>
+    <row r="121" spans="2:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="B121" s="78">
+        <v>46042</v>
+      </c>
+      <c r="C121" s="15" t="str">
+        <f>IF(ISBLANK(B121),"",TEXT(B121, "dddd"))</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="D121" s="52"/>
+      <c r="E121" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="F121" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="G121" s="44"/>
+      <c r="H121" s="16"/>
+    </row>
+    <row r="122" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B122" s="78">
+        <v>46042</v>
+      </c>
+      <c r="C122" s="15" t="str">
+        <f>IF(ISBLANK(B122),"",TEXT(B122, "dddd"))</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="D122" s="52"/>
+      <c r="E122" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="F122" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="G122" s="44"/>
+      <c r="H122" s="16"/>
+    </row>
+    <row r="123" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B123" s="78">
+        <v>46043</v>
+      </c>
+      <c r="C123" s="15" t="str">
+        <f>IF(ISBLANK(B123),"",TEXT(B123, "dddd"))</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="D123" s="52"/>
+      <c r="E123" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="F123" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="G123" s="44"/>
+      <c r="H123" s="16"/>
+    </row>
+    <row r="124" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B124" s="78">
+        <v>46043</v>
+      </c>
+      <c r="C124" s="15" t="str">
+        <f>IF(ISBLANK(B124),"",TEXT(B124, "dddd"))</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="D124" s="52"/>
+      <c r="E124" s="85" t="s">
+        <v>250</v>
+      </c>
+      <c r="F124" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="G124" s="44"/>
+      <c r="H124" s="16"/>
+    </row>
+    <row r="125" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B125" s="78">
+        <v>46043</v>
+      </c>
+      <c r="C125" s="15" t="str">
+        <f>IF(ISBLANK(B125),"",TEXT(B125, "dddd"))</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="D125" s="52"/>
+      <c r="E125" s="85" t="s">
+        <v>254</v>
+      </c>
+      <c r="F125" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="G125" s="44"/>
+      <c r="H125" s="16"/>
+    </row>
+    <row r="126" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B126" s="78">
+        <v>46043</v>
+      </c>
+      <c r="C126" s="15" t="str">
+        <f>IF(ISBLANK(B126),"",TEXT(B126, "dddd"))</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="D126" s="52"/>
+      <c r="E126" s="85" t="s">
+        <v>254</v>
+      </c>
+      <c r="F126" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="G126" s="44"/>
+      <c r="H126" s="16"/>
+    </row>
+    <row r="127" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B127" s="78">
+        <v>46043</v>
+      </c>
+      <c r="C127" s="15" t="str">
+        <f>IF(ISBLANK(B127),"",TEXT(B127, "dddd"))</f>
+        <v>Wednesday</v>
+      </c>
+      <c r="D127" s="52"/>
+      <c r="E127" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="F127" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="G127" s="44"/>
+      <c r="H127" s="16"/>
+    </row>
+    <row r="128" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B128" s="78">
+        <v>46044</v>
+      </c>
+      <c r="C128" s="15" t="str">
+        <f>IF(ISBLANK(B128),"",TEXT(B128, "dddd"))</f>
+        <v>Thursday</v>
+      </c>
+      <c r="D128" s="52"/>
+      <c r="E128" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="F128" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="G128" s="44"/>
+      <c r="H128" s="16"/>
+    </row>
+    <row r="129" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B129" s="78">
+        <v>46044</v>
+      </c>
+      <c r="C129" s="15" t="str">
+        <f>IF(ISBLANK(B129),"",TEXT(B129, "dddd"))</f>
+        <v>Thursday</v>
+      </c>
+      <c r="D129" s="52"/>
+      <c r="E129" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="F129" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="G129" s="44"/>
+      <c r="H129" s="16"/>
+    </row>
+    <row r="130" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B130" s="78">
+        <v>46045</v>
+      </c>
+      <c r="C130" s="15" t="str">
+        <f>IF(ISBLANK(B130),"",TEXT(B130, "dddd"))</f>
+        <v>Friday</v>
+      </c>
+      <c r="D130" s="52"/>
+      <c r="E130" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="F130" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="G130" s="44"/>
+      <c r="H130" s="16"/>
+    </row>
+    <row r="131" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B131" s="78">
+        <v>46045</v>
+      </c>
+      <c r="C131" s="15" t="str">
+        <f>IF(ISBLANK(B131),"",TEXT(B131, "dddd"))</f>
+        <v>Friday</v>
+      </c>
+      <c r="D131" s="52"/>
+      <c r="E131" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="F131" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="F117" s="74"/>
-      <c r="G117" s="58"/>
-      <c r="H117" s="21"/>
-    </row>
-    <row r="118" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B118" s="14">
-        <v>46038</v>
-      </c>
-      <c r="C118" s="16" t="str">
-        <f>IF(ISBLANK(B118),"",TEXT(B118, "dddd"))</f>
+      <c r="G131" s="44"/>
+      <c r="H131" s="16"/>
+    </row>
+    <row r="132" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B132" s="78">
+        <v>46045</v>
+      </c>
+      <c r="C132" s="15" t="str">
+        <f>IF(ISBLANK(B132),"",TEXT(B132, "dddd"))</f>
         <v>Friday</v>
       </c>
-      <c r="D118" s="69">
-        <v>1.3</v>
-      </c>
-      <c r="E118" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="F118" s="74"/>
-      <c r="G118" s="58"/>
-      <c r="H118" s="21"/>
-    </row>
-    <row r="119" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B119" s="14">
-        <v>46038</v>
-      </c>
-      <c r="C119" s="16" t="str">
-        <f>IF(ISBLANK(B119),"",TEXT(B119, "dddd"))</f>
-        <v>Friday</v>
-      </c>
-      <c r="D119" s="69">
-        <v>1.4</v>
-      </c>
-      <c r="E119" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="F119" s="74"/>
-      <c r="G119" s="58"/>
-      <c r="H119" s="21"/>
-    </row>
-    <row r="120" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B120" s="14">
-        <v>46038</v>
-      </c>
-      <c r="C120" s="16" t="str">
-        <f>IF(ISBLANK(B120),"",TEXT(B120, "dddd"))</f>
-        <v>Friday</v>
-      </c>
-      <c r="D120" s="69">
-        <v>3</v>
-      </c>
-      <c r="E120" s="16" t="s">
+      <c r="D132" s="52"/>
+      <c r="E132" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="F132" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="G132" s="44"/>
+      <c r="H132" s="16"/>
+    </row>
+    <row r="133" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B133" s="13">
+        <v>46055</v>
+      </c>
+      <c r="C133" s="15" t="str">
+        <f>IF(ISBLANK(B133),"",TEXT(B133, "dddd"))</f>
+        <v>Monday</v>
+      </c>
+      <c r="D133" s="52"/>
+      <c r="E133" s="85"/>
+      <c r="F133" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="F120" s="74"/>
-      <c r="G120" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H120" s="21"/>
-    </row>
-    <row r="121" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B121" s="14">
-        <v>46038</v>
-      </c>
-      <c r="C121" s="16" t="str">
-        <f>IF(ISBLANK(B121),"",TEXT(B121, "dddd"))</f>
-        <v>Friday</v>
-      </c>
-      <c r="D121" s="69">
-        <v>3.1</v>
-      </c>
-      <c r="E121" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="F121" s="74"/>
-      <c r="G121" s="58" t="s">
-        <v>248</v>
-      </c>
-      <c r="H121" s="21"/>
-    </row>
-    <row r="122" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B122" s="14">
-        <v>46038</v>
-      </c>
-      <c r="C122" s="16" t="str">
-        <f>IF(ISBLANK(B122),"",TEXT(B122, "dddd"))</f>
-        <v>Friday</v>
-      </c>
-      <c r="D122" s="69">
-        <v>3.2</v>
-      </c>
-      <c r="E122" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="F122" s="74"/>
-      <c r="G122" s="58" t="s">
-        <v>249</v>
-      </c>
-      <c r="H122" s="21"/>
-    </row>
-    <row r="123" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B123" s="14">
-        <v>46038</v>
-      </c>
-      <c r="C123" s="16" t="str">
-        <f>IF(ISBLANK(B123),"",TEXT(B123, "dddd"))</f>
-        <v>Friday</v>
-      </c>
-      <c r="D123" s="69">
-        <v>3.3</v>
-      </c>
-      <c r="E123" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="F123" s="74"/>
-      <c r="G123" s="58" t="s">
-        <v>248</v>
-      </c>
-      <c r="H123" s="21"/>
-    </row>
-    <row r="124" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B124" s="14">
-        <v>46038</v>
-      </c>
-      <c r="C124" s="16" t="str">
-        <f>IF(ISBLANK(B124),"",TEXT(B124, "dddd"))</f>
-        <v>Friday</v>
-      </c>
-      <c r="D124" s="69"/>
-      <c r="E124" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="F124" s="74"/>
-      <c r="G124" s="58"/>
-      <c r="H124" s="21"/>
-    </row>
-    <row r="125" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B125" s="14">
-        <v>46038</v>
-      </c>
-      <c r="C125" s="16" t="str">
-        <f>IF(ISBLANK(B125),"",TEXT(B125, "dddd"))</f>
-        <v>Friday</v>
-      </c>
-      <c r="D125" s="69"/>
-      <c r="E125" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="F125" s="74"/>
-      <c r="G125" s="58"/>
-      <c r="H125" s="21"/>
-    </row>
-    <row r="126" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B126" s="14">
-        <v>46042</v>
-      </c>
-      <c r="C126" s="16" t="str">
-        <f>IF(ISBLANK(B126),"",TEXT(B126, "dddd"))</f>
-        <v>Tuesday</v>
-      </c>
-      <c r="D126" s="69">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E126" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="F126" s="74"/>
-      <c r="G126" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H126" s="21"/>
-    </row>
-    <row r="127" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B127" s="14">
-        <v>46042</v>
-      </c>
-      <c r="C127" s="16" t="str">
-        <f>IF(ISBLANK(B127),"",TEXT(B127, "dddd"))</f>
-        <v>Tuesday</v>
-      </c>
-      <c r="D127" s="69">
-        <v>1.2</v>
-      </c>
-      <c r="E127" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="F127" s="74"/>
-      <c r="G127" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H127" s="21"/>
-    </row>
-    <row r="128" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B128" s="14">
-        <v>46042</v>
-      </c>
-      <c r="C128" s="16" t="str">
-        <f>IF(ISBLANK(B128),"",TEXT(B128, "dddd"))</f>
-        <v>Tuesday</v>
-      </c>
-      <c r="D128" s="69">
-        <v>1.3</v>
-      </c>
-      <c r="E128" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="F128" s="74"/>
-      <c r="G128" s="58" t="s">
-        <v>249</v>
-      </c>
-      <c r="H128" s="21"/>
-    </row>
-    <row r="129" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B129" s="14">
-        <v>46042</v>
-      </c>
-      <c r="C129" s="16" t="str">
-        <f>IF(ISBLANK(B129),"",TEXT(B129, "dddd"))</f>
-        <v>Tuesday</v>
-      </c>
-      <c r="D129" s="69">
-        <v>1.4</v>
-      </c>
-      <c r="E129" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="F129" s="74"/>
-      <c r="G129" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H129" s="21"/>
-    </row>
-    <row r="130" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B130" s="14">
-        <v>46042</v>
-      </c>
-      <c r="C130" s="16" t="str">
-        <f>IF(ISBLANK(B130),"",TEXT(B130, "dddd"))</f>
-        <v>Tuesday</v>
-      </c>
-      <c r="D130" s="69">
-        <v>1.45</v>
-      </c>
-      <c r="E130" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="F130" s="74"/>
-      <c r="G130" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H130" s="21"/>
-    </row>
-    <row r="131" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B131" s="14">
-        <v>46042</v>
-      </c>
-      <c r="C131" s="16" t="str">
-        <f>IF(ISBLANK(B131),"",TEXT(B131, "dddd"))</f>
-        <v>Tuesday</v>
-      </c>
-      <c r="D131" s="69">
-        <v>1.5</v>
-      </c>
-      <c r="E131" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="F131" s="74"/>
-      <c r="G131" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H131" s="21"/>
-    </row>
-    <row r="132" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B132" s="14">
-        <v>46044</v>
-      </c>
-      <c r="C132" s="16" t="str">
-        <f>IF(ISBLANK(B132),"",TEXT(B132, "dddd"))</f>
-        <v>Thursday</v>
-      </c>
-      <c r="D132" s="69"/>
-      <c r="E132" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="F132" s="74"/>
-      <c r="G132" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="H132" s="21"/>
-    </row>
-    <row r="133" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B133" s="14">
-        <v>46044</v>
-      </c>
-      <c r="C133" s="16" t="str">
-        <f>IF(ISBLANK(B133),"",TEXT(B133, "dddd"))</f>
-        <v>Thursday</v>
-      </c>
-      <c r="D133" s="69"/>
-      <c r="E133" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="F133" s="74"/>
-      <c r="G133" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="H133" s="21"/>
+      <c r="G133" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H133" s="16"/>
     </row>
     <row r="134" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B134" s="14">
-        <v>46044</v>
-      </c>
-      <c r="C134" s="16" t="str">
+      <c r="B134" s="13"/>
+      <c r="C134" s="15" t="str">
         <f>IF(ISBLANK(B134),"",TEXT(B134, "dddd"))</f>
-        <v>Thursday</v>
-      </c>
-      <c r="D134" s="69"/>
-      <c r="E134" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="F134" s="74"/>
-      <c r="G134" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="H134" s="21"/>
+        <v/>
+      </c>
+      <c r="D134" s="52"/>
+      <c r="E134" s="85"/>
+      <c r="F134" s="15"/>
+      <c r="G134" s="44"/>
+      <c r="H134" s="16"/>
     </row>
     <row r="135" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B135" s="14">
-        <v>46044</v>
-      </c>
-      <c r="C135" s="16" t="str">
+      <c r="B135" s="13"/>
+      <c r="C135" s="15" t="str">
         <f>IF(ISBLANK(B135),"",TEXT(B135, "dddd"))</f>
-        <v>Thursday</v>
-      </c>
-      <c r="D135" s="69"/>
-      <c r="E135" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="F135" s="74"/>
-      <c r="G135" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="H135" s="21"/>
+        <v/>
+      </c>
+      <c r="D135" s="52"/>
+      <c r="E135" s="85"/>
+      <c r="F135" s="15"/>
+      <c r="G135" s="44"/>
+      <c r="H135" s="16"/>
     </row>
     <row r="136" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B136" s="14">
-        <v>46044</v>
-      </c>
-      <c r="C136" s="16" t="str">
+      <c r="B136" s="13"/>
+      <c r="C136" s="15" t="str">
         <f>IF(ISBLANK(B136),"",TEXT(B136, "dddd"))</f>
-        <v>Thursday</v>
-      </c>
-      <c r="D136" s="69"/>
-      <c r="E136" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="F136" s="74"/>
-      <c r="G136" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="H136" s="21"/>
+        <v/>
+      </c>
+      <c r="D136" s="52"/>
+      <c r="E136" s="85"/>
+      <c r="F136" s="15"/>
+      <c r="G136" s="44"/>
+      <c r="H136" s="16"/>
     </row>
     <row r="137" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B137" s="14">
-        <v>46055</v>
-      </c>
-      <c r="C137" s="16" t="str">
+      <c r="B137" s="13"/>
+      <c r="C137" s="15" t="str">
         <f>IF(ISBLANK(B137),"",TEXT(B137, "dddd"))</f>
-        <v>Monday</v>
-      </c>
-      <c r="D137" s="69"/>
-      <c r="E137" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F137" s="74"/>
-      <c r="G137" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H137" s="21"/>
+        <v/>
+      </c>
+      <c r="D137" s="52"/>
+      <c r="E137" s="85"/>
+      <c r="F137" s="15"/>
+      <c r="G137" s="44"/>
+      <c r="H137" s="16"/>
     </row>
     <row r="138" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B138" s="14"/>
-      <c r="C138" s="16" t="str">
+      <c r="B138" s="13"/>
+      <c r="C138" s="15" t="str">
         <f>IF(ISBLANK(B138),"",TEXT(B138, "dddd"))</f>
         <v/>
       </c>
-      <c r="D138" s="69"/>
-      <c r="E138" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="F138" s="74"/>
-      <c r="G138" s="58" t="s">
-        <v>246</v>
-      </c>
-      <c r="H138" s="21"/>
+      <c r="D138" s="52"/>
+      <c r="E138" s="85"/>
+      <c r="F138" s="15"/>
+      <c r="G138" s="44"/>
+      <c r="H138" s="16"/>
     </row>
     <row r="139" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B139" s="14"/>
-      <c r="C139" s="16" t="str">
+      <c r="B139" s="13"/>
+      <c r="C139" s="15" t="str">
         <f>IF(ISBLANK(B139),"",TEXT(B139, "dddd"))</f>
         <v/>
       </c>
-      <c r="D139" s="69"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="74"/>
-      <c r="G139" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="H139" s="21"/>
+      <c r="D139" s="52"/>
+      <c r="E139" s="85"/>
+      <c r="F139" s="15"/>
+      <c r="G139" s="44"/>
+      <c r="H139" s="16"/>
     </row>
     <row r="140" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B140" s="14"/>
-      <c r="C140" s="16" t="str">
+      <c r="B140" s="13"/>
+      <c r="C140" s="15" t="str">
         <f>IF(ISBLANK(B140),"",TEXT(B140, "dddd"))</f>
         <v/>
       </c>
-      <c r="D140" s="69"/>
-      <c r="E140" s="16"/>
-      <c r="F140" s="74"/>
-      <c r="G140" s="58" t="s">
-        <v>248</v>
-      </c>
-      <c r="H140" s="21"/>
+      <c r="D140" s="52"/>
+      <c r="E140" s="85"/>
+      <c r="F140" s="15"/>
+      <c r="G140" s="44"/>
+      <c r="H140" s="16"/>
     </row>
     <row r="141" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B141" s="14"/>
-      <c r="C141" s="16" t="str">
+      <c r="B141" s="13"/>
+      <c r="C141" s="15" t="str">
         <f>IF(ISBLANK(B141),"",TEXT(B141, "dddd"))</f>
         <v/>
       </c>
-      <c r="D141" s="69"/>
-      <c r="E141" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="F141" s="74"/>
-      <c r="G141" s="58" t="s">
-        <v>249</v>
-      </c>
-      <c r="H141" s="21"/>
+      <c r="D141" s="52"/>
+      <c r="E141" s="85"/>
+      <c r="F141" s="15"/>
+      <c r="G141" s="44"/>
+      <c r="H141" s="16"/>
     </row>
     <row r="142" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B142" s="14"/>
-      <c r="C142" s="16" t="str">
+      <c r="B142" s="13"/>
+      <c r="C142" s="15" t="str">
         <f>IF(ISBLANK(B142),"",TEXT(B142, "dddd"))</f>
         <v/>
       </c>
-      <c r="D142" s="69"/>
-      <c r="E142" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="F142" s="74"/>
-      <c r="G142" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H142" s="21"/>
+      <c r="D142" s="52"/>
+      <c r="E142" s="85"/>
+      <c r="F142" s="15"/>
+      <c r="G142" s="44"/>
+      <c r="H142" s="16"/>
     </row>
     <row r="143" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B143" s="14"/>
-      <c r="C143" s="16" t="str">
+      <c r="B143" s="13"/>
+      <c r="C143" s="15" t="str">
         <f>IF(ISBLANK(B143),"",TEXT(B143, "dddd"))</f>
         <v/>
       </c>
-      <c r="D143" s="69"/>
-      <c r="E143" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F143" s="74"/>
-      <c r="G143" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H143" s="21"/>
+      <c r="D143" s="52"/>
+      <c r="E143" s="85"/>
+      <c r="F143" s="15"/>
+      <c r="G143" s="44"/>
+      <c r="H143" s="16"/>
     </row>
     <row r="144" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B144" s="14"/>
-      <c r="C144" s="16" t="str">
+      <c r="B144" s="13"/>
+      <c r="C144" s="15" t="str">
         <f>IF(ISBLANK(B144),"",TEXT(B144, "dddd"))</f>
         <v/>
       </c>
-      <c r="D144" s="69"/>
-      <c r="E144" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="F144" s="74"/>
-      <c r="G144" s="58" t="s">
-        <v>247</v>
-      </c>
-      <c r="H144" s="21"/>
+      <c r="D144" s="52"/>
+      <c r="E144" s="85"/>
+      <c r="F144" s="15"/>
+      <c r="G144" s="44"/>
+      <c r="H144" s="16"/>
     </row>
     <row r="145" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B145" s="14"/>
-      <c r="C145" s="16" t="str">
+      <c r="B145" s="13"/>
+      <c r="C145" s="15" t="str">
         <f>IF(ISBLANK(B145),"",TEXT(B145, "dddd"))</f>
         <v/>
       </c>
-      <c r="D145" s="69"/>
-      <c r="E145" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="F145" s="74"/>
-      <c r="G145" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H145" s="30"/>
+      <c r="D145" s="52"/>
+      <c r="E145" s="85"/>
+      <c r="F145" s="15"/>
+      <c r="G145" s="44"/>
+      <c r="H145" s="16"/>
     </row>
     <row r="146" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B146" s="14"/>
-      <c r="C146" s="16" t="str">
+      <c r="B146" s="13"/>
+      <c r="C146" s="15" t="str">
         <f>IF(ISBLANK(B146),"",TEXT(B146, "dddd"))</f>
         <v/>
       </c>
-      <c r="D146" s="69"/>
-      <c r="E146" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="F146" s="74"/>
-      <c r="G146" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H146" s="30"/>
+      <c r="D146" s="52"/>
+      <c r="E146" s="85"/>
+      <c r="F146" s="15"/>
+      <c r="G146" s="44"/>
+      <c r="H146" s="16"/>
     </row>
     <row r="147" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B147" s="14"/>
-      <c r="C147" s="16" t="str">
+      <c r="B147" s="13"/>
+      <c r="C147" s="15" t="str">
         <f>IF(ISBLANK(B147),"",TEXT(B147, "dddd"))</f>
         <v/>
       </c>
-      <c r="D147" s="69"/>
-      <c r="E147" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="F147" s="74"/>
-      <c r="G147" s="58"/>
-      <c r="H147" s="21"/>
+      <c r="D147" s="52"/>
+      <c r="E147" s="85"/>
+      <c r="F147" s="15"/>
+      <c r="G147" s="44"/>
+      <c r="H147" s="16"/>
     </row>
     <row r="148" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B148" s="14"/>
-      <c r="C148" s="16" t="str">
+      <c r="B148" s="13"/>
+      <c r="C148" s="15" t="str">
         <f>IF(ISBLANK(B148),"",TEXT(B148, "dddd"))</f>
         <v/>
       </c>
-      <c r="D148" s="69"/>
-      <c r="E148" s="16"/>
-      <c r="F148" s="74"/>
-      <c r="G148" s="58"/>
-      <c r="H148" s="21"/>
+      <c r="D148" s="52"/>
+      <c r="E148" s="85"/>
+      <c r="F148" s="15"/>
+      <c r="G148" s="44"/>
+      <c r="H148" s="16"/>
     </row>
     <row r="149" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B149" s="14"/>
-      <c r="C149" s="16" t="str">
+      <c r="B149" s="13"/>
+      <c r="C149" s="15" t="str">
         <f>IF(ISBLANK(B149),"",TEXT(B149, "dddd"))</f>
         <v/>
       </c>
-      <c r="D149" s="69"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="74"/>
-      <c r="G149" s="58"/>
-      <c r="H149" s="21"/>
+      <c r="D149" s="52"/>
+      <c r="E149" s="85"/>
+      <c r="F149" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="G149" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="H149" s="16"/>
     </row>
     <row r="150" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B150" s="14"/>
-      <c r="C150" s="16" t="str">
+      <c r="B150" s="13"/>
+      <c r="C150" s="15" t="str">
         <f>IF(ISBLANK(B150),"",TEXT(B150, "dddd"))</f>
         <v/>
       </c>
-      <c r="D150" s="69"/>
-      <c r="E150" s="65"/>
-      <c r="F150" s="76"/>
-      <c r="G150" s="58"/>
-      <c r="H150" s="21"/>
+      <c r="D150" s="52"/>
+      <c r="E150" s="85"/>
+      <c r="F150" s="15"/>
+      <c r="G150" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="H150" s="16"/>
     </row>
     <row r="151" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B151" s="14"/>
-      <c r="C151" s="16" t="str">
+      <c r="B151" s="13"/>
+      <c r="C151" s="15" t="str">
         <f>IF(ISBLANK(B151),"",TEXT(B151, "dddd"))</f>
         <v/>
       </c>
-      <c r="D151" s="69"/>
-      <c r="E151" s="16"/>
-      <c r="F151" s="74"/>
-      <c r="G151" s="58"/>
-      <c r="H151" s="21"/>
+      <c r="D151" s="52"/>
+      <c r="E151" s="85"/>
+      <c r="F151" s="15"/>
+      <c r="G151" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="H151" s="16"/>
     </row>
     <row r="152" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B152" s="14"/>
-      <c r="C152" s="16" t="str">
+      <c r="B152" s="13"/>
+      <c r="C152" s="15" t="str">
         <f>IF(ISBLANK(B152),"",TEXT(B152, "dddd"))</f>
         <v/>
       </c>
-      <c r="D152" s="69"/>
-      <c r="E152" s="16"/>
-      <c r="F152" s="74"/>
-      <c r="G152" s="58"/>
-      <c r="H152" s="21"/>
+      <c r="D152" s="52"/>
+      <c r="E152" s="85"/>
+      <c r="F152" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G152" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="H152" s="16"/>
     </row>
     <row r="153" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B153" s="14"/>
-      <c r="C153" s="16" t="str">
+      <c r="B153" s="13"/>
+      <c r="C153" s="15" t="str">
         <f>IF(ISBLANK(B153),"",TEXT(B153, "dddd"))</f>
         <v/>
       </c>
-      <c r="D153" s="69"/>
-      <c r="E153" s="12"/>
-      <c r="F153" s="75"/>
-      <c r="G153" s="58"/>
-      <c r="H153" s="21"/>
+      <c r="D153" s="52"/>
+      <c r="E153" s="85"/>
+      <c r="F153" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="G153" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H153" s="16"/>
     </row>
     <row r="154" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B154" s="14"/>
-      <c r="C154" s="16" t="str">
+      <c r="B154" s="13"/>
+      <c r="C154" s="15" t="str">
         <f>IF(ISBLANK(B154),"",TEXT(B154, "dddd"))</f>
         <v/>
       </c>
-      <c r="D154" s="69"/>
-      <c r="E154" s="16"/>
-      <c r="F154" s="74"/>
-      <c r="G154" s="58"/>
-      <c r="H154" s="21"/>
+      <c r="D154" s="52"/>
+      <c r="E154" s="85"/>
+      <c r="F154" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="G154" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H154" s="16"/>
     </row>
     <row r="155" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B155" s="14"/>
-      <c r="C155" s="16" t="str">
+      <c r="B155" s="13"/>
+      <c r="C155" s="15" t="str">
         <f>IF(ISBLANK(B155),"",TEXT(B155, "dddd"))</f>
         <v/>
       </c>
-      <c r="D155" s="69"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="74"/>
-      <c r="G155" s="58"/>
-      <c r="H155" s="30"/>
+      <c r="D155" s="52"/>
+      <c r="E155" s="85"/>
+      <c r="F155" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="G155" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="H155" s="16"/>
     </row>
     <row r="156" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B156" s="14"/>
-      <c r="C156" s="16" t="str">
+      <c r="B156" s="13"/>
+      <c r="C156" s="15" t="str">
         <f>IF(ISBLANK(B156),"",TEXT(B156, "dddd"))</f>
         <v/>
       </c>
-      <c r="D156" s="69"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="74"/>
-      <c r="G156" s="58"/>
-      <c r="H156" s="30"/>
-    </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B157" s="14"/>
-      <c r="C157" s="16"/>
-      <c r="D157" s="69"/>
-      <c r="E157" s="16"/>
-      <c r="F157" s="74"/>
-      <c r="G157" s="58"/>
-      <c r="H157" s="30"/>
+      <c r="D156" s="52"/>
+      <c r="E156" s="44"/>
+      <c r="F156" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="G156" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H156" s="17"/>
+    </row>
+    <row r="157" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B157" s="13"/>
+      <c r="C157" s="15" t="str">
+        <f>IF(ISBLANK(B157),"",TEXT(B157, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D157" s="52"/>
+      <c r="E157" s="44"/>
+      <c r="F157" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="G157" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H157" s="17"/>
     </row>
     <row r="158" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B158" s="14"/>
-      <c r="C158" s="16" t="str">
+      <c r="B158" s="13"/>
+      <c r="C158" s="15" t="str">
         <f>IF(ISBLANK(B158),"",TEXT(B158, "dddd"))</f>
         <v/>
       </c>
-      <c r="D158" s="69"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="74"/>
-      <c r="G158" s="58"/>
-      <c r="H158" s="30"/>
+      <c r="D158" s="52"/>
+      <c r="E158" s="85"/>
+      <c r="F158" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="G158" s="44"/>
+      <c r="H158" s="16"/>
     </row>
     <row r="159" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B159" s="14"/>
-      <c r="C159" s="16" t="str">
+      <c r="B159" s="13"/>
+      <c r="C159" s="15" t="str">
         <f>IF(ISBLANK(B159),"",TEXT(B159, "dddd"))</f>
         <v/>
       </c>
-      <c r="D159" s="69"/>
-      <c r="E159" s="16"/>
-      <c r="F159" s="74"/>
-      <c r="G159" s="58"/>
-      <c r="H159" s="30"/>
+      <c r="D159" s="52"/>
+      <c r="E159" s="85"/>
+      <c r="F159" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="G159" s="44"/>
+      <c r="H159" s="16"/>
     </row>
     <row r="160" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B160" s="14"/>
-      <c r="C160" s="16" t="str">
+      <c r="B160" s="13"/>
+      <c r="C160" s="15" t="str">
         <f>IF(ISBLANK(B160),"",TEXT(B160, "dddd"))</f>
         <v/>
       </c>
-      <c r="D160" s="69"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="74"/>
-      <c r="G160" s="58"/>
-      <c r="H160" s="30"/>
-    </row>
-    <row r="161" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="66"/>
-      <c r="C161" s="31"/>
-      <c r="D161" s="70"/>
-      <c r="E161" s="31"/>
-      <c r="F161" s="77"/>
-      <c r="G161" s="61"/>
-      <c r="H161" s="32"/>
+      <c r="D160" s="52"/>
+      <c r="E160" s="85"/>
+      <c r="F160" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="G160" s="44"/>
+      <c r="H160" s="16"/>
+    </row>
+    <row r="161" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B161" s="13"/>
+      <c r="C161" s="15" t="str">
+        <f>IF(ISBLANK(B161),"",TEXT(B161, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D161" s="52"/>
+      <c r="E161" s="85"/>
+      <c r="F161" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="G161" s="44"/>
+      <c r="H161" s="16"/>
+    </row>
+    <row r="162" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B162" s="13"/>
+      <c r="C162" s="15" t="str">
+        <f>IF(ISBLANK(B162),"",TEXT(B162, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D162" s="52"/>
+      <c r="E162" s="85"/>
+      <c r="F162" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="G162" s="44"/>
+      <c r="H162" s="16"/>
+    </row>
+    <row r="163" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B163" s="13"/>
+      <c r="C163" s="15" t="str">
+        <f>IF(ISBLANK(B163),"",TEXT(B163, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D163" s="52"/>
+      <c r="E163" s="85"/>
+      <c r="F163" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="G163" s="44"/>
+      <c r="H163" s="16"/>
+    </row>
+    <row r="164" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B164" s="13"/>
+      <c r="C164" s="15" t="str">
+        <f>IF(ISBLANK(B164),"",TEXT(B164, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D164" s="52"/>
+      <c r="E164" s="85"/>
+      <c r="F164" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G164" s="44"/>
+      <c r="H164" s="16"/>
+    </row>
+    <row r="165" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B165" s="13"/>
+      <c r="C165" s="15" t="str">
+        <f>IF(ISBLANK(B165),"",TEXT(B165, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D165" s="52"/>
+      <c r="E165" s="85"/>
+      <c r="F165" s="15"/>
+      <c r="G165" s="44"/>
+      <c r="H165" s="16"/>
+    </row>
+    <row r="166" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B166" s="13"/>
+      <c r="C166" s="15" t="str">
+        <f>IF(ISBLANK(B166),"",TEXT(B166, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D166" s="52"/>
+      <c r="E166" s="44"/>
+      <c r="F166" s="15"/>
+      <c r="G166" s="44"/>
+      <c r="H166" s="17"/>
+    </row>
+    <row r="167" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B167" s="13"/>
+      <c r="C167" s="15" t="str">
+        <f>IF(ISBLANK(B167),"",TEXT(B167, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D167" s="52"/>
+      <c r="E167" s="44"/>
+      <c r="F167" s="15"/>
+      <c r="G167" s="44"/>
+      <c r="H167" s="17"/>
+    </row>
+    <row r="168" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B168" s="13"/>
+      <c r="C168" s="15"/>
+      <c r="D168" s="52"/>
+      <c r="E168" s="44"/>
+      <c r="F168" s="15"/>
+      <c r="G168" s="44"/>
+      <c r="H168" s="17"/>
+    </row>
+    <row r="169" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B169" s="13"/>
+      <c r="C169" s="15" t="str">
+        <f>IF(ISBLANK(B169),"",TEXT(B169, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D169" s="52"/>
+      <c r="E169" s="44"/>
+      <c r="F169" s="15"/>
+      <c r="G169" s="44"/>
+      <c r="H169" s="17"/>
+    </row>
+    <row r="170" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B170" s="13"/>
+      <c r="C170" s="15" t="str">
+        <f>IF(ISBLANK(B170),"",TEXT(B170, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D170" s="52"/>
+      <c r="E170" s="44"/>
+      <c r="F170" s="15"/>
+      <c r="G170" s="44"/>
+      <c r="H170" s="17"/>
+    </row>
+    <row r="171" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B171" s="13"/>
+      <c r="C171" s="15" t="str">
+        <f>IF(ISBLANK(B171),"",TEXT(B171, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D171" s="52"/>
+      <c r="E171" s="44"/>
+      <c r="F171" s="15"/>
+      <c r="G171" s="44"/>
+      <c r="H171" s="17"/>
+    </row>
+    <row r="172" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="49"/>
+      <c r="C172" s="18"/>
+      <c r="D172" s="53"/>
+      <c r="E172" s="45"/>
+      <c r="F172" s="18"/>
+      <c r="G172" s="45"/>
+      <c r="H172" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H160" xr:uid="{40A518F1-E8D1-4EDA-B8FC-EAEFD9F39116}">
-    <filterColumn colId="0">
-      <filters blank="1">
-        <dateGroupItem year="2025" month="12" day="8" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="12" day="9" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="12" day="10" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="12" day="11" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="12" day="12" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="12" day="15" dateTimeGrouping="day"/>
-        <dateGroupItem year="2025" month="12" day="16" dateTimeGrouping="day"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B33:H160">
-      <sortCondition ref="B2:B160"/>
-    </sortState>
-  </autoFilter>
-  <conditionalFormatting sqref="B2:H446">
-    <cfRule type="expression" dxfId="11" priority="1">
+  <autoFilter ref="B2:H172" xr:uid="{40A518F1-E8D1-4EDA-B8FC-EAEFD9F39116}"/>
+  <conditionalFormatting sqref="B2:H457">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>$C2=Saturday</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>$C2="Monday"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>$C2="Tuesday"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$C2="Wednesday"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>$C2="Thursday"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>$C2="Friday"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33:H161" xr:uid="{E9D8798E-C0C3-A54B-821A-835C9C1B93C1}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E33:E172 H33:H172" xr:uid="{F96E5036-0CE7-4348-B733-74DDF2C8E069}">
       <formula1>45658</formula1>
       <formula2>46388</formula2>
     </dataValidation>
@@ -5239,7 +5635,57 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17702B44-67CA-224A-8B7B-AFB2F9E126A1}">
+  <dimension ref="B6:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CF99CA-4416-4E89-816C-1EB7F12FACC6}">
   <dimension ref="B1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5258,21 +5704,21 @@
   <sheetData>
     <row r="1" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:14" ht="30" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="64"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="48"/>
     </row>
     <row r="3" spans="2:14" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
@@ -5316,667 +5762,667 @@
       </c>
     </row>
     <row r="4" spans="2:14" ht="32" x14ac:dyDescent="0.2">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="45">
+      <c r="G4" s="32">
         <v>45610</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44" t="s">
+      <c r="J4" s="31"/>
+      <c r="K4" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="44" t="s">
+      <c r="L4" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="49" t="s">
+      <c r="M4" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="46"/>
+      <c r="N4" s="33"/>
     </row>
     <row r="5" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="24">
         <v>45966</v>
       </c>
-      <c r="H5" s="48">
+      <c r="H5" s="35">
         <v>9492307588</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36" t="s">
+      <c r="J5" s="23"/>
+      <c r="K5" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="36" t="s">
+      <c r="L5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="38"/>
+      <c r="N5" s="25"/>
     </row>
     <row r="6" spans="2:14" ht="32" x14ac:dyDescent="0.2">
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="24">
         <v>45975</v>
       </c>
-      <c r="H6" s="48">
+      <c r="H6" s="35">
         <v>5622575100</v>
       </c>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36" t="s">
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="38"/>
+      <c r="N6" s="25"/>
     </row>
     <row r="7" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="24">
         <v>45973</v>
       </c>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36" t="s">
+      <c r="J7" s="23"/>
+      <c r="K7" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="L7" s="36" t="s">
+      <c r="L7" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="N7" s="38"/>
+      <c r="N7" s="25"/>
     </row>
     <row r="8" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="24">
         <v>45973</v>
       </c>
-      <c r="H8" s="48" t="s">
+      <c r="H8" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="36" t="s">
+      <c r="I8" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36" t="s">
+      <c r="J8" s="23"/>
+      <c r="K8" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="36" t="s">
+      <c r="L8" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="38"/>
+      <c r="N8" s="25"/>
     </row>
     <row r="9" spans="2:14" ht="160" x14ac:dyDescent="0.2">
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="24">
         <v>45992</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="I9" s="36" t="s">
+      <c r="I9" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="K9" s="36" t="s">
+      <c r="K9" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="L9" s="36" t="s">
+      <c r="L9" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="N9" s="38"/>
+      <c r="N9" s="25"/>
     </row>
     <row r="10" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="24">
         <v>45968</v>
       </c>
-      <c r="H10" s="48" t="s">
+      <c r="H10" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="36" t="s">
+      <c r="I10" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36" t="s">
+      <c r="J10" s="23"/>
+      <c r="K10" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="36" t="s">
+      <c r="L10" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="N10" s="38"/>
+      <c r="N10" s="25"/>
     </row>
     <row r="11" spans="2:14" ht="80" x14ac:dyDescent="0.2">
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36" t="s">
+      <c r="C11" s="23"/>
+      <c r="D11" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="24">
         <v>45967</v>
       </c>
-      <c r="H11" s="48">
+      <c r="H11" s="35">
         <v>7075445575</v>
       </c>
-      <c r="I11" s="36" t="s">
+      <c r="I11" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36" t="s">
+      <c r="J11" s="23"/>
+      <c r="K11" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="36" t="s">
+      <c r="L11" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="N11" s="38"/>
+      <c r="N11" s="25"/>
     </row>
     <row r="12" spans="2:14" ht="32" x14ac:dyDescent="0.2">
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36" t="s">
+      <c r="C12" s="23"/>
+      <c r="D12" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="24">
         <v>45967</v>
       </c>
-      <c r="H12" s="48">
+      <c r="H12" s="35">
         <v>5629978800</v>
       </c>
-      <c r="I12" s="36" t="s">
+      <c r="I12" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36" t="s">
+      <c r="J12" s="23"/>
+      <c r="K12" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="36" t="s">
+      <c r="L12" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="N12" s="38"/>
+      <c r="N12" s="25"/>
     </row>
     <row r="13" spans="2:14" ht="32" x14ac:dyDescent="0.2">
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36" t="s">
+      <c r="C13" s="23"/>
+      <c r="D13" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="36" t="s">
+      <c r="E13" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="37">
+      <c r="F13" s="23"/>
+      <c r="G13" s="24">
         <v>45975</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="23">
         <v>9294137405</v>
       </c>
-      <c r="I13" s="50" t="s">
+      <c r="I13" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36" t="s">
+      <c r="J13" s="23"/>
+      <c r="K13" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="L13" s="36" t="s">
+      <c r="L13" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="M13" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="N13" s="38"/>
+      <c r="M13" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="N13" s="25"/>
     </row>
     <row r="14" spans="2:14" ht="32" x14ac:dyDescent="0.2">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="24">
         <v>45992</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36" t="s">
+      <c r="H14" s="23"/>
+      <c r="I14" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="J14" s="36" t="s">
+      <c r="J14" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="K14" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="L14" s="36" t="s">
+      <c r="L14" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="N14" s="38"/>
+      <c r="N14" s="25"/>
     </row>
     <row r="15" spans="2:14" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36" t="s">
+      <c r="C15" s="23"/>
+      <c r="D15" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="24">
         <v>45993</v>
       </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36" t="s">
+      <c r="H15" s="23"/>
+      <c r="I15" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="L15" s="36" t="s">
+      <c r="L15" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="N15" s="38"/>
+      <c r="M15" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="N15" s="25"/>
     </row>
     <row r="16" spans="2:14" ht="48" x14ac:dyDescent="0.2">
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36" t="s">
+      <c r="C16" s="23"/>
+      <c r="D16" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36" t="s">
+      <c r="E16" s="23"/>
+      <c r="F16" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="24">
         <v>45992</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="J16" s="36" t="s">
+      <c r="J16" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="K16" s="36" t="s">
+      <c r="K16" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="L16" s="36" t="s">
+      <c r="L16" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="N16" s="38"/>
+      <c r="N16" s="25"/>
     </row>
     <row r="17" spans="2:14" ht="80" x14ac:dyDescent="0.2">
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36" t="s">
+      <c r="C17" s="23"/>
+      <c r="D17" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="24">
         <v>45966</v>
       </c>
-      <c r="H17" s="48">
+      <c r="H17" s="35">
         <v>3238521900</v>
       </c>
-      <c r="I17" s="36" t="s">
+      <c r="I17" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36" t="s">
+      <c r="J17" s="23"/>
+      <c r="K17" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="L17" s="36" t="s">
+      <c r="L17" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="N17" s="39">
+      <c r="N17" s="26">
         <v>45789</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="38"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="25"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="38"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="25"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="35"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="38"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="25"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="38"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="25"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="38"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="25"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B23" s="35"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="38"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="25"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B24" s="35"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="36"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="38"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="25"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B25" s="35"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="38"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="25"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B26" s="35"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="38"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="25"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="35"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="38"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="25"/>
     </row>
     <row r="28" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="42"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:N28" xr:uid="{80CF99CA-4416-4E89-816C-1EB7F12FACC6}">
@@ -5988,25 +6434,25 @@
     <mergeCell ref="B2:N2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:N28">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>LEFT($B4,1)="7"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>LEFT($B4,1)="1"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>LEFT($B4,1)="2"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>LEFT($B4,1)="3"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="5">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>LEFT($B4,1)="4"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="6">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>LEFT($B4,1)="5"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="7">
+    <cfRule type="expression" dxfId="0" priority="7">
       <formula>LEFT($B4,1)="6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6030,93 +6476,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFAB370-5E5C-46A0-8279-06017109B5E9}">
-  <dimension ref="B2:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E04BDE-9139-43BE-8886-A956CCD7558E}">
   <dimension ref="B2:B9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="21" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="21" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="21" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="21" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="21" t="s">
         <v>108</v>
       </c>
     </row>

--- a/ToDo.xlsx
+++ b/ToDo.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleckleinman/Documents/TheGrantScout/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4764223A-D0A9-234C-A808-D89EE6397066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA2FAE4-9A7F-C94B-934B-E3F963016C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19280" yWindow="500" windowWidth="18960" windowHeight="19200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19280" yWindow="500" windowWidth="18960" windowHeight="19200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
     <sheet name="To Do" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
-    <sheet name="Beta Leads" sheetId="7" state="hidden" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="8" state="hidden" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="11" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId4"/>
+    <sheet name="Beta Leads" sheetId="7" state="hidden" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="8" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Beta Leads'!$B$3:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beta Leads'!$B$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Do'!$B$2:$H$172</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="290">
   <si>
     <t>Task</t>
   </si>
@@ -900,6 +901,36 @@
   </si>
   <si>
     <t>FC</t>
+  </si>
+  <si>
+    <t>Linkedin Connection Requests</t>
+  </si>
+  <si>
+    <t>Accepted Requests</t>
+  </si>
+  <si>
+    <t>Messaged</t>
+  </si>
+  <si>
+    <t>Sent List</t>
+  </si>
+  <si>
+    <t>Scheduled Meeting</t>
+  </si>
+  <si>
+    <t>Called</t>
+  </si>
+  <si>
+    <t>VM</t>
+  </si>
+  <si>
+    <t>Calls Returned</t>
+  </si>
+  <si>
+    <t>Sent Email</t>
+  </si>
+  <si>
+    <t>Meeting Scheduled</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1360,30 +1391,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1398,25 +1407,22 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1440,6 +1446,18 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1834,10 +1852,10 @@
   <sheetData>
     <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="57" t="s">
         <v>255</v>
       </c>
     </row>
@@ -1845,229 +1863,229 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="54" t="s">
         <v>250</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="55">
         <v>46041</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="50" t="s">
         <v>251</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="51">
         <v>46041</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="50" t="s">
         <v>252</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="51">
         <v>46041</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="50" t="s">
         <v>253</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="51">
         <v>46041</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="51">
         <v>46041</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="53">
         <v>46041</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
     </row>
     <row r="11" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:5" ht="30" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="66"/>
-      <c r="D12" s="67" t="s">
+      <c r="C12" s="58"/>
+      <c r="D12" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="60" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="54" t="s">
         <v>250</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="61" t="s">
         <v>269</v>
       </c>
-      <c r="E13" s="73">
+      <c r="E13" s="63">
         <v>46042</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="D14" s="64" t="s">
+      <c r="D14" s="56" t="s">
         <v>270</v>
       </c>
-      <c r="E14" s="71">
+      <c r="E14" s="51">
         <v>46042</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="D15" s="64" t="s">
+      <c r="D15" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="51">
         <v>46043</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="64" t="s">
+      <c r="D16" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="E16" s="71">
+      <c r="E16" s="51">
         <v>46043</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="64" t="s">
+      <c r="D17" s="56" t="s">
         <v>260</v>
       </c>
-      <c r="E17" s="71">
+      <c r="E17" s="51">
         <v>46042</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="D18" s="64" t="s">
+      <c r="D18" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="E18" s="71">
+      <c r="E18" s="51">
         <v>46043</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="D19" s="64" t="s">
+      <c r="D19" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="E19" s="74">
+      <c r="E19" s="64">
         <v>46043</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="D20" s="64" t="s">
+      <c r="D20" s="56" t="s">
         <v>263</v>
       </c>
-      <c r="E20" s="71">
+      <c r="E20" s="51">
         <v>46044</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="D21" s="64" t="s">
+      <c r="D21" s="56" t="s">
         <v>264</v>
       </c>
-      <c r="E21" s="71">
+      <c r="E21" s="51">
         <v>46045</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="D22" s="64" t="s">
+      <c r="D22" s="56" t="s">
         <v>265</v>
       </c>
-      <c r="E22" s="71">
+      <c r="E22" s="51">
         <v>46045</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="D23" s="64" t="s">
+      <c r="D23" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="E23" s="71">
+      <c r="E23" s="51">
         <v>46042</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="50" t="s">
         <v>253</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="E24" s="71">
+      <c r="E24" s="51">
         <v>46042</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="50" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="56" t="s">
         <v>268</v>
       </c>
-      <c r="E25" s="71">
+      <c r="E25" s="51">
         <v>46043</v>
       </c>
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="50" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="D26" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="E26" s="71">
+      <c r="E26" s="51">
         <v>46044</v>
       </c>
     </row>
     <row r="27" spans="3:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="60" t="s">
+      <c r="C27" s="52" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="70" t="s">
+      <c r="D27" s="62" t="s">
         <v>268</v>
       </c>
-      <c r="E27" s="72">
+      <c r="E27" s="53">
         <v>46045</v>
       </c>
     </row>
@@ -2081,10 +2099,10 @@
   <dimension ref="B1:S172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="23.5" style="76" customWidth="1"/>
+    <col min="2" max="2" width="23.5" style="66" customWidth="1"/>
     <col min="3" max="3" width="23.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="54" customWidth="1"/>
-    <col min="5" max="5" width="34.1640625" style="77" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="34.1640625" customWidth="1"/>
     <col min="6" max="6" width="49.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.83203125" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="16.1640625" style="2" customWidth="1"/>
@@ -2093,20 +2111,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="56"/>
+      <c r="B1" s="48"/>
       <c r="C1"/>
-      <c r="D1" s="50"/>
+      <c r="D1"/>
       <c r="F1"/>
       <c r="H1"/>
     </row>
     <row r="2" spans="2:19" s="2" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="65" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="43" t="s">
@@ -2132,24 +2150,24 @@
       <c r="S2" s="1"/>
     </row>
     <row r="3" spans="2:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="B3" s="79">
+      <c r="B3" s="68">
         <v>45992</v>
       </c>
-      <c r="C3" s="80" t="str">
-        <f>TEXT(B3, "dddd")</f>
+      <c r="C3" s="69" t="str">
+        <f t="shared" ref="C3:C11" si="0">TEXT(B3, "dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="D3" s="81">
+      <c r="D3" s="70">
         <v>1</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="81" t="s">
+      <c r="E3" s="71"/>
+      <c r="F3" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="83" t="s">
+      <c r="G3" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="84">
+      <c r="H3" s="73">
         <v>45992</v>
       </c>
       <c r="I3" s="3"/>
@@ -2169,13 +2187,13 @@
         <v>45992</v>
       </c>
       <c r="C4" s="14" t="str">
-        <f>TEXT(B4, "dddd")</f>
+        <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
       <c r="D4" s="15">
         <v>1</v>
       </c>
-      <c r="E4" s="85"/>
+      <c r="E4" s="74"/>
       <c r="F4" s="15" t="s">
         <v>4</v>
       </c>
@@ -2202,13 +2220,13 @@
         <v>45992</v>
       </c>
       <c r="C5" s="14" t="str">
-        <f>TEXT(B5, "dddd")</f>
+        <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="85"/>
+      <c r="E5" s="74"/>
       <c r="F5" s="15" t="s">
         <v>10</v>
       </c>
@@ -2235,13 +2253,13 @@
         <v>45992</v>
       </c>
       <c r="C6" s="14" t="str">
-        <f>TEXT(B6, "dddd")</f>
+        <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
       <c r="D6" s="15">
         <v>2</v>
       </c>
-      <c r="E6" s="85"/>
+      <c r="E6" s="74"/>
       <c r="F6" s="15" t="s">
         <v>17</v>
       </c>
@@ -2268,13 +2286,13 @@
         <v>45992</v>
       </c>
       <c r="C7" s="14" t="str">
-        <f>TEXT(B7, "dddd")</f>
+        <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
       <c r="D7" s="15">
         <v>3</v>
       </c>
-      <c r="E7" s="85"/>
+      <c r="E7" s="74"/>
       <c r="F7" s="15" t="s">
         <v>9</v>
       </c>
@@ -2301,13 +2319,13 @@
         <v>45992</v>
       </c>
       <c r="C8" s="14" t="str">
-        <f>TEXT(B8, "dddd")</f>
+        <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
       <c r="D8" s="15">
         <v>4</v>
       </c>
-      <c r="E8" s="85"/>
+      <c r="E8" s="74"/>
       <c r="F8" s="15" t="s">
         <v>7</v>
       </c>
@@ -2334,13 +2352,13 @@
         <v>45992</v>
       </c>
       <c r="C9" s="14" t="str">
-        <f>TEXT(B9, "dddd")</f>
+        <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
       <c r="D9" s="15">
         <v>5</v>
       </c>
-      <c r="E9" s="85"/>
+      <c r="E9" s="74"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
@@ -2367,13 +2385,13 @@
         <v>45992</v>
       </c>
       <c r="C10" s="14" t="str">
-        <f>TEXT(B10, "dddd")</f>
+        <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
       <c r="D10" s="15">
         <v>5</v>
       </c>
-      <c r="E10" s="85"/>
+      <c r="E10" s="74"/>
       <c r="F10" s="15" t="s">
         <v>6</v>
       </c>
@@ -2400,13 +2418,13 @@
         <v>45992</v>
       </c>
       <c r="C11" s="14" t="str">
-        <f>TEXT(B11, "dddd")</f>
+        <f t="shared" si="0"/>
         <v>Monday</v>
       </c>
       <c r="D11" s="15">
         <v>6</v>
       </c>
-      <c r="E11" s="85"/>
+      <c r="E11" s="74"/>
       <c r="F11" s="15" t="s">
         <v>23</v>
       </c>
@@ -2433,13 +2451,13 @@
         <v>45992</v>
       </c>
       <c r="C12" s="15" t="str">
-        <f>IF(ISBLANK(B12),"",TEXT(B12, "dddd"))</f>
+        <f t="shared" ref="C12:C43" si="1">IF(ISBLANK(B12),"",TEXT(B12, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D12" s="15">
         <v>6</v>
       </c>
-      <c r="E12" s="85"/>
+      <c r="E12" s="74"/>
       <c r="F12" s="15" t="s">
         <v>11</v>
       </c>
@@ -2466,13 +2484,13 @@
         <v>45994</v>
       </c>
       <c r="C13" s="15" t="str">
-        <f>IF(ISBLANK(B13),"",TEXT(B13, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
       <c r="D13" s="15">
         <v>1</v>
       </c>
-      <c r="E13" s="85"/>
+      <c r="E13" s="74"/>
       <c r="F13" s="15" t="s">
         <v>19</v>
       </c>
@@ -2499,13 +2517,13 @@
         <v>45994</v>
       </c>
       <c r="C14" s="15" t="str">
-        <f>IF(ISBLANK(B14),"",TEXT(B14, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
       <c r="D14" s="15">
         <v>1.5</v>
       </c>
-      <c r="E14" s="85"/>
+      <c r="E14" s="74"/>
       <c r="F14" s="15" t="s">
         <v>25</v>
       </c>
@@ -2532,13 +2550,13 @@
         <v>45994</v>
       </c>
       <c r="C15" s="15" t="str">
-        <f>IF(ISBLANK(B15),"",TEXT(B15, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
       <c r="D15" s="38">
         <v>2</v>
       </c>
-      <c r="E15" s="86"/>
+      <c r="E15" s="75"/>
       <c r="F15" s="38" t="s">
         <v>26</v>
       </c>
@@ -2565,13 +2583,13 @@
         <v>45994</v>
       </c>
       <c r="C16" s="15" t="str">
-        <f>IF(ISBLANK(B16),"",TEXT(B16, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="E16" s="85"/>
+      <c r="E16" s="74"/>
       <c r="F16" s="15" t="s">
         <v>134</v>
       </c>
@@ -2598,13 +2616,13 @@
         <v>45994</v>
       </c>
       <c r="C17" s="15" t="str">
-        <f>IF(ISBLANK(B17),"",TEXT(B17, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
       <c r="D17" s="15">
         <v>3</v>
       </c>
-      <c r="E17" s="85"/>
+      <c r="E17" s="74"/>
       <c r="F17" s="15" t="s">
         <v>27</v>
       </c>
@@ -2631,13 +2649,13 @@
         <v>45994</v>
       </c>
       <c r="C18" s="15" t="str">
-        <f>IF(ISBLANK(B18),"",TEXT(B18, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="E18" s="85"/>
+      <c r="E18" s="74"/>
       <c r="F18" s="15" t="s">
         <v>29</v>
       </c>
@@ -2664,13 +2682,13 @@
         <v>45994</v>
       </c>
       <c r="C19" s="15" t="str">
-        <f>IF(ISBLANK(B19),"",TEXT(B19, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
       <c r="D19" s="15">
         <v>4</v>
       </c>
-      <c r="E19" s="85"/>
+      <c r="E19" s="74"/>
       <c r="F19" s="15" t="s">
         <v>22</v>
       </c>
@@ -2697,13 +2715,13 @@
         <v>45994</v>
       </c>
       <c r="C20" s="15" t="str">
-        <f>IF(ISBLANK(B20),"",TEXT(B20, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
       <c r="D20" s="15">
         <v>5</v>
       </c>
-      <c r="E20" s="85"/>
+      <c r="E20" s="74"/>
       <c r="F20" s="15" t="s">
         <v>24</v>
       </c>
@@ -2730,13 +2748,13 @@
         <v>45995</v>
       </c>
       <c r="C21" s="15" t="str">
-        <f>IF(ISBLANK(B21),"",TEXT(B21, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Thursday</v>
       </c>
       <c r="D21" s="15">
         <v>1</v>
       </c>
-      <c r="E21" s="85"/>
+      <c r="E21" s="74"/>
       <c r="F21" s="15" t="s">
         <v>21</v>
       </c>
@@ -2763,13 +2781,13 @@
         <v>45995</v>
       </c>
       <c r="C22" s="15" t="str">
-        <f>IF(ISBLANK(B22),"",TEXT(B22, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Thursday</v>
       </c>
       <c r="D22" s="15">
         <v>1.5</v>
       </c>
-      <c r="E22" s="85"/>
+      <c r="E22" s="74"/>
       <c r="F22" s="15" t="s">
         <v>18</v>
       </c>
@@ -2796,13 +2814,13 @@
         <v>45995</v>
       </c>
       <c r="C23" s="15" t="str">
-        <f>IF(ISBLANK(B23),"",TEXT(B23, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Thursday</v>
       </c>
       <c r="D23" s="15">
         <v>2</v>
       </c>
-      <c r="E23" s="85"/>
+      <c r="E23" s="74"/>
       <c r="F23" s="15" t="s">
         <v>135</v>
       </c>
@@ -2829,13 +2847,13 @@
         <v>45995</v>
       </c>
       <c r="C24" s="15" t="str">
-        <f>IF(ISBLANK(B24),"",TEXT(B24, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Thursday</v>
       </c>
       <c r="D24" s="15">
         <v>4</v>
       </c>
-      <c r="E24" s="85"/>
+      <c r="E24" s="74"/>
       <c r="F24" s="15" t="s">
         <v>131</v>
       </c>
@@ -2862,13 +2880,13 @@
         <v>45995</v>
       </c>
       <c r="C25" s="15" t="str">
-        <f>IF(ISBLANK(B25),"",TEXT(B25, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Thursday</v>
       </c>
       <c r="D25" s="15">
         <v>5</v>
       </c>
-      <c r="E25" s="85"/>
+      <c r="E25" s="74"/>
       <c r="F25" s="15" t="s">
         <v>141</v>
       </c>
@@ -2895,13 +2913,13 @@
         <v>45995</v>
       </c>
       <c r="C26" s="15" t="str">
-        <f>IF(ISBLANK(B26),"",TEXT(B26, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Thursday</v>
       </c>
       <c r="D26" s="15">
         <v>6</v>
       </c>
-      <c r="E26" s="85"/>
+      <c r="E26" s="74"/>
       <c r="F26" s="15" t="s">
         <v>28</v>
       </c>
@@ -2928,11 +2946,11 @@
         <v>45995</v>
       </c>
       <c r="C27" s="15" t="str">
-        <f>IF(ISBLANK(B27),"",TEXT(B27, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Thursday</v>
       </c>
       <c r="D27" s="15"/>
-      <c r="E27" s="85"/>
+      <c r="E27" s="74"/>
       <c r="F27" s="15" t="s">
         <v>143</v>
       </c>
@@ -2957,13 +2975,13 @@
         <v>45996</v>
       </c>
       <c r="C28" s="15" t="str">
-        <f>IF(ISBLANK(B28),"",TEXT(B28, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Friday</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="85"/>
+      <c r="E28" s="74"/>
       <c r="F28" s="15" t="s">
         <v>136</v>
       </c>
@@ -2990,13 +3008,13 @@
         <v>45996</v>
       </c>
       <c r="C29" s="15" t="str">
-        <f>IF(ISBLANK(B29),"",TEXT(B29, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Friday</v>
       </c>
       <c r="D29" s="15">
         <v>1</v>
       </c>
-      <c r="E29" s="85"/>
+      <c r="E29" s="74"/>
       <c r="F29" s="15" t="s">
         <v>144</v>
       </c>
@@ -3023,13 +3041,13 @@
         <v>45996</v>
       </c>
       <c r="C30" s="15" t="str">
-        <f>IF(ISBLANK(B30),"",TEXT(B30, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Friday</v>
       </c>
       <c r="D30" s="15">
         <v>1</v>
       </c>
-      <c r="E30" s="85"/>
+      <c r="E30" s="74"/>
       <c r="F30" s="15" t="s">
         <v>132</v>
       </c>
@@ -3056,13 +3074,13 @@
         <v>45996</v>
       </c>
       <c r="C31" s="15" t="str">
-        <f>IF(ISBLANK(B31),"",TEXT(B31, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Friday</v>
       </c>
       <c r="D31" s="15">
         <v>1.5</v>
       </c>
-      <c r="E31" s="85"/>
+      <c r="E31" s="74"/>
       <c r="F31" s="15" t="s">
         <v>145</v>
       </c>
@@ -3089,11 +3107,11 @@
         <v>45996</v>
       </c>
       <c r="C32" s="15" t="str">
-        <f>IF(ISBLANK(B32),"",TEXT(B32, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Friday</v>
       </c>
       <c r="D32" s="15"/>
-      <c r="E32" s="85"/>
+      <c r="E32" s="74"/>
       <c r="F32" s="15" t="s">
         <v>146</v>
       </c>
@@ -3120,10 +3138,10 @@
         <v>45999</v>
       </c>
       <c r="C33" s="15" t="str">
-        <f>IF(ISBLANK(B33),"",TEXT(B33, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Monday</v>
       </c>
-      <c r="D33" s="52">
+      <c r="D33" s="15">
         <v>3</v>
       </c>
       <c r="E33" s="44"/>
@@ -3138,10 +3156,10 @@
         <v>45999</v>
       </c>
       <c r="C34" s="15" t="str">
-        <f>IF(ISBLANK(B34),"",TEXT(B34, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Monday</v>
       </c>
-      <c r="D34" s="52">
+      <c r="D34" s="15">
         <v>3</v>
       </c>
       <c r="E34" s="44"/>
@@ -3156,10 +3174,10 @@
         <v>45999</v>
       </c>
       <c r="C35" s="15" t="str">
-        <f>IF(ISBLANK(B35),"",TEXT(B35, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Monday</v>
       </c>
-      <c r="D35" s="52">
+      <c r="D35" s="15">
         <v>4</v>
       </c>
       <c r="E35" s="44"/>
@@ -3174,10 +3192,10 @@
         <v>45999</v>
       </c>
       <c r="C36" s="15" t="str">
-        <f>IF(ISBLANK(B36),"",TEXT(B36, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Monday</v>
       </c>
-      <c r="D36" s="52">
+      <c r="D36" s="15">
         <v>5</v>
       </c>
       <c r="E36" s="44"/>
@@ -3192,11 +3210,11 @@
         <v>46000</v>
       </c>
       <c r="C37" s="15" t="str">
-        <f>IF(ISBLANK(B37),"",TEXT(B37, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Tuesday</v>
       </c>
-      <c r="D37" s="52"/>
-      <c r="E37" s="85"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="74"/>
       <c r="F37" s="15" t="s">
         <v>147</v>
       </c>
@@ -3212,13 +3230,13 @@
         <v>46001</v>
       </c>
       <c r="C38" s="15" t="str">
-        <f>IF(ISBLANK(B38),"",TEXT(B38, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="15">
         <v>1</v>
       </c>
-      <c r="E38" s="85"/>
+      <c r="E38" s="74"/>
       <c r="F38" s="15" t="s">
         <v>149</v>
       </c>
@@ -3234,13 +3252,13 @@
         <v>46001</v>
       </c>
       <c r="C39" s="15" t="str">
-        <f>IF(ISBLANK(B39),"",TEXT(B39, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
-      <c r="D39" s="52">
+      <c r="D39" s="15">
         <v>2</v>
       </c>
-      <c r="E39" s="85"/>
+      <c r="E39" s="74"/>
       <c r="F39" s="15" t="s">
         <v>151</v>
       </c>
@@ -3256,13 +3274,13 @@
         <v>46001</v>
       </c>
       <c r="C40" s="15" t="str">
-        <f>IF(ISBLANK(B40),"",TEXT(B40, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
-      <c r="D40" s="52">
+      <c r="D40" s="15">
         <v>2.1</v>
       </c>
-      <c r="E40" s="85"/>
+      <c r="E40" s="74"/>
       <c r="F40" s="15" t="s">
         <v>152</v>
       </c>
@@ -3278,13 +3296,13 @@
         <v>46001</v>
       </c>
       <c r="C41" s="15" t="str">
-        <f>IF(ISBLANK(B41),"",TEXT(B41, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
-      <c r="D41" s="52">
+      <c r="D41" s="15">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E41" s="85"/>
+      <c r="E41" s="74"/>
       <c r="F41" s="15" t="s">
         <v>153</v>
       </c>
@@ -3300,13 +3318,13 @@
         <v>46001</v>
       </c>
       <c r="C42" s="15" t="str">
-        <f>IF(ISBLANK(B42),"",TEXT(B42, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="15">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E42" s="85"/>
+      <c r="E42" s="74"/>
       <c r="F42" s="15" t="s">
         <v>154</v>
       </c>
@@ -3322,13 +3340,13 @@
         <v>46001</v>
       </c>
       <c r="C43" s="15" t="str">
-        <f>IF(ISBLANK(B43),"",TEXT(B43, "dddd"))</f>
+        <f t="shared" si="1"/>
         <v>Wednesday</v>
       </c>
-      <c r="D43" s="52">
+      <c r="D43" s="15">
         <v>2.4</v>
       </c>
-      <c r="E43" s="85"/>
+      <c r="E43" s="74"/>
       <c r="F43" s="15" t="s">
         <v>155</v>
       </c>
@@ -3344,13 +3362,13 @@
         <v>46001</v>
       </c>
       <c r="C44" s="15" t="str">
-        <f>IF(ISBLANK(B44),"",TEXT(B44, "dddd"))</f>
+        <f t="shared" ref="C44:C75" si="2">IF(ISBLANK(B44),"",TEXT(B44, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D44" s="52">
+      <c r="D44" s="15">
         <v>2.4500000000000002</v>
       </c>
-      <c r="E44" s="85"/>
+      <c r="E44" s="74"/>
       <c r="F44" s="15" t="s">
         <v>176</v>
       </c>
@@ -3362,13 +3380,13 @@
         <v>46001</v>
       </c>
       <c r="C45" s="15" t="str">
-        <f>IF(ISBLANK(B45),"",TEXT(B45, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D45" s="52">
+      <c r="D45" s="15">
         <v>2.5</v>
       </c>
-      <c r="E45" s="85"/>
+      <c r="E45" s="74"/>
       <c r="F45" s="15" t="s">
         <v>156</v>
       </c>
@@ -3382,10 +3400,10 @@
         <v>46001</v>
       </c>
       <c r="C46" s="15" t="str">
-        <f>IF(ISBLANK(B46),"",TEXT(B46, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D46" s="52">
+      <c r="D46" s="15">
         <v>2.6</v>
       </c>
       <c r="E46" s="44"/>
@@ -3402,13 +3420,13 @@
         <v>46001</v>
       </c>
       <c r="C47" s="15" t="str">
-        <f>IF(ISBLANK(B47),"",TEXT(B47, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D47" s="52">
+      <c r="D47" s="15">
         <v>8</v>
       </c>
-      <c r="E47" s="85"/>
+      <c r="E47" s="74"/>
       <c r="F47" s="15" t="s">
         <v>150</v>
       </c>
@@ -3424,10 +3442,10 @@
         <v>46002</v>
       </c>
       <c r="C48" s="15" t="str">
-        <f>IF(ISBLANK(B48),"",TEXT(B48, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Thursday</v>
       </c>
-      <c r="D48" s="52">
+      <c r="D48" s="15">
         <v>1</v>
       </c>
       <c r="E48" s="44"/>
@@ -3444,13 +3462,13 @@
         <v>46003</v>
       </c>
       <c r="C49" s="15" t="str">
-        <f>IF(ISBLANK(B49),"",TEXT(B49, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Friday</v>
       </c>
-      <c r="D49" s="52">
+      <c r="D49" s="15">
         <v>1</v>
       </c>
-      <c r="E49" s="85"/>
+      <c r="E49" s="74"/>
       <c r="F49" s="15" t="s">
         <v>161</v>
       </c>
@@ -3466,13 +3484,13 @@
         <v>46006</v>
       </c>
       <c r="C50" s="15" t="str">
-        <f>IF(ISBLANK(B50),"",TEXT(B50, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D50" s="52">
+      <c r="D50" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E50" s="85"/>
+      <c r="E50" s="74"/>
       <c r="F50" s="15" t="s">
         <v>158</v>
       </c>
@@ -3488,13 +3506,13 @@
         <v>46006</v>
       </c>
       <c r="C51" s="15" t="str">
-        <f>IF(ISBLANK(B51),"",TEXT(B51, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D51" s="52">
+      <c r="D51" s="15">
         <v>1.2</v>
       </c>
-      <c r="E51" s="85"/>
+      <c r="E51" s="74"/>
       <c r="F51" s="15" t="s">
         <v>159</v>
       </c>
@@ -3510,13 +3528,13 @@
         <v>46006</v>
       </c>
       <c r="C52" s="15" t="str">
-        <f>IF(ISBLANK(B52),"",TEXT(B52, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D52" s="52">
+      <c r="D52" s="15">
         <v>2.1</v>
       </c>
-      <c r="E52" s="85"/>
+      <c r="E52" s="74"/>
       <c r="F52" s="15" t="s">
         <v>162</v>
       </c>
@@ -3532,13 +3550,13 @@
         <v>46006</v>
       </c>
       <c r="C53" s="15" t="str">
-        <f>IF(ISBLANK(B53),"",TEXT(B53, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D53" s="52">
+      <c r="D53" s="15">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E53" s="85"/>
+      <c r="E53" s="74"/>
       <c r="F53" s="15" t="s">
         <v>163</v>
       </c>
@@ -3554,13 +3572,13 @@
         <v>46006</v>
       </c>
       <c r="C54" s="15" t="str">
-        <f>IF(ISBLANK(B54),"",TEXT(B54, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D54" s="52">
+      <c r="D54" s="15">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E54" s="85"/>
+      <c r="E54" s="74"/>
       <c r="F54" s="15" t="s">
         <v>164</v>
       </c>
@@ -3576,13 +3594,13 @@
         <v>46006</v>
       </c>
       <c r="C55" s="15" t="str">
-        <f>IF(ISBLANK(B55),"",TEXT(B55, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D55" s="52">
+      <c r="D55" s="15">
         <v>3.1</v>
       </c>
-      <c r="E55" s="85"/>
+      <c r="E55" s="74"/>
       <c r="F55" s="15" t="s">
         <v>165</v>
       </c>
@@ -3598,13 +3616,13 @@
         <v>46006</v>
       </c>
       <c r="C56" s="15" t="str">
-        <f>IF(ISBLANK(B56),"",TEXT(B56, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D56" s="52">
+      <c r="D56" s="15">
         <v>3.2</v>
       </c>
-      <c r="E56" s="85"/>
+      <c r="E56" s="74"/>
       <c r="F56" s="15" t="s">
         <v>172</v>
       </c>
@@ -3620,13 +3638,13 @@
         <v>46006</v>
       </c>
       <c r="C57" s="15" t="str">
-        <f>IF(ISBLANK(B57),"",TEXT(B57, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D57" s="52">
+      <c r="D57" s="15">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E57" s="85"/>
+      <c r="E57" s="74"/>
       <c r="F57" s="15" t="s">
         <v>167</v>
       </c>
@@ -3642,13 +3660,13 @@
         <v>46006</v>
       </c>
       <c r="C58" s="15" t="str">
-        <f>IF(ISBLANK(B58),"",TEXT(B58, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D58" s="52">
+      <c r="D58" s="15">
         <v>4.2</v>
       </c>
-      <c r="E58" s="85"/>
+      <c r="E58" s="74"/>
       <c r="F58" s="15" t="s">
         <v>166</v>
       </c>
@@ -3664,13 +3682,13 @@
         <v>46006</v>
       </c>
       <c r="C59" s="15" t="str">
-        <f>IF(ISBLANK(B59),"",TEXT(B59, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D59" s="52">
+      <c r="D59" s="15">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E59" s="85"/>
+      <c r="E59" s="74"/>
       <c r="F59" s="15" t="s">
         <v>173</v>
       </c>
@@ -3686,13 +3704,13 @@
         <v>46006</v>
       </c>
       <c r="C60" s="15" t="str">
-        <f>IF(ISBLANK(B60),"",TEXT(B60, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Monday</v>
       </c>
-      <c r="D60" s="52">
+      <c r="D60" s="15">
         <v>5.2</v>
       </c>
-      <c r="E60" s="85"/>
+      <c r="E60" s="74"/>
       <c r="F60" s="15" t="s">
         <v>177</v>
       </c>
@@ -3708,13 +3726,13 @@
         <v>46007</v>
       </c>
       <c r="C61" s="15" t="str">
-        <f>IF(ISBLANK(B61),"",TEXT(B61, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Tuesday</v>
       </c>
-      <c r="D61" s="52">
+      <c r="D61" s="15">
         <v>4.3</v>
       </c>
-      <c r="E61" s="85"/>
+      <c r="E61" s="74"/>
       <c r="F61" s="15" t="s">
         <v>168</v>
       </c>
@@ -3730,13 +3748,13 @@
         <v>46007</v>
       </c>
       <c r="C62" s="15" t="str">
-        <f>IF(ISBLANK(B62),"",TEXT(B62, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Tuesday</v>
       </c>
-      <c r="D62" s="52">
+      <c r="D62" s="15">
         <v>4.5</v>
       </c>
-      <c r="E62" s="85"/>
+      <c r="E62" s="74"/>
       <c r="F62" s="15" t="s">
         <v>189</v>
       </c>
@@ -3752,13 +3770,13 @@
         <v>46007</v>
       </c>
       <c r="C63" s="15" t="str">
-        <f>IF(ISBLANK(B63),"",TEXT(B63, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Tuesday</v>
       </c>
-      <c r="D63" s="52">
+      <c r="D63" s="15">
         <v>5.3</v>
       </c>
-      <c r="E63" s="85"/>
+      <c r="E63" s="74"/>
       <c r="F63" s="15" t="s">
         <v>175</v>
       </c>
@@ -3774,13 +3792,13 @@
         <v>46007</v>
       </c>
       <c r="C64" s="15" t="str">
-        <f>IF(ISBLANK(B64),"",TEXT(B64, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Tuesday</v>
       </c>
-      <c r="D64" s="52">
+      <c r="D64" s="15">
         <v>5.4</v>
       </c>
-      <c r="E64" s="85"/>
+      <c r="E64" s="74"/>
       <c r="F64" s="15" t="s">
         <v>186</v>
       </c>
@@ -3796,13 +3814,13 @@
         <v>46008</v>
       </c>
       <c r="C65" s="15" t="str">
-        <f>IF(ISBLANK(B65),"",TEXT(B65, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D65" s="52">
+      <c r="D65" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E65" s="85"/>
+      <c r="E65" s="74"/>
       <c r="F65" s="15" t="s">
         <v>190</v>
       </c>
@@ -3816,13 +3834,13 @@
         <v>46008</v>
       </c>
       <c r="C66" s="15" t="str">
-        <f>IF(ISBLANK(B66),"",TEXT(B66, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D66" s="52">
+      <c r="D66" s="15">
         <v>1.2</v>
       </c>
-      <c r="E66" s="85"/>
+      <c r="E66" s="74"/>
       <c r="F66" s="15" t="s">
         <v>191</v>
       </c>
@@ -3836,13 +3854,13 @@
         <v>46008</v>
       </c>
       <c r="C67" s="15" t="str">
-        <f>IF(ISBLANK(B67),"",TEXT(B67, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D67" s="52">
+      <c r="D67" s="15">
         <v>5.3</v>
       </c>
-      <c r="E67" s="85"/>
+      <c r="E67" s="74"/>
       <c r="F67" s="15" t="s">
         <v>192</v>
       </c>
@@ -3854,13 +3872,13 @@
         <v>46008</v>
       </c>
       <c r="C68" s="15" t="str">
-        <f>IF(ISBLANK(B68),"",TEXT(B68, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D68" s="52">
+      <c r="D68" s="15">
         <v>5.6</v>
       </c>
-      <c r="E68" s="85"/>
+      <c r="E68" s="74"/>
       <c r="F68" s="15" t="s">
         <v>174</v>
       </c>
@@ -3874,13 +3892,13 @@
         <v>46009</v>
       </c>
       <c r="C69" s="15" t="str">
-        <f>IF(ISBLANK(B69),"",TEXT(B69, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Thursday</v>
       </c>
-      <c r="D69" s="52">
+      <c r="D69" s="15">
         <v>5.4</v>
       </c>
-      <c r="E69" s="85"/>
+      <c r="E69" s="74"/>
       <c r="F69" s="15" t="s">
         <v>193</v>
       </c>
@@ -3894,11 +3912,11 @@
         <v>46009</v>
       </c>
       <c r="C70" s="15" t="str">
-        <f>IF(ISBLANK(B70),"",TEXT(B70, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Thursday</v>
       </c>
-      <c r="D70" s="52"/>
-      <c r="E70" s="85"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="74"/>
       <c r="F70" s="15" t="s">
         <v>194</v>
       </c>
@@ -3912,13 +3930,13 @@
         <v>46015</v>
       </c>
       <c r="C71" s="15" t="str">
-        <f>IF(ISBLANK(B71),"",TEXT(B71, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D71" s="52">
+      <c r="D71" s="15">
         <v>2.1</v>
       </c>
-      <c r="E71" s="85"/>
+      <c r="E71" s="74"/>
       <c r="F71" s="15" t="s">
         <v>187</v>
       </c>
@@ -3932,13 +3950,13 @@
         <v>46015</v>
       </c>
       <c r="C72" s="15" t="str">
-        <f>IF(ISBLANK(B72),"",TEXT(B72, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D72" s="52">
+      <c r="D72" s="15">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E72" s="85"/>
+      <c r="E72" s="74"/>
       <c r="F72" s="15" t="s">
         <v>188</v>
       </c>
@@ -3952,11 +3970,11 @@
         <v>46015</v>
       </c>
       <c r="C73" s="15" t="str">
-        <f>IF(ISBLANK(B73),"",TEXT(B73, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D73" s="52"/>
-      <c r="E73" s="85"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="74"/>
       <c r="F73" s="15" t="s">
         <v>180</v>
       </c>
@@ -3970,11 +3988,11 @@
         <v>46015</v>
       </c>
       <c r="C74" s="15" t="str">
-        <f>IF(ISBLANK(B74),"",TEXT(B74, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D74" s="52"/>
-      <c r="E74" s="85"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="74"/>
       <c r="F74" s="15" t="s">
         <v>185</v>
       </c>
@@ -3988,11 +4006,11 @@
         <v>46015</v>
       </c>
       <c r="C75" s="15" t="str">
-        <f>IF(ISBLANK(B75),"",TEXT(B75, "dddd"))</f>
+        <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="D75" s="52"/>
-      <c r="E75" s="85"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="74"/>
       <c r="F75" s="15" t="s">
         <v>179</v>
       </c>
@@ -4006,11 +4024,11 @@
         <v>46022</v>
       </c>
       <c r="C76" s="15" t="str">
-        <f>IF(ISBLANK(B76),"",TEXT(B76, "dddd"))</f>
+        <f t="shared" ref="C76:C107" si="3">IF(ISBLANK(B76),"",TEXT(B76, "dddd"))</f>
         <v>Wednesday</v>
       </c>
-      <c r="D76" s="52"/>
-      <c r="E76" s="85"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="74"/>
       <c r="F76" s="15" t="s">
         <v>195</v>
       </c>
@@ -4024,11 +4042,11 @@
         <v>46022</v>
       </c>
       <c r="C77" s="15" t="str">
-        <f>IF(ISBLANK(B77),"",TEXT(B77, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Wednesday</v>
       </c>
-      <c r="D77" s="52"/>
-      <c r="E77" s="85"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="74"/>
       <c r="F77" s="15" t="s">
         <v>202</v>
       </c>
@@ -4042,11 +4060,11 @@
         <v>46022</v>
       </c>
       <c r="C78" s="15" t="str">
-        <f>IF(ISBLANK(B78),"",TEXT(B78, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Wednesday</v>
       </c>
-      <c r="D78" s="52"/>
-      <c r="E78" s="85"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="74"/>
       <c r="F78" s="15" t="s">
         <v>196</v>
       </c>
@@ -4060,13 +4078,13 @@
         <v>46024</v>
       </c>
       <c r="C79" s="15" t="str">
-        <f>IF(ISBLANK(B79),"",TEXT(B79, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D79" s="52">
+      <c r="D79" s="15">
         <v>0.1</v>
       </c>
-      <c r="E79" s="85"/>
+      <c r="E79" s="74"/>
       <c r="F79" s="15" t="s">
         <v>204</v>
       </c>
@@ -4080,13 +4098,13 @@
         <v>46024</v>
       </c>
       <c r="C80" s="15" t="str">
-        <f>IF(ISBLANK(B80),"",TEXT(B80, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D80" s="52">
+      <c r="D80" s="15">
         <v>0.15</v>
       </c>
-      <c r="E80" s="85"/>
+      <c r="E80" s="74"/>
       <c r="F80" s="15" t="s">
         <v>211</v>
       </c>
@@ -4100,13 +4118,13 @@
         <v>46024</v>
       </c>
       <c r="C81" s="15" t="str">
-        <f>IF(ISBLANK(B81),"",TEXT(B81, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D81" s="52">
+      <c r="D81" s="15">
         <v>0.2</v>
       </c>
-      <c r="E81" s="85"/>
+      <c r="E81" s="74"/>
       <c r="F81" s="15" t="s">
         <v>207</v>
       </c>
@@ -4120,13 +4138,13 @@
         <v>46024</v>
       </c>
       <c r="C82" s="15" t="str">
-        <f>IF(ISBLANK(B82),"",TEXT(B82, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D82" s="52">
+      <c r="D82" s="15">
         <v>0.3</v>
       </c>
-      <c r="E82" s="85"/>
+      <c r="E82" s="74"/>
       <c r="F82" s="15" t="s">
         <v>205</v>
       </c>
@@ -4140,13 +4158,13 @@
         <v>46024</v>
       </c>
       <c r="C83" s="15" t="str">
-        <f>IF(ISBLANK(B83),"",TEXT(B83, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D83" s="52">
+      <c r="D83" s="15">
         <v>0.4</v>
       </c>
-      <c r="E83" s="85"/>
+      <c r="E83" s="74"/>
       <c r="F83" s="15" t="s">
         <v>206</v>
       </c>
@@ -4160,13 +4178,13 @@
         <v>46024</v>
       </c>
       <c r="C84" s="15" t="str">
-        <f>IF(ISBLANK(B84),"",TEXT(B84, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D84" s="52">
+      <c r="D84" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E84" s="85"/>
+      <c r="E84" s="74"/>
       <c r="F84" s="15" t="s">
         <v>197</v>
       </c>
@@ -4180,13 +4198,13 @@
         <v>46024</v>
       </c>
       <c r="C85" s="15" t="str">
-        <f>IF(ISBLANK(B85),"",TEXT(B85, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D85" s="52">
+      <c r="D85" s="15">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E85" s="85"/>
+      <c r="E85" s="74"/>
       <c r="F85" s="15" t="s">
         <v>212</v>
       </c>
@@ -4200,13 +4218,13 @@
         <v>46024</v>
       </c>
       <c r="C86" s="15" t="str">
-        <f>IF(ISBLANK(B86),"",TEXT(B86, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D86" s="52">
+      <c r="D86" s="15">
         <v>1.1299999999999999</v>
       </c>
-      <c r="E86" s="85"/>
+      <c r="E86" s="74"/>
       <c r="F86" s="15" t="s">
         <v>214</v>
       </c>
@@ -4218,13 +4236,13 @@
         <v>46024</v>
       </c>
       <c r="C87" s="15" t="str">
-        <f>IF(ISBLANK(B87),"",TEXT(B87, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D87" s="52">
+      <c r="D87" s="15">
         <v>1.2</v>
       </c>
-      <c r="E87" s="85"/>
+      <c r="E87" s="74"/>
       <c r="F87" s="15" t="s">
         <v>10</v>
       </c>
@@ -4238,13 +4256,13 @@
         <v>46024</v>
       </c>
       <c r="C88" s="15" t="str">
-        <f>IF(ISBLANK(B88),"",TEXT(B88, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D88" s="52">
+      <c r="D88" s="15">
         <v>1.3</v>
       </c>
-      <c r="E88" s="85"/>
+      <c r="E88" s="74"/>
       <c r="F88" s="15" t="s">
         <v>200</v>
       </c>
@@ -4256,13 +4274,13 @@
         <v>46024</v>
       </c>
       <c r="C89" s="15" t="str">
-        <f>IF(ISBLANK(B89),"",TEXT(B89, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D89" s="52">
+      <c r="D89" s="15">
         <v>2.1</v>
       </c>
-      <c r="E89" s="85"/>
+      <c r="E89" s="74"/>
       <c r="F89" s="15" t="s">
         <v>215</v>
       </c>
@@ -4276,13 +4294,13 @@
         <v>46024</v>
       </c>
       <c r="C90" s="15" t="str">
-        <f>IF(ISBLANK(B90),"",TEXT(B90, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D90" s="52">
+      <c r="D90" s="15">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E90" s="85"/>
+      <c r="E90" s="74"/>
       <c r="F90" s="15" t="s">
         <v>217</v>
       </c>
@@ -4296,13 +4314,13 @@
         <v>46024</v>
       </c>
       <c r="C91" s="15" t="str">
-        <f>IF(ISBLANK(B91),"",TEXT(B91, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D91" s="52">
+      <c r="D91" s="15">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E91" s="85"/>
+      <c r="E91" s="74"/>
       <c r="F91" s="15" t="s">
         <v>216</v>
       </c>
@@ -4316,13 +4334,13 @@
         <v>46024</v>
       </c>
       <c r="C92" s="15" t="str">
-        <f>IF(ISBLANK(B92),"",TEXT(B92, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D92" s="52">
+      <c r="D92" s="15">
         <v>3.1</v>
       </c>
-      <c r="E92" s="85"/>
+      <c r="E92" s="74"/>
       <c r="F92" s="15" t="s">
         <v>213</v>
       </c>
@@ -4336,13 +4354,13 @@
         <v>46024</v>
       </c>
       <c r="C93" s="15" t="str">
-        <f>IF(ISBLANK(B93),"",TEXT(B93, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D93" s="52">
+      <c r="D93" s="15">
         <v>3.2</v>
       </c>
-      <c r="E93" s="85"/>
+      <c r="E93" s="74"/>
       <c r="F93" s="15" t="s">
         <v>203</v>
       </c>
@@ -4356,13 +4374,13 @@
         <v>46024</v>
       </c>
       <c r="C94" s="15" t="str">
-        <f>IF(ISBLANK(B94),"",TEXT(B94, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D94" s="52">
+      <c r="D94" s="15">
         <v>3.3</v>
       </c>
-      <c r="E94" s="85"/>
+      <c r="E94" s="74"/>
       <c r="F94" s="15" t="s">
         <v>184</v>
       </c>
@@ -4376,13 +4394,13 @@
         <v>46024</v>
       </c>
       <c r="C95" s="15" t="str">
-        <f>IF(ISBLANK(B95),"",TEXT(B95, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D95" s="52">
+      <c r="D95" s="15">
         <v>3.4</v>
       </c>
-      <c r="E95" s="85"/>
+      <c r="E95" s="74"/>
       <c r="F95" s="15" t="s">
         <v>199</v>
       </c>
@@ -4396,13 +4414,13 @@
         <v>46024</v>
       </c>
       <c r="C96" s="15" t="str">
-        <f>IF(ISBLANK(B96),"",TEXT(B96, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D96" s="52">
+      <c r="D96" s="15">
         <v>3.6</v>
       </c>
-      <c r="E96" s="85"/>
+      <c r="E96" s="74"/>
       <c r="F96" s="15" t="s">
         <v>208</v>
       </c>
@@ -4416,10 +4434,10 @@
         <v>46024</v>
       </c>
       <c r="C97" s="15" t="str">
-        <f>IF(ISBLANK(B97),"",TEXT(B97, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D97" s="52">
+      <c r="D97" s="15">
         <v>4.0999999999999996</v>
       </c>
       <c r="E97" s="44"/>
@@ -4434,10 +4452,10 @@
         <v>46024</v>
       </c>
       <c r="C98" s="15" t="str">
-        <f>IF(ISBLANK(B98),"",TEXT(B98, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D98" s="52">
+      <c r="D98" s="15">
         <v>4.2</v>
       </c>
       <c r="E98" s="44"/>
@@ -4452,10 +4470,10 @@
         <v>46024</v>
       </c>
       <c r="C99" s="15" t="str">
-        <f>IF(ISBLANK(B99),"",TEXT(B99, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
-      <c r="D99" s="52">
+      <c r="D99" s="15">
         <v>4.3</v>
       </c>
       <c r="E99" s="44"/>
@@ -4470,11 +4488,11 @@
         <v>46027</v>
       </c>
       <c r="C100" s="15" t="str">
-        <f>IF(ISBLANK(B100),"",TEXT(B100, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Monday</v>
       </c>
-      <c r="D100" s="52"/>
-      <c r="E100" s="85"/>
+      <c r="D100" s="15"/>
+      <c r="E100" s="74"/>
       <c r="F100" s="15" t="s">
         <v>201</v>
       </c>
@@ -4488,11 +4506,11 @@
         <v>46028</v>
       </c>
       <c r="C101" s="15" t="str">
-        <f>IF(ISBLANK(B101),"",TEXT(B101, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Tuesday</v>
       </c>
-      <c r="D101" s="52"/>
-      <c r="E101" s="85"/>
+      <c r="D101" s="15"/>
+      <c r="E101" s="74"/>
       <c r="F101" s="11" t="s">
         <v>218</v>
       </c>
@@ -4506,10 +4524,10 @@
         <v>46028</v>
       </c>
       <c r="C102" s="15" t="str">
-        <f>IF(ISBLANK(B102),"",TEXT(B102, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Tuesday</v>
       </c>
-      <c r="D102" s="52"/>
+      <c r="D102" s="15"/>
       <c r="E102" s="44"/>
       <c r="F102" s="15" t="s">
         <v>219</v>
@@ -4522,10 +4540,10 @@
         <v>46028</v>
       </c>
       <c r="C103" s="15" t="str">
-        <f>IF(ISBLANK(B103),"",TEXT(B103, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Tuesday</v>
       </c>
-      <c r="D103" s="52"/>
+      <c r="D103" s="15"/>
       <c r="E103" s="44"/>
       <c r="F103" s="15" t="s">
         <v>220</v>
@@ -4538,11 +4556,11 @@
         <v>46030</v>
       </c>
       <c r="C104" s="15" t="str">
-        <f>IF(ISBLANK(B104),"",TEXT(B104, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Thursday</v>
       </c>
-      <c r="D104" s="52"/>
-      <c r="E104" s="85"/>
+      <c r="D104" s="15"/>
+      <c r="E104" s="74"/>
       <c r="F104" s="15" t="s">
         <v>198</v>
       </c>
@@ -4558,11 +4576,11 @@
         <v>46030</v>
       </c>
       <c r="C105" s="15" t="str">
-        <f>IF(ISBLANK(B105),"",TEXT(B105, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Thursday</v>
       </c>
-      <c r="D105" s="52"/>
-      <c r="E105" s="85"/>
+      <c r="D105" s="15"/>
+      <c r="E105" s="74"/>
       <c r="F105" s="15" t="s">
         <v>221</v>
       </c>
@@ -4578,11 +4596,11 @@
         <v>46034</v>
       </c>
       <c r="C106" s="15" t="str">
-        <f>IF(ISBLANK(B106),"",TEXT(B106, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Monday</v>
       </c>
-      <c r="D106" s="52"/>
-      <c r="E106" s="85"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="74"/>
       <c r="F106" s="15" t="s">
         <v>224</v>
       </c>
@@ -4598,13 +4616,13 @@
         <v>46035</v>
       </c>
       <c r="C107" s="15" t="str">
-        <f>IF(ISBLANK(B107),"",TEXT(B107, "dddd"))</f>
+        <f t="shared" si="3"/>
         <v>Tuesday</v>
       </c>
-      <c r="D107" s="52">
+      <c r="D107" s="15">
         <v>3.2</v>
       </c>
-      <c r="E107" s="85"/>
+      <c r="E107" s="74"/>
       <c r="F107" s="15" t="s">
         <v>225</v>
       </c>
@@ -4618,13 +4636,13 @@
         <v>46035</v>
       </c>
       <c r="C108" s="15" t="str">
-        <f>IF(ISBLANK(B108),"",TEXT(B108, "dddd"))</f>
+        <f t="shared" ref="C108:C139" si="4">IF(ISBLANK(B108),"",TEXT(B108, "dddd"))</f>
         <v>Tuesday</v>
       </c>
-      <c r="D108" s="52">
+      <c r="D108" s="15">
         <v>3.3</v>
       </c>
-      <c r="E108" s="85"/>
+      <c r="E108" s="74"/>
       <c r="F108" s="15" t="s">
         <v>234</v>
       </c>
@@ -4638,11 +4656,11 @@
         <v>46036</v>
       </c>
       <c r="C109" s="15" t="str">
-        <f>IF(ISBLANK(B109),"",TEXT(B109, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D109" s="52"/>
-      <c r="E109" s="85"/>
+      <c r="D109" s="15"/>
+      <c r="E109" s="74"/>
       <c r="F109" s="15" t="s">
         <v>235</v>
       </c>
@@ -4656,11 +4674,11 @@
         <v>46036</v>
       </c>
       <c r="C110" s="15" t="str">
-        <f>IF(ISBLANK(B110),"",TEXT(B110, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D110" s="52"/>
-      <c r="E110" s="85"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="74"/>
       <c r="F110" s="15" t="s">
         <v>236</v>
       </c>
@@ -4674,11 +4692,11 @@
         <v>46036</v>
       </c>
       <c r="C111" s="15" t="str">
-        <f>IF(ISBLANK(B111),"",TEXT(B111, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D111" s="52"/>
-      <c r="E111" s="85"/>
+      <c r="D111" s="15"/>
+      <c r="E111" s="74"/>
       <c r="F111" s="15" t="s">
         <v>237</v>
       </c>
@@ -4692,11 +4710,11 @@
         <v>46036</v>
       </c>
       <c r="C112" s="15" t="str">
-        <f>IF(ISBLANK(B112),"",TEXT(B112, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D112" s="52"/>
-      <c r="E112" s="85"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="74"/>
       <c r="F112" s="15" t="s">
         <v>238</v>
       </c>
@@ -4710,11 +4728,11 @@
         <v>46037</v>
       </c>
       <c r="C113" s="15" t="str">
-        <f>IF(ISBLANK(B113),"",TEXT(B113, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Thursday</v>
       </c>
-      <c r="D113" s="52"/>
-      <c r="E113" s="85"/>
+      <c r="D113" s="15"/>
+      <c r="E113" s="74"/>
       <c r="F113" s="15" t="s">
         <v>239</v>
       </c>
@@ -4728,13 +4746,13 @@
         <v>46038</v>
       </c>
       <c r="C114" s="15" t="str">
-        <f>IF(ISBLANK(B114),"",TEXT(B114, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Friday</v>
       </c>
-      <c r="D114" s="52">
+      <c r="D114" s="15">
         <v>0.01</v>
       </c>
-      <c r="E114" s="85"/>
+      <c r="E114" s="74"/>
       <c r="F114" s="15" t="s">
         <v>242</v>
       </c>
@@ -4750,13 +4768,13 @@
         <v>46038</v>
       </c>
       <c r="C115" s="15" t="str">
-        <f>IF(ISBLANK(B115),"",TEXT(B115, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Friday</v>
       </c>
-      <c r="D115" s="52">
+      <c r="D115" s="15">
         <v>0.1</v>
       </c>
-      <c r="E115" s="85"/>
+      <c r="E115" s="74"/>
       <c r="F115" s="15" t="s">
         <v>240</v>
       </c>
@@ -4772,13 +4790,13 @@
         <v>46038</v>
       </c>
       <c r="C116" s="15" t="str">
-        <f>IF(ISBLANK(B116),"",TEXT(B116, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Friday</v>
       </c>
-      <c r="D116" s="52">
+      <c r="D116" s="15">
         <v>3.3</v>
       </c>
-      <c r="E116" s="85"/>
+      <c r="E116" s="74"/>
       <c r="F116" s="15" t="s">
         <v>241</v>
       </c>
@@ -4794,25 +4812,25 @@
         <v>46038</v>
       </c>
       <c r="C117" s="15" t="str">
-        <f>IF(ISBLANK(B117),"",TEXT(B117, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Friday</v>
       </c>
-      <c r="D117" s="52"/>
-      <c r="E117" s="85"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="74"/>
       <c r="F117" s="15"/>
       <c r="G117" s="44"/>
       <c r="H117" s="16"/>
     </row>
     <row r="118" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B118" s="78">
+      <c r="B118" s="67">
         <v>46042</v>
       </c>
       <c r="C118" s="15" t="str">
-        <f>IF(ISBLANK(B118),"",TEXT(B118, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Tuesday</v>
       </c>
-      <c r="D118" s="52"/>
-      <c r="E118" s="85" t="s">
+      <c r="D118" s="15"/>
+      <c r="E118" s="74" t="s">
         <v>250</v>
       </c>
       <c r="F118" s="15" t="s">
@@ -4824,15 +4842,15 @@
       </c>
     </row>
     <row r="119" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B119" s="78">
+      <c r="B119" s="67">
         <v>46042</v>
       </c>
       <c r="C119" s="15" t="str">
-        <f>IF(ISBLANK(B119),"",TEXT(B119, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Tuesday</v>
       </c>
-      <c r="D119" s="52"/>
-      <c r="E119" s="85" t="s">
+      <c r="D119" s="15"/>
+      <c r="E119" s="74" t="s">
         <v>250</v>
       </c>
       <c r="F119" s="15" t="s">
@@ -4844,15 +4862,15 @@
       </c>
     </row>
     <row r="120" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B120" s="78">
+      <c r="B120" s="67">
         <v>46042</v>
       </c>
       <c r="C120" s="15" t="str">
-        <f>IF(ISBLANK(B120),"",TEXT(B120, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Tuesday</v>
       </c>
-      <c r="D120" s="52"/>
-      <c r="E120" s="85" t="s">
+      <c r="D120" s="15"/>
+      <c r="E120" s="74" t="s">
         <v>250</v>
       </c>
       <c r="F120" s="15" t="s">
@@ -4862,15 +4880,15 @@
       <c r="H120" s="16"/>
     </row>
     <row r="121" spans="2:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="B121" s="78">
+      <c r="B121" s="67">
         <v>46042</v>
       </c>
       <c r="C121" s="15" t="str">
-        <f>IF(ISBLANK(B121),"",TEXT(B121, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Tuesday</v>
       </c>
-      <c r="D121" s="52"/>
-      <c r="E121" s="85" t="s">
+      <c r="D121" s="15"/>
+      <c r="E121" s="74" t="s">
         <v>249</v>
       </c>
       <c r="F121" s="15" t="s">
@@ -4880,15 +4898,15 @@
       <c r="H121" s="16"/>
     </row>
     <row r="122" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B122" s="78">
+      <c r="B122" s="67">
         <v>46042</v>
       </c>
       <c r="C122" s="15" t="str">
-        <f>IF(ISBLANK(B122),"",TEXT(B122, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Tuesday</v>
       </c>
-      <c r="D122" s="52"/>
-      <c r="E122" s="85" t="s">
+      <c r="D122" s="15"/>
+      <c r="E122" s="74" t="s">
         <v>253</v>
       </c>
       <c r="F122" s="15" t="s">
@@ -4898,15 +4916,15 @@
       <c r="H122" s="16"/>
     </row>
     <row r="123" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B123" s="78">
+      <c r="B123" s="67">
         <v>46043</v>
       </c>
       <c r="C123" s="15" t="str">
-        <f>IF(ISBLANK(B123),"",TEXT(B123, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D123" s="52"/>
-      <c r="E123" s="85" t="s">
+      <c r="D123" s="15"/>
+      <c r="E123" s="74" t="s">
         <v>250</v>
       </c>
       <c r="F123" s="15" t="s">
@@ -4916,15 +4934,15 @@
       <c r="H123" s="16"/>
     </row>
     <row r="124" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B124" s="78">
+      <c r="B124" s="67">
         <v>46043</v>
       </c>
       <c r="C124" s="15" t="str">
-        <f>IF(ISBLANK(B124),"",TEXT(B124, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D124" s="52"/>
-      <c r="E124" s="85" t="s">
+      <c r="D124" s="15"/>
+      <c r="E124" s="74" t="s">
         <v>250</v>
       </c>
       <c r="F124" s="15" t="s">
@@ -4934,15 +4952,15 @@
       <c r="H124" s="16"/>
     </row>
     <row r="125" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B125" s="78">
+      <c r="B125" s="67">
         <v>46043</v>
       </c>
       <c r="C125" s="15" t="str">
-        <f>IF(ISBLANK(B125),"",TEXT(B125, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D125" s="52"/>
-      <c r="E125" s="85" t="s">
+      <c r="D125" s="15"/>
+      <c r="E125" s="74" t="s">
         <v>254</v>
       </c>
       <c r="F125" s="15" t="s">
@@ -4952,15 +4970,15 @@
       <c r="H125" s="16"/>
     </row>
     <row r="126" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B126" s="78">
+      <c r="B126" s="67">
         <v>46043</v>
       </c>
       <c r="C126" s="15" t="str">
-        <f>IF(ISBLANK(B126),"",TEXT(B126, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D126" s="52"/>
-      <c r="E126" s="85" t="s">
+      <c r="D126" s="15"/>
+      <c r="E126" s="74" t="s">
         <v>254</v>
       </c>
       <c r="F126" s="15" t="s">
@@ -4970,15 +4988,15 @@
       <c r="H126" s="16"/>
     </row>
     <row r="127" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B127" s="78">
+      <c r="B127" s="67">
         <v>46043</v>
       </c>
       <c r="C127" s="15" t="str">
-        <f>IF(ISBLANK(B127),"",TEXT(B127, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="D127" s="52"/>
-      <c r="E127" s="85" t="s">
+      <c r="D127" s="15"/>
+      <c r="E127" s="74" t="s">
         <v>253</v>
       </c>
       <c r="F127" s="15" t="s">
@@ -4988,15 +5006,15 @@
       <c r="H127" s="16"/>
     </row>
     <row r="128" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B128" s="78">
+      <c r="B128" s="67">
         <v>46044</v>
       </c>
       <c r="C128" s="15" t="str">
-        <f>IF(ISBLANK(B128),"",TEXT(B128, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Thursday</v>
       </c>
-      <c r="D128" s="52"/>
-      <c r="E128" s="85" t="s">
+      <c r="D128" s="15"/>
+      <c r="E128" s="74" t="s">
         <v>249</v>
       </c>
       <c r="F128" s="15" t="s">
@@ -5006,15 +5024,15 @@
       <c r="H128" s="16"/>
     </row>
     <row r="129" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B129" s="78">
+      <c r="B129" s="67">
         <v>46044</v>
       </c>
       <c r="C129" s="15" t="str">
-        <f>IF(ISBLANK(B129),"",TEXT(B129, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Thursday</v>
       </c>
-      <c r="D129" s="52"/>
-      <c r="E129" s="85" t="s">
+      <c r="D129" s="15"/>
+      <c r="E129" s="74" t="s">
         <v>253</v>
       </c>
       <c r="F129" s="15" t="s">
@@ -5024,15 +5042,15 @@
       <c r="H129" s="16"/>
     </row>
     <row r="130" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B130" s="78">
+      <c r="B130" s="67">
         <v>46045</v>
       </c>
       <c r="C130" s="15" t="str">
-        <f>IF(ISBLANK(B130),"",TEXT(B130, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Friday</v>
       </c>
-      <c r="D130" s="52"/>
-      <c r="E130" s="85" t="s">
+      <c r="D130" s="15"/>
+      <c r="E130" s="74" t="s">
         <v>249</v>
       </c>
       <c r="F130" s="15" t="s">
@@ -5042,15 +5060,15 @@
       <c r="H130" s="16"/>
     </row>
     <row r="131" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B131" s="78">
+      <c r="B131" s="67">
         <v>46045</v>
       </c>
       <c r="C131" s="15" t="str">
-        <f>IF(ISBLANK(B131),"",TEXT(B131, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Friday</v>
       </c>
-      <c r="D131" s="52"/>
-      <c r="E131" s="85" t="s">
+      <c r="D131" s="15"/>
+      <c r="E131" s="74" t="s">
         <v>249</v>
       </c>
       <c r="F131" s="15" t="s">
@@ -5060,15 +5078,15 @@
       <c r="H131" s="16"/>
     </row>
     <row r="132" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B132" s="78">
+      <c r="B132" s="67">
         <v>46045</v>
       </c>
       <c r="C132" s="15" t="str">
-        <f>IF(ISBLANK(B132),"",TEXT(B132, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Friday</v>
       </c>
-      <c r="D132" s="52"/>
-      <c r="E132" s="85" t="s">
+      <c r="D132" s="15"/>
+      <c r="E132" s="74" t="s">
         <v>253</v>
       </c>
       <c r="F132" s="15" t="s">
@@ -5082,11 +5100,11 @@
         <v>46055</v>
       </c>
       <c r="C133" s="15" t="str">
-        <f>IF(ISBLANK(B133),"",TEXT(B133, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v>Monday</v>
       </c>
-      <c r="D133" s="52"/>
-      <c r="E133" s="85"/>
+      <c r="D133" s="15"/>
+      <c r="E133" s="74"/>
       <c r="F133" s="15" t="s">
         <v>232</v>
       </c>
@@ -5098,11 +5116,11 @@
     <row r="134" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B134" s="13"/>
       <c r="C134" s="15" t="str">
-        <f>IF(ISBLANK(B134),"",TEXT(B134, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="D134" s="52"/>
-      <c r="E134" s="85"/>
+      <c r="D134" s="15"/>
+      <c r="E134" s="74"/>
       <c r="F134" s="15"/>
       <c r="G134" s="44"/>
       <c r="H134" s="16"/>
@@ -5110,11 +5128,11 @@
     <row r="135" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B135" s="13"/>
       <c r="C135" s="15" t="str">
-        <f>IF(ISBLANK(B135),"",TEXT(B135, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="D135" s="52"/>
-      <c r="E135" s="85"/>
+      <c r="D135" s="15"/>
+      <c r="E135" s="74"/>
       <c r="F135" s="15"/>
       <c r="G135" s="44"/>
       <c r="H135" s="16"/>
@@ -5122,11 +5140,11 @@
     <row r="136" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B136" s="13"/>
       <c r="C136" s="15" t="str">
-        <f>IF(ISBLANK(B136),"",TEXT(B136, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="D136" s="52"/>
-      <c r="E136" s="85"/>
+      <c r="D136" s="15"/>
+      <c r="E136" s="74"/>
       <c r="F136" s="15"/>
       <c r="G136" s="44"/>
       <c r="H136" s="16"/>
@@ -5134,11 +5152,11 @@
     <row r="137" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B137" s="13"/>
       <c r="C137" s="15" t="str">
-        <f>IF(ISBLANK(B137),"",TEXT(B137, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="D137" s="52"/>
-      <c r="E137" s="85"/>
+      <c r="D137" s="15"/>
+      <c r="E137" s="74"/>
       <c r="F137" s="15"/>
       <c r="G137" s="44"/>
       <c r="H137" s="16"/>
@@ -5146,11 +5164,11 @@
     <row r="138" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B138" s="13"/>
       <c r="C138" s="15" t="str">
-        <f>IF(ISBLANK(B138),"",TEXT(B138, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="D138" s="52"/>
-      <c r="E138" s="85"/>
+      <c r="D138" s="15"/>
+      <c r="E138" s="74"/>
       <c r="F138" s="15"/>
       <c r="G138" s="44"/>
       <c r="H138" s="16"/>
@@ -5158,11 +5176,11 @@
     <row r="139" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B139" s="13"/>
       <c r="C139" s="15" t="str">
-        <f>IF(ISBLANK(B139),"",TEXT(B139, "dddd"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="D139" s="52"/>
-      <c r="E139" s="85"/>
+      <c r="D139" s="15"/>
+      <c r="E139" s="74"/>
       <c r="F139" s="15"/>
       <c r="G139" s="44"/>
       <c r="H139" s="16"/>
@@ -5170,11 +5188,11 @@
     <row r="140" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B140" s="13"/>
       <c r="C140" s="15" t="str">
-        <f>IF(ISBLANK(B140),"",TEXT(B140, "dddd"))</f>
+        <f t="shared" ref="C140:C171" si="5">IF(ISBLANK(B140),"",TEXT(B140, "dddd"))</f>
         <v/>
       </c>
-      <c r="D140" s="52"/>
-      <c r="E140" s="85"/>
+      <c r="D140" s="15"/>
+      <c r="E140" s="74"/>
       <c r="F140" s="15"/>
       <c r="G140" s="44"/>
       <c r="H140" s="16"/>
@@ -5182,11 +5200,11 @@
     <row r="141" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B141" s="13"/>
       <c r="C141" s="15" t="str">
-        <f>IF(ISBLANK(B141),"",TEXT(B141, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D141" s="52"/>
-      <c r="E141" s="85"/>
+      <c r="D141" s="15"/>
+      <c r="E141" s="74"/>
       <c r="F141" s="15"/>
       <c r="G141" s="44"/>
       <c r="H141" s="16"/>
@@ -5194,11 +5212,11 @@
     <row r="142" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B142" s="13"/>
       <c r="C142" s="15" t="str">
-        <f>IF(ISBLANK(B142),"",TEXT(B142, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D142" s="52"/>
-      <c r="E142" s="85"/>
+      <c r="D142" s="15"/>
+      <c r="E142" s="74"/>
       <c r="F142" s="15"/>
       <c r="G142" s="44"/>
       <c r="H142" s="16"/>
@@ -5206,11 +5224,11 @@
     <row r="143" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B143" s="13"/>
       <c r="C143" s="15" t="str">
-        <f>IF(ISBLANK(B143),"",TEXT(B143, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D143" s="52"/>
-      <c r="E143" s="85"/>
+      <c r="D143" s="15"/>
+      <c r="E143" s="74"/>
       <c r="F143" s="15"/>
       <c r="G143" s="44"/>
       <c r="H143" s="16"/>
@@ -5218,11 +5236,11 @@
     <row r="144" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B144" s="13"/>
       <c r="C144" s="15" t="str">
-        <f>IF(ISBLANK(B144),"",TEXT(B144, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D144" s="52"/>
-      <c r="E144" s="85"/>
+      <c r="D144" s="15"/>
+      <c r="E144" s="74"/>
       <c r="F144" s="15"/>
       <c r="G144" s="44"/>
       <c r="H144" s="16"/>
@@ -5230,11 +5248,11 @@
     <row r="145" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B145" s="13"/>
       <c r="C145" s="15" t="str">
-        <f>IF(ISBLANK(B145),"",TEXT(B145, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D145" s="52"/>
-      <c r="E145" s="85"/>
+      <c r="D145" s="15"/>
+      <c r="E145" s="74"/>
       <c r="F145" s="15"/>
       <c r="G145" s="44"/>
       <c r="H145" s="16"/>
@@ -5242,11 +5260,11 @@
     <row r="146" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B146" s="13"/>
       <c r="C146" s="15" t="str">
-        <f>IF(ISBLANK(B146),"",TEXT(B146, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D146" s="52"/>
-      <c r="E146" s="85"/>
+      <c r="D146" s="15"/>
+      <c r="E146" s="74"/>
       <c r="F146" s="15"/>
       <c r="G146" s="44"/>
       <c r="H146" s="16"/>
@@ -5254,11 +5272,11 @@
     <row r="147" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B147" s="13"/>
       <c r="C147" s="15" t="str">
-        <f>IF(ISBLANK(B147),"",TEXT(B147, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D147" s="52"/>
-      <c r="E147" s="85"/>
+      <c r="D147" s="15"/>
+      <c r="E147" s="74"/>
       <c r="F147" s="15"/>
       <c r="G147" s="44"/>
       <c r="H147" s="16"/>
@@ -5266,11 +5284,11 @@
     <row r="148" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B148" s="13"/>
       <c r="C148" s="15" t="str">
-        <f>IF(ISBLANK(B148),"",TEXT(B148, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D148" s="52"/>
-      <c r="E148" s="85"/>
+      <c r="D148" s="15"/>
+      <c r="E148" s="74"/>
       <c r="F148" s="15"/>
       <c r="G148" s="44"/>
       <c r="H148" s="16"/>
@@ -5278,11 +5296,11 @@
     <row r="149" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B149" s="13"/>
       <c r="C149" s="15" t="str">
-        <f>IF(ISBLANK(B149),"",TEXT(B149, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D149" s="52"/>
-      <c r="E149" s="85"/>
+      <c r="D149" s="15"/>
+      <c r="E149" s="74"/>
       <c r="F149" s="15" t="s">
         <v>182</v>
       </c>
@@ -5294,11 +5312,11 @@
     <row r="150" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B150" s="13"/>
       <c r="C150" s="15" t="str">
-        <f>IF(ISBLANK(B150),"",TEXT(B150, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D150" s="52"/>
-      <c r="E150" s="85"/>
+      <c r="D150" s="15"/>
+      <c r="E150" s="74"/>
       <c r="F150" s="15"/>
       <c r="G150" s="44" t="s">
         <v>231</v>
@@ -5308,11 +5326,11 @@
     <row r="151" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B151" s="13"/>
       <c r="C151" s="15" t="str">
-        <f>IF(ISBLANK(B151),"",TEXT(B151, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D151" s="52"/>
-      <c r="E151" s="85"/>
+      <c r="D151" s="15"/>
+      <c r="E151" s="74"/>
       <c r="F151" s="15"/>
       <c r="G151" s="44" t="s">
         <v>229</v>
@@ -5322,11 +5340,11 @@
     <row r="152" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B152" s="13"/>
       <c r="C152" s="15" t="str">
-        <f>IF(ISBLANK(B152),"",TEXT(B152, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D152" s="52"/>
-      <c r="E152" s="85"/>
+      <c r="D152" s="15"/>
+      <c r="E152" s="74"/>
       <c r="F152" s="15" t="s">
         <v>226</v>
       </c>
@@ -5338,11 +5356,11 @@
     <row r="153" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B153" s="13"/>
       <c r="C153" s="15" t="str">
-        <f>IF(ISBLANK(B153),"",TEXT(B153, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D153" s="52"/>
-      <c r="E153" s="85"/>
+      <c r="D153" s="15"/>
+      <c r="E153" s="74"/>
       <c r="F153" s="15" t="s">
         <v>178</v>
       </c>
@@ -5354,11 +5372,11 @@
     <row r="154" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B154" s="13"/>
       <c r="C154" s="15" t="str">
-        <f>IF(ISBLANK(B154),"",TEXT(B154, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D154" s="52"/>
-      <c r="E154" s="85"/>
+      <c r="D154" s="15"/>
+      <c r="E154" s="74"/>
       <c r="F154" s="15" t="s">
         <v>181</v>
       </c>
@@ -5370,11 +5388,11 @@
     <row r="155" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B155" s="13"/>
       <c r="C155" s="15" t="str">
-        <f>IF(ISBLANK(B155),"",TEXT(B155, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D155" s="52"/>
-      <c r="E155" s="85"/>
+      <c r="D155" s="15"/>
+      <c r="E155" s="74"/>
       <c r="F155" s="15" t="s">
         <v>169</v>
       </c>
@@ -5386,10 +5404,10 @@
     <row r="156" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B156" s="13"/>
       <c r="C156" s="15" t="str">
-        <f>IF(ISBLANK(B156),"",TEXT(B156, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D156" s="52"/>
+      <c r="D156" s="15"/>
       <c r="E156" s="44"/>
       <c r="F156" s="15" t="s">
         <v>222</v>
@@ -5402,10 +5420,10 @@
     <row r="157" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B157" s="13"/>
       <c r="C157" s="15" t="str">
-        <f>IF(ISBLANK(B157),"",TEXT(B157, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D157" s="52"/>
+      <c r="D157" s="15"/>
       <c r="E157" s="44"/>
       <c r="F157" s="15" t="s">
         <v>223</v>
@@ -5418,11 +5436,11 @@
     <row r="158" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B158" s="13"/>
       <c r="C158" s="15" t="str">
-        <f>IF(ISBLANK(B158),"",TEXT(B158, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D158" s="52"/>
-      <c r="E158" s="85"/>
+      <c r="D158" s="15"/>
+      <c r="E158" s="74"/>
       <c r="F158" s="15" t="s">
         <v>233</v>
       </c>
@@ -5432,11 +5450,11 @@
     <row r="159" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B159" s="13"/>
       <c r="C159" s="15" t="str">
-        <f>IF(ISBLANK(B159),"",TEXT(B159, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D159" s="52"/>
-      <c r="E159" s="85"/>
+      <c r="D159" s="15"/>
+      <c r="E159" s="74"/>
       <c r="F159" s="15" t="s">
         <v>244</v>
       </c>
@@ -5446,11 +5464,11 @@
     <row r="160" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B160" s="13"/>
       <c r="C160" s="15" t="str">
-        <f>IF(ISBLANK(B160),"",TEXT(B160, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D160" s="52"/>
-      <c r="E160" s="85"/>
+      <c r="D160" s="15"/>
+      <c r="E160" s="74"/>
       <c r="F160" s="15" t="s">
         <v>245</v>
       </c>
@@ -5460,11 +5478,11 @@
     <row r="161" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B161" s="13"/>
       <c r="C161" s="15" t="str">
-        <f>IF(ISBLANK(B161),"",TEXT(B161, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D161" s="52"/>
-      <c r="E161" s="85"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="74"/>
       <c r="F161" s="15" t="s">
         <v>246</v>
       </c>
@@ -5474,11 +5492,11 @@
     <row r="162" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B162" s="13"/>
       <c r="C162" s="15" t="str">
-        <f>IF(ISBLANK(B162),"",TEXT(B162, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D162" s="52"/>
-      <c r="E162" s="85"/>
+      <c r="D162" s="15"/>
+      <c r="E162" s="74"/>
       <c r="F162" s="15" t="s">
         <v>247</v>
       </c>
@@ -5488,11 +5506,11 @@
     <row r="163" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B163" s="13"/>
       <c r="C163" s="15" t="str">
-        <f>IF(ISBLANK(B163),"",TEXT(B163, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D163" s="52"/>
-      <c r="E163" s="85"/>
+      <c r="D163" s="15"/>
+      <c r="E163" s="74"/>
       <c r="F163" s="15" t="s">
         <v>248</v>
       </c>
@@ -5502,11 +5520,11 @@
     <row r="164" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B164" s="13"/>
       <c r="C164" s="15" t="str">
-        <f>IF(ISBLANK(B164),"",TEXT(B164, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D164" s="52"/>
-      <c r="E164" s="85"/>
+      <c r="D164" s="15"/>
+      <c r="E164" s="74"/>
       <c r="F164" s="11" t="s">
         <v>249</v>
       </c>
@@ -5516,11 +5534,11 @@
     <row r="165" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B165" s="13"/>
       <c r="C165" s="15" t="str">
-        <f>IF(ISBLANK(B165),"",TEXT(B165, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D165" s="52"/>
-      <c r="E165" s="85"/>
+      <c r="D165" s="15"/>
+      <c r="E165" s="74"/>
       <c r="F165" s="15"/>
       <c r="G165" s="44"/>
       <c r="H165" s="16"/>
@@ -5528,10 +5546,10 @@
     <row r="166" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B166" s="13"/>
       <c r="C166" s="15" t="str">
-        <f>IF(ISBLANK(B166),"",TEXT(B166, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D166" s="52"/>
+      <c r="D166" s="15"/>
       <c r="E166" s="44"/>
       <c r="F166" s="15"/>
       <c r="G166" s="44"/>
@@ -5540,10 +5558,10 @@
     <row r="167" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B167" s="13"/>
       <c r="C167" s="15" t="str">
-        <f>IF(ISBLANK(B167),"",TEXT(B167, "dddd"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="D167" s="52"/>
+      <c r="D167" s="15"/>
       <c r="E167" s="44"/>
       <c r="F167" s="15"/>
       <c r="G167" s="44"/>
@@ -5552,7 +5570,7 @@
     <row r="168" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B168" s="13"/>
       <c r="C168" s="15"/>
-      <c r="D168" s="52"/>
+      <c r="D168" s="15"/>
       <c r="E168" s="44"/>
       <c r="F168" s="15"/>
       <c r="G168" s="44"/>
@@ -5564,7 +5582,7 @@
         <f>IF(ISBLANK(B169),"",TEXT(B169, "dddd"))</f>
         <v/>
       </c>
-      <c r="D169" s="52"/>
+      <c r="D169" s="15"/>
       <c r="E169" s="44"/>
       <c r="F169" s="15"/>
       <c r="G169" s="44"/>
@@ -5576,7 +5594,7 @@
         <f>IF(ISBLANK(B170),"",TEXT(B170, "dddd"))</f>
         <v/>
       </c>
-      <c r="D170" s="52"/>
+      <c r="D170" s="15"/>
       <c r="E170" s="44"/>
       <c r="F170" s="15"/>
       <c r="G170" s="44"/>
@@ -5588,16 +5606,16 @@
         <f>IF(ISBLANK(B171),"",TEXT(B171, "dddd"))</f>
         <v/>
       </c>
-      <c r="D171" s="52"/>
+      <c r="D171" s="15"/>
       <c r="E171" s="44"/>
       <c r="F171" s="15"/>
       <c r="G171" s="44"/>
       <c r="H171" s="17"/>
     </row>
     <row r="172" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="49"/>
+      <c r="B172" s="46"/>
       <c r="C172" s="18"/>
-      <c r="D172" s="53"/>
+      <c r="D172" s="18"/>
       <c r="E172" s="45"/>
       <c r="F172" s="18"/>
       <c r="G172" s="45"/>
@@ -5636,6 +5654,62 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A494E0C-A444-1348-8A46-46138A1D3E36}">
+  <dimension ref="B2:M3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="C2" s="79" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>281</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>282</v>
+      </c>
+      <c r="F2" s="79" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="79" t="s">
+        <v>284</v>
+      </c>
+      <c r="I2" s="79" t="s">
+        <v>285</v>
+      </c>
+      <c r="J2" s="79" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" s="79" t="s">
+        <v>287</v>
+      </c>
+      <c r="L2" s="79" t="s">
+        <v>288</v>
+      </c>
+      <c r="M2" s="79" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" s="48">
+        <v>46076</v>
+      </c>
+      <c r="C3">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17702B44-67CA-224A-8B7B-AFB2F9E126A1}">
   <dimension ref="B6:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5685,7 +5759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CF99CA-4416-4E89-816C-1EB7F12FACC6}">
   <dimension ref="B1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5704,21 +5778,21 @@
   <sheetData>
     <row r="1" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:14" ht="30" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="48"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="3" spans="2:14" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
@@ -6476,7 +6550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E04BDE-9139-43BE-8886-A956CCD7558E}">
   <dimension ref="B2:B9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/ToDo.xlsx
+++ b/ToDo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleckleinman/Documents/TheGrantScout/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA2FAE4-9A7F-C94B-934B-E3F963016C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DEAD82-EEE0-3245-ABD0-ACC9078E84C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19280" yWindow="500" windowWidth="18960" windowHeight="19200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="680" windowWidth="18960" windowHeight="19220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beta Leads'!$B$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Do'!$B$2:$H$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Do'!$B$2:$H$179</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="301">
   <si>
     <t>Task</t>
   </si>
@@ -931,6 +931,39 @@
   </si>
   <si>
     <t>Meeting Scheduled</t>
+  </si>
+  <si>
+    <t>Linkedin posts on Fridays</t>
+  </si>
+  <si>
+    <t>update TGS data dictionary</t>
+  </si>
+  <si>
+    <t>Analyze VB report process</t>
+  </si>
+  <si>
+    <t>Research CNE adhacent companies</t>
+  </si>
+  <si>
+    <t>Email accountability my KPI goals for the week (and my new process)</t>
+  </si>
+  <si>
+    <t>Open the leads excel sheet and see who to follow up with? (afternoon activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learn about what kind of nonprofits we can work with now that we have section I data (public charities) </t>
+  </si>
+  <si>
+    <t>How does the I data impact our reports flow?</t>
+  </si>
+  <si>
+    <t>How much time did we save Matt looking through websites to find out eligibility - add that to the website</t>
+  </si>
+  <si>
+    <t>Put a more current example report on the website</t>
+  </si>
+  <si>
+    <t>Make Matts March Report</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1459,12 +1492,225 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="37">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9966"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF7FDAA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9966"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB7C3FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFABE0FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB7C3FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9966"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB7C3FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9966"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1514,57 +1760,19 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB7C3FD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9966"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC6C7FF"/>
+      <color rgb="FF9999FF"/>
+      <color rgb="FFABE0FF"/>
+      <color rgb="FFBAE9EF"/>
+      <color rgb="FFF7FDAA"/>
       <color rgb="FFB7C3FD"/>
       <color rgb="FFCCCCFF"/>
       <color rgb="FFFFCCFF"/>
       <color rgb="FFFF9966"/>
-      <color rgb="FF9999FF"/>
       <color rgb="FFFF99CC"/>
     </mruColors>
   </colors>
@@ -2096,7 +2304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A518F1-E8D1-4EDA-B8FC-EAEFD9F39116}">
-  <dimension ref="B1:S172"/>
+  <dimension ref="B1:S179"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="23.5" style="66" customWidth="1"/>
@@ -2154,7 +2362,7 @@
         <v>45992</v>
       </c>
       <c r="C3" s="69" t="str">
-        <f t="shared" ref="C3:C11" si="0">TEXT(B3, "dddd")</f>
+        <f>TEXT(B3, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D3" s="70">
@@ -2187,7 +2395,7 @@
         <v>45992</v>
       </c>
       <c r="C4" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B4, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D4" s="15">
@@ -2220,7 +2428,7 @@
         <v>45992</v>
       </c>
       <c r="C5" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B5, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D5" s="15">
@@ -2253,7 +2461,7 @@
         <v>45992</v>
       </c>
       <c r="C6" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B6, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D6" s="15">
@@ -2286,7 +2494,7 @@
         <v>45992</v>
       </c>
       <c r="C7" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B7, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D7" s="15">
@@ -2319,7 +2527,7 @@
         <v>45992</v>
       </c>
       <c r="C8" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B8, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D8" s="15">
@@ -2352,7 +2560,7 @@
         <v>45992</v>
       </c>
       <c r="C9" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B9, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D9" s="15">
@@ -2385,7 +2593,7 @@
         <v>45992</v>
       </c>
       <c r="C10" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B10, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D10" s="15">
@@ -2418,7 +2626,7 @@
         <v>45992</v>
       </c>
       <c r="C11" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(B11, "dddd")</f>
         <v>Monday</v>
       </c>
       <c r="D11" s="15">
@@ -2451,7 +2659,7 @@
         <v>45992</v>
       </c>
       <c r="C12" s="15" t="str">
-        <f t="shared" ref="C12:C43" si="1">IF(ISBLANK(B12),"",TEXT(B12, "dddd"))</f>
+        <f>IF(ISBLANK(B12),"",TEXT(B12, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D12" s="15">
@@ -2484,7 +2692,7 @@
         <v>45994</v>
       </c>
       <c r="C13" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B13),"",TEXT(B13, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D13" s="15">
@@ -2517,7 +2725,7 @@
         <v>45994</v>
       </c>
       <c r="C14" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B14),"",TEXT(B14, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D14" s="15">
@@ -2550,7 +2758,7 @@
         <v>45994</v>
       </c>
       <c r="C15" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B15),"",TEXT(B15, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D15" s="38">
@@ -2583,7 +2791,7 @@
         <v>45994</v>
       </c>
       <c r="C16" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B16),"",TEXT(B16, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D16" s="15">
@@ -2616,7 +2824,7 @@
         <v>45994</v>
       </c>
       <c r="C17" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B17),"",TEXT(B17, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D17" s="15">
@@ -2649,7 +2857,7 @@
         <v>45994</v>
       </c>
       <c r="C18" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B18),"",TEXT(B18, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D18" s="15">
@@ -2682,7 +2890,7 @@
         <v>45994</v>
       </c>
       <c r="C19" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B19),"",TEXT(B19, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D19" s="15">
@@ -2715,7 +2923,7 @@
         <v>45994</v>
       </c>
       <c r="C20" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B20),"",TEXT(B20, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D20" s="15">
@@ -2748,7 +2956,7 @@
         <v>45995</v>
       </c>
       <c r="C21" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B21),"",TEXT(B21, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D21" s="15">
@@ -2781,7 +2989,7 @@
         <v>45995</v>
       </c>
       <c r="C22" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B22),"",TEXT(B22, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D22" s="15">
@@ -2814,7 +3022,7 @@
         <v>45995</v>
       </c>
       <c r="C23" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B23),"",TEXT(B23, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D23" s="15">
@@ -2847,7 +3055,7 @@
         <v>45995</v>
       </c>
       <c r="C24" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B24),"",TEXT(B24, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D24" s="15">
@@ -2880,7 +3088,7 @@
         <v>45995</v>
       </c>
       <c r="C25" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B25),"",TEXT(B25, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D25" s="15">
@@ -2913,7 +3121,7 @@
         <v>45995</v>
       </c>
       <c r="C26" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B26),"",TEXT(B26, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D26" s="15">
@@ -2946,7 +3154,7 @@
         <v>45995</v>
       </c>
       <c r="C27" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B27),"",TEXT(B27, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D27" s="15"/>
@@ -2975,7 +3183,7 @@
         <v>45996</v>
       </c>
       <c r="C28" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B28),"",TEXT(B28, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D28" s="15">
@@ -3008,7 +3216,7 @@
         <v>45996</v>
       </c>
       <c r="C29" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B29),"",TEXT(B29, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D29" s="15">
@@ -3041,7 +3249,7 @@
         <v>45996</v>
       </c>
       <c r="C30" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B30),"",TEXT(B30, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D30" s="15">
@@ -3074,7 +3282,7 @@
         <v>45996</v>
       </c>
       <c r="C31" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B31),"",TEXT(B31, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D31" s="15">
@@ -3107,7 +3315,7 @@
         <v>45996</v>
       </c>
       <c r="C32" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B32),"",TEXT(B32, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D32" s="15"/>
@@ -3138,7 +3346,7 @@
         <v>45999</v>
       </c>
       <c r="C33" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B33),"",TEXT(B33, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D33" s="15">
@@ -3156,7 +3364,7 @@
         <v>45999</v>
       </c>
       <c r="C34" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B34),"",TEXT(B34, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D34" s="15">
@@ -3174,7 +3382,7 @@
         <v>45999</v>
       </c>
       <c r="C35" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B35),"",TEXT(B35, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D35" s="15">
@@ -3192,7 +3400,7 @@
         <v>45999</v>
       </c>
       <c r="C36" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B36),"",TEXT(B36, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D36" s="15">
@@ -3210,7 +3418,7 @@
         <v>46000</v>
       </c>
       <c r="C37" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B37),"",TEXT(B37, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D37" s="15"/>
@@ -3230,7 +3438,7 @@
         <v>46001</v>
       </c>
       <c r="C38" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B38),"",TEXT(B38, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D38" s="15">
@@ -3252,7 +3460,7 @@
         <v>46001</v>
       </c>
       <c r="C39" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B39),"",TEXT(B39, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D39" s="15">
@@ -3274,7 +3482,7 @@
         <v>46001</v>
       </c>
       <c r="C40" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B40),"",TEXT(B40, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D40" s="15">
@@ -3296,7 +3504,7 @@
         <v>46001</v>
       </c>
       <c r="C41" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B41),"",TEXT(B41, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D41" s="15">
@@ -3318,7 +3526,7 @@
         <v>46001</v>
       </c>
       <c r="C42" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B42),"",TEXT(B42, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D42" s="15">
@@ -3340,7 +3548,7 @@
         <v>46001</v>
       </c>
       <c r="C43" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(B43),"",TEXT(B43, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D43" s="15">
@@ -3362,7 +3570,7 @@
         <v>46001</v>
       </c>
       <c r="C44" s="15" t="str">
-        <f t="shared" ref="C44:C75" si="2">IF(ISBLANK(B44),"",TEXT(B44, "dddd"))</f>
+        <f>IF(ISBLANK(B44),"",TEXT(B44, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D44" s="15">
@@ -3380,7 +3588,7 @@
         <v>46001</v>
       </c>
       <c r="C45" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B45),"",TEXT(B45, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D45" s="15">
@@ -3400,7 +3608,7 @@
         <v>46001</v>
       </c>
       <c r="C46" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B46),"",TEXT(B46, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D46" s="15">
@@ -3420,7 +3628,7 @@
         <v>46001</v>
       </c>
       <c r="C47" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B47),"",TEXT(B47, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D47" s="15">
@@ -3442,7 +3650,7 @@
         <v>46002</v>
       </c>
       <c r="C48" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B48),"",TEXT(B48, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D48" s="15">
@@ -3462,7 +3670,7 @@
         <v>46003</v>
       </c>
       <c r="C49" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B49),"",TEXT(B49, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D49" s="15">
@@ -3484,7 +3692,7 @@
         <v>46006</v>
       </c>
       <c r="C50" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B50),"",TEXT(B50, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D50" s="15">
@@ -3506,7 +3714,7 @@
         <v>46006</v>
       </c>
       <c r="C51" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B51),"",TEXT(B51, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D51" s="15">
@@ -3528,7 +3736,7 @@
         <v>46006</v>
       </c>
       <c r="C52" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B52),"",TEXT(B52, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D52" s="15">
@@ -3550,7 +3758,7 @@
         <v>46006</v>
       </c>
       <c r="C53" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B53),"",TEXT(B53, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D53" s="15">
@@ -3572,7 +3780,7 @@
         <v>46006</v>
       </c>
       <c r="C54" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B54),"",TEXT(B54, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D54" s="15">
@@ -3594,7 +3802,7 @@
         <v>46006</v>
       </c>
       <c r="C55" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B55),"",TEXT(B55, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D55" s="15">
@@ -3616,7 +3824,7 @@
         <v>46006</v>
       </c>
       <c r="C56" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B56),"",TEXT(B56, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D56" s="15">
@@ -3638,7 +3846,7 @@
         <v>46006</v>
       </c>
       <c r="C57" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B57),"",TEXT(B57, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D57" s="15">
@@ -3660,7 +3868,7 @@
         <v>46006</v>
       </c>
       <c r="C58" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B58),"",TEXT(B58, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D58" s="15">
@@ -3682,7 +3890,7 @@
         <v>46006</v>
       </c>
       <c r="C59" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B59),"",TEXT(B59, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D59" s="15">
@@ -3704,7 +3912,7 @@
         <v>46006</v>
       </c>
       <c r="C60" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B60),"",TEXT(B60, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D60" s="15">
@@ -3726,7 +3934,7 @@
         <v>46007</v>
       </c>
       <c r="C61" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B61),"",TEXT(B61, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D61" s="15">
@@ -3748,7 +3956,7 @@
         <v>46007</v>
       </c>
       <c r="C62" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B62),"",TEXT(B62, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D62" s="15">
@@ -3770,7 +3978,7 @@
         <v>46007</v>
       </c>
       <c r="C63" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B63),"",TEXT(B63, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D63" s="15">
@@ -3792,7 +4000,7 @@
         <v>46007</v>
       </c>
       <c r="C64" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B64),"",TEXT(B64, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D64" s="15">
@@ -3814,7 +4022,7 @@
         <v>46008</v>
       </c>
       <c r="C65" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B65),"",TEXT(B65, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D65" s="15">
@@ -3834,7 +4042,7 @@
         <v>46008</v>
       </c>
       <c r="C66" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B66),"",TEXT(B66, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D66" s="15">
@@ -3854,7 +4062,7 @@
         <v>46008</v>
       </c>
       <c r="C67" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B67),"",TEXT(B67, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D67" s="15">
@@ -3872,7 +4080,7 @@
         <v>46008</v>
       </c>
       <c r="C68" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B68),"",TEXT(B68, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D68" s="15">
@@ -3892,7 +4100,7 @@
         <v>46009</v>
       </c>
       <c r="C69" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B69),"",TEXT(B69, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D69" s="15">
@@ -3912,7 +4120,7 @@
         <v>46009</v>
       </c>
       <c r="C70" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B70),"",TEXT(B70, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D70" s="15"/>
@@ -3930,7 +4138,7 @@
         <v>46015</v>
       </c>
       <c r="C71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B71),"",TEXT(B71, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D71" s="15">
@@ -3950,7 +4158,7 @@
         <v>46015</v>
       </c>
       <c r="C72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B72),"",TEXT(B72, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D72" s="15">
@@ -3970,7 +4178,7 @@
         <v>46015</v>
       </c>
       <c r="C73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B73),"",TEXT(B73, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D73" s="15"/>
@@ -3988,7 +4196,7 @@
         <v>46015</v>
       </c>
       <c r="C74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B74),"",TEXT(B74, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D74" s="15"/>
@@ -4006,7 +4214,7 @@
         <v>46015</v>
       </c>
       <c r="C75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(B75),"",TEXT(B75, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D75" s="15"/>
@@ -4024,7 +4232,7 @@
         <v>46022</v>
       </c>
       <c r="C76" s="15" t="str">
-        <f t="shared" ref="C76:C107" si="3">IF(ISBLANK(B76),"",TEXT(B76, "dddd"))</f>
+        <f>IF(ISBLANK(B76),"",TEXT(B76, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D76" s="15"/>
@@ -4042,7 +4250,7 @@
         <v>46022</v>
       </c>
       <c r="C77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B77),"",TEXT(B77, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D77" s="15"/>
@@ -4060,7 +4268,7 @@
         <v>46022</v>
       </c>
       <c r="C78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B78),"",TEXT(B78, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D78" s="15"/>
@@ -4078,7 +4286,7 @@
         <v>46024</v>
       </c>
       <c r="C79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B79),"",TEXT(B79, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D79" s="15">
@@ -4098,7 +4306,7 @@
         <v>46024</v>
       </c>
       <c r="C80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B80),"",TEXT(B80, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D80" s="15">
@@ -4118,7 +4326,7 @@
         <v>46024</v>
       </c>
       <c r="C81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B81),"",TEXT(B81, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D81" s="15">
@@ -4138,7 +4346,7 @@
         <v>46024</v>
       </c>
       <c r="C82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B82),"",TEXT(B82, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D82" s="15">
@@ -4158,7 +4366,7 @@
         <v>46024</v>
       </c>
       <c r="C83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B83),"",TEXT(B83, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D83" s="15">
@@ -4178,7 +4386,7 @@
         <v>46024</v>
       </c>
       <c r="C84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B84),"",TEXT(B84, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D84" s="15">
@@ -4198,7 +4406,7 @@
         <v>46024</v>
       </c>
       <c r="C85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B85),"",TEXT(B85, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D85" s="15">
@@ -4218,7 +4426,7 @@
         <v>46024</v>
       </c>
       <c r="C86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B86),"",TEXT(B86, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D86" s="15">
@@ -4236,7 +4444,7 @@
         <v>46024</v>
       </c>
       <c r="C87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B87),"",TEXT(B87, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D87" s="15">
@@ -4256,7 +4464,7 @@
         <v>46024</v>
       </c>
       <c r="C88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B88),"",TEXT(B88, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D88" s="15">
@@ -4274,7 +4482,7 @@
         <v>46024</v>
       </c>
       <c r="C89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B89),"",TEXT(B89, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D89" s="15">
@@ -4294,7 +4502,7 @@
         <v>46024</v>
       </c>
       <c r="C90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B90),"",TEXT(B90, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D90" s="15">
@@ -4314,7 +4522,7 @@
         <v>46024</v>
       </c>
       <c r="C91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B91),"",TEXT(B91, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D91" s="15">
@@ -4334,7 +4542,7 @@
         <v>46024</v>
       </c>
       <c r="C92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B92),"",TEXT(B92, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D92" s="15">
@@ -4354,7 +4562,7 @@
         <v>46024</v>
       </c>
       <c r="C93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B93),"",TEXT(B93, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D93" s="15">
@@ -4374,7 +4582,7 @@
         <v>46024</v>
       </c>
       <c r="C94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B94),"",TEXT(B94, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D94" s="15">
@@ -4394,7 +4602,7 @@
         <v>46024</v>
       </c>
       <c r="C95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B95),"",TEXT(B95, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D95" s="15">
@@ -4414,7 +4622,7 @@
         <v>46024</v>
       </c>
       <c r="C96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B96),"",TEXT(B96, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D96" s="15">
@@ -4434,7 +4642,7 @@
         <v>46024</v>
       </c>
       <c r="C97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B97),"",TEXT(B97, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D97" s="15">
@@ -4452,7 +4660,7 @@
         <v>46024</v>
       </c>
       <c r="C98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B98),"",TEXT(B98, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D98" s="15">
@@ -4470,7 +4678,7 @@
         <v>46024</v>
       </c>
       <c r="C99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B99),"",TEXT(B99, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D99" s="15">
@@ -4488,7 +4696,7 @@
         <v>46027</v>
       </c>
       <c r="C100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B100),"",TEXT(B100, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D100" s="15"/>
@@ -4506,7 +4714,7 @@
         <v>46028</v>
       </c>
       <c r="C101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B101),"",TEXT(B101, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D101" s="15"/>
@@ -4524,7 +4732,7 @@
         <v>46028</v>
       </c>
       <c r="C102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B102),"",TEXT(B102, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D102" s="15"/>
@@ -4540,7 +4748,7 @@
         <v>46028</v>
       </c>
       <c r="C103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B103),"",TEXT(B103, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D103" s="15"/>
@@ -4556,7 +4764,7 @@
         <v>46030</v>
       </c>
       <c r="C104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B104),"",TEXT(B104, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D104" s="15"/>
@@ -4576,7 +4784,7 @@
         <v>46030</v>
       </c>
       <c r="C105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B105),"",TEXT(B105, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D105" s="15"/>
@@ -4596,7 +4804,7 @@
         <v>46034</v>
       </c>
       <c r="C106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B106),"",TEXT(B106, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D106" s="15"/>
@@ -4616,7 +4824,7 @@
         <v>46035</v>
       </c>
       <c r="C107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(B107),"",TEXT(B107, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D107" s="15">
@@ -4636,7 +4844,7 @@
         <v>46035</v>
       </c>
       <c r="C108" s="15" t="str">
-        <f t="shared" ref="C108:C139" si="4">IF(ISBLANK(B108),"",TEXT(B108, "dddd"))</f>
+        <f>IF(ISBLANK(B108),"",TEXT(B108, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D108" s="15">
@@ -4656,7 +4864,7 @@
         <v>46036</v>
       </c>
       <c r="C109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B109),"",TEXT(B109, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D109" s="15"/>
@@ -4674,7 +4882,7 @@
         <v>46036</v>
       </c>
       <c r="C110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B110),"",TEXT(B110, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D110" s="15"/>
@@ -4692,7 +4900,7 @@
         <v>46036</v>
       </c>
       <c r="C111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B111),"",TEXT(B111, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D111" s="15"/>
@@ -4710,7 +4918,7 @@
         <v>46036</v>
       </c>
       <c r="C112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B112),"",TEXT(B112, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D112" s="15"/>
@@ -4728,7 +4936,7 @@
         <v>46037</v>
       </c>
       <c r="C113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B113),"",TEXT(B113, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D113" s="15"/>
@@ -4746,7 +4954,7 @@
         <v>46038</v>
       </c>
       <c r="C114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B114),"",TEXT(B114, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D114" s="15">
@@ -4768,7 +4976,7 @@
         <v>46038</v>
       </c>
       <c r="C115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B115),"",TEXT(B115, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D115" s="15">
@@ -4790,7 +4998,7 @@
         <v>46038</v>
       </c>
       <c r="C116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B116),"",TEXT(B116, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D116" s="15">
@@ -4812,7 +5020,7 @@
         <v>46038</v>
       </c>
       <c r="C117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B117),"",TEXT(B117, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D117" s="15"/>
@@ -4826,7 +5034,7 @@
         <v>46042</v>
       </c>
       <c r="C118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B118),"",TEXT(B118, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D118" s="15"/>
@@ -4846,7 +5054,7 @@
         <v>46042</v>
       </c>
       <c r="C119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B119),"",TEXT(B119, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D119" s="15"/>
@@ -4866,7 +5074,7 @@
         <v>46042</v>
       </c>
       <c r="C120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B120),"",TEXT(B120, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D120" s="15"/>
@@ -4884,7 +5092,7 @@
         <v>46042</v>
       </c>
       <c r="C121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B121),"",TEXT(B121, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D121" s="15"/>
@@ -4902,7 +5110,7 @@
         <v>46042</v>
       </c>
       <c r="C122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B122),"",TEXT(B122, "dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D122" s="15"/>
@@ -4920,7 +5128,7 @@
         <v>46043</v>
       </c>
       <c r="C123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B123),"",TEXT(B123, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D123" s="15"/>
@@ -4938,7 +5146,7 @@
         <v>46043</v>
       </c>
       <c r="C124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B124),"",TEXT(B124, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D124" s="15"/>
@@ -4956,7 +5164,7 @@
         <v>46043</v>
       </c>
       <c r="C125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B125),"",TEXT(B125, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D125" s="15"/>
@@ -4974,7 +5182,7 @@
         <v>46043</v>
       </c>
       <c r="C126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B126),"",TEXT(B126, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D126" s="15"/>
@@ -4992,7 +5200,7 @@
         <v>46043</v>
       </c>
       <c r="C127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B127),"",TEXT(B127, "dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D127" s="15"/>
@@ -5010,7 +5218,7 @@
         <v>46044</v>
       </c>
       <c r="C128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B128),"",TEXT(B128, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D128" s="15"/>
@@ -5028,7 +5236,7 @@
         <v>46044</v>
       </c>
       <c r="C129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B129),"",TEXT(B129, "dddd"))</f>
         <v>Thursday</v>
       </c>
       <c r="D129" s="15"/>
@@ -5046,7 +5254,7 @@
         <v>46045</v>
       </c>
       <c r="C130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B130),"",TEXT(B130, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D130" s="15"/>
@@ -5064,7 +5272,7 @@
         <v>46045</v>
       </c>
       <c r="C131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B131),"",TEXT(B131, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D131" s="15"/>
@@ -5082,7 +5290,7 @@
         <v>46045</v>
       </c>
       <c r="C132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B132),"",TEXT(B132, "dddd"))</f>
         <v>Friday</v>
       </c>
       <c r="D132" s="15"/>
@@ -5100,7 +5308,7 @@
         <v>46055</v>
       </c>
       <c r="C133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B133),"",TEXT(B133, "dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D133" s="15"/>
@@ -5114,141 +5322,185 @@
       <c r="H133" s="16"/>
     </row>
     <row r="134" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B134" s="13"/>
+      <c r="B134" s="13">
+        <v>46078</v>
+      </c>
       <c r="C134" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(ISBLANK(B134),"",TEXT(B134, "dddd"))</f>
+        <v>Wednesday</v>
       </c>
       <c r="D134" s="15"/>
       <c r="E134" s="74"/>
-      <c r="F134" s="15"/>
+      <c r="F134" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="G134" s="44"/>
       <c r="H134" s="16"/>
     </row>
-    <row r="135" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B135" s="13"/>
+    <row r="135" spans="2:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="B135" s="13">
+        <v>46079</v>
+      </c>
       <c r="C135" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(ISBLANK(B135),"",TEXT(B135, "dddd"))</f>
+        <v>Thursday</v>
       </c>
       <c r="D135" s="15"/>
       <c r="E135" s="74"/>
-      <c r="F135" s="15"/>
+      <c r="F135" s="15" t="s">
+        <v>295</v>
+      </c>
       <c r="G135" s="44"/>
       <c r="H135" s="16"/>
     </row>
-    <row r="136" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B136" s="13"/>
+    <row r="136" spans="2:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="B136" s="13">
+        <v>46079</v>
+      </c>
       <c r="C136" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(ISBLANK(B136),"",TEXT(B136, "dddd"))</f>
+        <v>Thursday</v>
       </c>
       <c r="D136" s="15"/>
       <c r="E136" s="74"/>
-      <c r="F136" s="15"/>
+      <c r="F136" s="11" t="s">
+        <v>298</v>
+      </c>
       <c r="G136" s="44"/>
       <c r="H136" s="16"/>
     </row>
     <row r="137" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B137" s="13"/>
+      <c r="B137" s="13">
+        <v>46079</v>
+      </c>
       <c r="C137" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(ISBLANK(B137),"",TEXT(B137, "dddd"))</f>
+        <v>Thursday</v>
       </c>
       <c r="D137" s="15"/>
       <c r="E137" s="74"/>
-      <c r="F137" s="15"/>
+      <c r="F137" s="15" t="s">
+        <v>299</v>
+      </c>
       <c r="G137" s="44"/>
       <c r="H137" s="16"/>
     </row>
     <row r="138" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B138" s="13"/>
+      <c r="B138" s="13">
+        <v>46080</v>
+      </c>
       <c r="C138" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(ISBLANK(B138),"",TEXT(B138, "dddd"))</f>
+        <v>Friday</v>
       </c>
       <c r="D138" s="15"/>
       <c r="E138" s="74"/>
-      <c r="F138" s="15"/>
+      <c r="F138" s="15" t="s">
+        <v>292</v>
+      </c>
       <c r="G138" s="44"/>
       <c r="H138" s="16"/>
     </row>
     <row r="139" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B139" s="13"/>
+      <c r="B139" s="13">
+        <v>46080</v>
+      </c>
       <c r="C139" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(ISBLANK(B139),"",TEXT(B139, "dddd"))</f>
+        <v>Friday</v>
       </c>
       <c r="D139" s="15"/>
       <c r="E139" s="74"/>
-      <c r="F139" s="15"/>
+      <c r="F139" s="15" t="s">
+        <v>300</v>
+      </c>
       <c r="G139" s="44"/>
       <c r="H139" s="16"/>
     </row>
     <row r="140" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B140" s="13"/>
+      <c r="B140" s="13">
+        <v>46080</v>
+      </c>
       <c r="C140" s="15" t="str">
-        <f t="shared" ref="C140:C171" si="5">IF(ISBLANK(B140),"",TEXT(B140, "dddd"))</f>
-        <v/>
+        <f>IF(ISBLANK(B140),"",TEXT(B140, "dddd"))</f>
+        <v>Friday</v>
       </c>
       <c r="D140" s="15"/>
       <c r="E140" s="74"/>
-      <c r="F140" s="15"/>
+      <c r="F140" s="80" t="s">
+        <v>290</v>
+      </c>
       <c r="G140" s="44"/>
       <c r="H140" s="16"/>
     </row>
-    <row r="141" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B141" s="13"/>
+    <row r="141" spans="2:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="B141" s="13">
+        <v>46080</v>
+      </c>
       <c r="C141" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f>IF(ISBLANK(B141),"",TEXT(B141, "dddd"))</f>
+        <v>Friday</v>
       </c>
       <c r="D141" s="15"/>
       <c r="E141" s="74"/>
-      <c r="F141" s="15"/>
+      <c r="F141" s="15" t="s">
+        <v>296</v>
+      </c>
       <c r="G141" s="44"/>
       <c r="H141" s="16"/>
     </row>
     <row r="142" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B142" s="13"/>
+      <c r="B142" s="13">
+        <v>46080</v>
+      </c>
       <c r="C142" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f>IF(ISBLANK(B142),"",TEXT(B142, "dddd"))</f>
+        <v>Friday</v>
       </c>
       <c r="D142" s="15"/>
       <c r="E142" s="74"/>
-      <c r="F142" s="15"/>
+      <c r="F142" s="15" t="s">
+        <v>297</v>
+      </c>
       <c r="G142" s="44"/>
       <c r="H142" s="16"/>
     </row>
     <row r="143" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B143" s="13"/>
+      <c r="B143" s="13">
+        <v>46083</v>
+      </c>
       <c r="C143" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f>IF(ISBLANK(B143),"",TEXT(B143, "dddd"))</f>
+        <v>Monday</v>
       </c>
       <c r="D143" s="15"/>
       <c r="E143" s="74"/>
-      <c r="F143" s="15"/>
+      <c r="F143" s="15" t="s">
+        <v>293</v>
+      </c>
       <c r="G143" s="44"/>
       <c r="H143" s="16"/>
     </row>
-    <row r="144" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B144" s="13"/>
+    <row r="144" spans="2:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="B144" s="13">
+        <v>46083</v>
+      </c>
       <c r="C144" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <f>IF(ISBLANK(B144),"",TEXT(B144, "dddd"))</f>
+        <v>Monday</v>
       </c>
       <c r="D144" s="15"/>
       <c r="E144" s="74"/>
-      <c r="F144" s="15"/>
+      <c r="F144" s="15" t="s">
+        <v>294</v>
+      </c>
       <c r="G144" s="44"/>
       <c r="H144" s="16"/>
     </row>
     <row r="145" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B145" s="13"/>
       <c r="C145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B145),"",TEXT(B145, "dddd"))</f>
         <v/>
       </c>
       <c r="D145" s="15"/>
@@ -5260,7 +5512,7 @@
     <row r="146" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B146" s="13"/>
       <c r="C146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B146),"",TEXT(B146, "dddd"))</f>
         <v/>
       </c>
       <c r="D146" s="15"/>
@@ -5272,19 +5524,19 @@
     <row r="147" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B147" s="13"/>
       <c r="C147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B147),"",TEXT(B147, "dddd"))</f>
         <v/>
       </c>
       <c r="D147" s="15"/>
       <c r="E147" s="74"/>
-      <c r="F147" s="15"/>
+      <c r="F147" s="11"/>
       <c r="G147" s="44"/>
       <c r="H147" s="16"/>
     </row>
     <row r="148" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B148" s="13"/>
       <c r="C148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B148),"",TEXT(B148, "dddd"))</f>
         <v/>
       </c>
       <c r="D148" s="15"/>
@@ -5296,285 +5548,267 @@
     <row r="149" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B149" s="13"/>
       <c r="C149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B149),"",TEXT(B149, "dddd"))</f>
         <v/>
       </c>
       <c r="D149" s="15"/>
       <c r="E149" s="74"/>
-      <c r="F149" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="G149" s="44" t="s">
-        <v>227</v>
-      </c>
+      <c r="F149" s="15"/>
+      <c r="G149" s="44"/>
       <c r="H149" s="16"/>
     </row>
-    <row r="150" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B150" s="13"/>
-      <c r="C150" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="C150" s="15"/>
       <c r="D150" s="15"/>
       <c r="E150" s="74"/>
       <c r="F150" s="15"/>
-      <c r="G150" s="44" t="s">
-        <v>231</v>
-      </c>
+      <c r="G150" s="44"/>
       <c r="H150" s="16"/>
     </row>
-    <row r="151" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B151" s="13"/>
-      <c r="C151" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="C151" s="15"/>
       <c r="D151" s="15"/>
       <c r="E151" s="74"/>
       <c r="F151" s="15"/>
-      <c r="G151" s="44" t="s">
-        <v>229</v>
-      </c>
+      <c r="G151" s="44"/>
       <c r="H151" s="16"/>
     </row>
-    <row r="152" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B152" s="13"/>
-      <c r="C152" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="C152" s="15"/>
       <c r="D152" s="15"/>
       <c r="E152" s="74"/>
-      <c r="F152" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="G152" s="44" t="s">
-        <v>230</v>
-      </c>
+      <c r="F152" s="15"/>
+      <c r="G152" s="44"/>
       <c r="H152" s="16"/>
     </row>
-    <row r="153" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B153" s="13"/>
-      <c r="C153" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="C153" s="15"/>
       <c r="D153" s="15"/>
       <c r="E153" s="74"/>
-      <c r="F153" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="G153" s="44" t="s">
-        <v>140</v>
-      </c>
+      <c r="F153" s="15"/>
+      <c r="G153" s="44"/>
       <c r="H153" s="16"/>
     </row>
-    <row r="154" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B154" s="13"/>
-      <c r="C154" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="C154" s="15"/>
       <c r="D154" s="15"/>
       <c r="E154" s="74"/>
-      <c r="F154" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="G154" s="44" t="s">
-        <v>140</v>
-      </c>
+      <c r="F154" s="15"/>
+      <c r="G154" s="44"/>
       <c r="H154" s="16"/>
     </row>
     <row r="155" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B155" s="13"/>
       <c r="C155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B155),"",TEXT(B155, "dddd"))</f>
         <v/>
       </c>
       <c r="D155" s="15"/>
       <c r="E155" s="74"/>
-      <c r="F155" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="G155" s="44" t="s">
-        <v>228</v>
-      </c>
+      <c r="F155" s="15"/>
+      <c r="G155" s="44"/>
       <c r="H155" s="16"/>
     </row>
     <row r="156" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B156" s="13"/>
       <c r="C156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B156),"",TEXT(B156, "dddd"))</f>
         <v/>
       </c>
       <c r="D156" s="15"/>
-      <c r="E156" s="44"/>
+      <c r="E156" s="74"/>
       <c r="F156" s="15" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="G156" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="H156" s="17"/>
+        <v>227</v>
+      </c>
+      <c r="H156" s="16"/>
     </row>
     <row r="157" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B157" s="13"/>
       <c r="C157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B157),"",TEXT(B157, "dddd"))</f>
         <v/>
       </c>
       <c r="D157" s="15"/>
-      <c r="E157" s="44"/>
-      <c r="F157" s="15" t="s">
-        <v>223</v>
-      </c>
+      <c r="E157" s="74"/>
+      <c r="F157" s="15"/>
       <c r="G157" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="H157" s="17"/>
+        <v>231</v>
+      </c>
+      <c r="H157" s="16"/>
     </row>
     <row r="158" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B158" s="13"/>
       <c r="C158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B158),"",TEXT(B158, "dddd"))</f>
         <v/>
       </c>
       <c r="D158" s="15"/>
       <c r="E158" s="74"/>
-      <c r="F158" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="G158" s="44"/>
+      <c r="F158" s="15"/>
+      <c r="G158" s="44" t="s">
+        <v>229</v>
+      </c>
       <c r="H158" s="16"/>
     </row>
     <row r="159" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B159" s="13"/>
       <c r="C159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B159),"",TEXT(B159, "dddd"))</f>
         <v/>
       </c>
       <c r="D159" s="15"/>
       <c r="E159" s="74"/>
       <c r="F159" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="G159" s="44"/>
+        <v>226</v>
+      </c>
+      <c r="G159" s="44" t="s">
+        <v>230</v>
+      </c>
       <c r="H159" s="16"/>
     </row>
     <row r="160" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B160" s="13"/>
       <c r="C160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B160),"",TEXT(B160, "dddd"))</f>
         <v/>
       </c>
       <c r="D160" s="15"/>
       <c r="E160" s="74"/>
       <c r="F160" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="G160" s="44"/>
+        <v>178</v>
+      </c>
+      <c r="G160" s="44" t="s">
+        <v>140</v>
+      </c>
       <c r="H160" s="16"/>
     </row>
     <row r="161" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B161" s="13"/>
       <c r="C161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B161),"",TEXT(B161, "dddd"))</f>
         <v/>
       </c>
       <c r="D161" s="15"/>
       <c r="E161" s="74"/>
       <c r="F161" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="G161" s="44"/>
+        <v>181</v>
+      </c>
+      <c r="G161" s="44" t="s">
+        <v>140</v>
+      </c>
       <c r="H161" s="16"/>
     </row>
     <row r="162" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B162" s="13"/>
       <c r="C162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B162),"",TEXT(B162, "dddd"))</f>
         <v/>
       </c>
       <c r="D162" s="15"/>
       <c r="E162" s="74"/>
       <c r="F162" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="G162" s="44"/>
+        <v>169</v>
+      </c>
+      <c r="G162" s="44" t="s">
+        <v>228</v>
+      </c>
       <c r="H162" s="16"/>
     </row>
     <row r="163" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B163" s="13"/>
       <c r="C163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B163),"",TEXT(B163, "dddd"))</f>
         <v/>
       </c>
       <c r="D163" s="15"/>
-      <c r="E163" s="74"/>
+      <c r="E163" s="44"/>
       <c r="F163" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="G163" s="44"/>
-      <c r="H163" s="16"/>
+        <v>222</v>
+      </c>
+      <c r="G163" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H163" s="17"/>
     </row>
     <row r="164" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B164" s="13"/>
       <c r="C164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B164),"",TEXT(B164, "dddd"))</f>
         <v/>
       </c>
       <c r="D164" s="15"/>
-      <c r="E164" s="74"/>
-      <c r="F164" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="G164" s="44"/>
-      <c r="H164" s="16"/>
+      <c r="E164" s="44"/>
+      <c r="F164" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="G164" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H164" s="17"/>
     </row>
     <row r="165" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B165" s="13"/>
       <c r="C165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B165),"",TEXT(B165, "dddd"))</f>
         <v/>
       </c>
       <c r="D165" s="15"/>
       <c r="E165" s="74"/>
-      <c r="F165" s="15"/>
+      <c r="F165" s="15" t="s">
+        <v>233</v>
+      </c>
       <c r="G165" s="44"/>
       <c r="H165" s="16"/>
     </row>
     <row r="166" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B166" s="13"/>
       <c r="C166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B166),"",TEXT(B166, "dddd"))</f>
         <v/>
       </c>
       <c r="D166" s="15"/>
-      <c r="E166" s="44"/>
-      <c r="F166" s="15"/>
+      <c r="E166" s="74"/>
+      <c r="F166" s="15" t="s">
+        <v>244</v>
+      </c>
       <c r="G166" s="44"/>
-      <c r="H166" s="17"/>
+      <c r="H166" s="16"/>
     </row>
     <row r="167" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B167" s="13"/>
       <c r="C167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(B167),"",TEXT(B167, "dddd"))</f>
         <v/>
       </c>
       <c r="D167" s="15"/>
-      <c r="E167" s="44"/>
-      <c r="F167" s="15"/>
+      <c r="E167" s="74"/>
+      <c r="F167" s="15" t="s">
+        <v>245</v>
+      </c>
       <c r="G167" s="44"/>
-      <c r="H167" s="17"/>
-    </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H167" s="16"/>
+    </row>
+    <row r="168" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B168" s="13"/>
-      <c r="C168" s="15"/>
+      <c r="C168" s="15" t="str">
+        <f>IF(ISBLANK(B168),"",TEXT(B168, "dddd"))</f>
+        <v/>
+      </c>
       <c r="D168" s="15"/>
-      <c r="E168" s="44"/>
-      <c r="F168" s="15"/>
+      <c r="E168" s="74"/>
+      <c r="F168" s="15" t="s">
+        <v>246</v>
+      </c>
       <c r="G168" s="44"/>
-      <c r="H168" s="17"/>
+      <c r="H168" s="16"/>
     </row>
     <row r="169" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B169" s="13"/>
@@ -5583,10 +5817,12 @@
         <v/>
       </c>
       <c r="D169" s="15"/>
-      <c r="E169" s="44"/>
-      <c r="F169" s="15"/>
+      <c r="E169" s="74"/>
+      <c r="F169" s="15" t="s">
+        <v>247</v>
+      </c>
       <c r="G169" s="44"/>
-      <c r="H169" s="17"/>
+      <c r="H169" s="16"/>
     </row>
     <row r="170" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B170" s="13"/>
@@ -5595,10 +5831,12 @@
         <v/>
       </c>
       <c r="D170" s="15"/>
-      <c r="E170" s="44"/>
-      <c r="F170" s="15"/>
+      <c r="E170" s="74"/>
+      <c r="F170" s="15" t="s">
+        <v>248</v>
+      </c>
       <c r="G170" s="44"/>
-      <c r="H170" s="17"/>
+      <c r="H170" s="16"/>
     </row>
     <row r="171" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B171" s="13"/>
@@ -5607,44 +5845,131 @@
         <v/>
       </c>
       <c r="D171" s="15"/>
-      <c r="E171" s="44"/>
-      <c r="F171" s="15"/>
+      <c r="E171" s="74"/>
+      <c r="F171" s="11" t="s">
+        <v>249</v>
+      </c>
       <c r="G171" s="44"/>
-      <c r="H171" s="17"/>
-    </row>
-    <row r="172" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="46"/>
-      <c r="C172" s="18"/>
-      <c r="D172" s="18"/>
-      <c r="E172" s="45"/>
-      <c r="F172" s="18"/>
-      <c r="G172" s="45"/>
-      <c r="H172" s="19"/>
+      <c r="H171" s="16"/>
+    </row>
+    <row r="172" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B172" s="13"/>
+      <c r="C172" s="15" t="str">
+        <f>IF(ISBLANK(B172),"",TEXT(B172, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D172" s="15"/>
+      <c r="E172" s="74"/>
+      <c r="F172" s="15"/>
+      <c r="G172" s="44"/>
+      <c r="H172" s="16"/>
+    </row>
+    <row r="173" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B173" s="13"/>
+      <c r="C173" s="15" t="str">
+        <f>IF(ISBLANK(B173),"",TEXT(B173, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D173" s="15"/>
+      <c r="E173" s="44"/>
+      <c r="F173" s="15"/>
+      <c r="G173" s="44"/>
+      <c r="H173" s="17"/>
+    </row>
+    <row r="174" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B174" s="13"/>
+      <c r="C174" s="15" t="str">
+        <f>IF(ISBLANK(B174),"",TEXT(B174, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D174" s="15"/>
+      <c r="E174" s="44"/>
+      <c r="F174" s="15"/>
+      <c r="G174" s="44"/>
+      <c r="H174" s="17"/>
+    </row>
+    <row r="175" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B175" s="13"/>
+      <c r="C175" s="15"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="44"/>
+      <c r="F175" s="15"/>
+      <c r="G175" s="44"/>
+      <c r="H175" s="17"/>
+    </row>
+    <row r="176" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B176" s="13"/>
+      <c r="C176" s="15" t="str">
+        <f>IF(ISBLANK(B176),"",TEXT(B176, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D176" s="15"/>
+      <c r="E176" s="44"/>
+      <c r="F176" s="15"/>
+      <c r="G176" s="44"/>
+      <c r="H176" s="17"/>
+    </row>
+    <row r="177" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B177" s="13"/>
+      <c r="C177" s="15" t="str">
+        <f>IF(ISBLANK(B177),"",TEXT(B177, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D177" s="15"/>
+      <c r="E177" s="44"/>
+      <c r="F177" s="15"/>
+      <c r="G177" s="44"/>
+      <c r="H177" s="17"/>
+    </row>
+    <row r="178" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B178" s="13"/>
+      <c r="C178" s="15" t="str">
+        <f>IF(ISBLANK(B178),"",TEXT(B178, "dddd"))</f>
+        <v/>
+      </c>
+      <c r="D178" s="15"/>
+      <c r="E178" s="44"/>
+      <c r="F178" s="15"/>
+      <c r="G178" s="44"/>
+      <c r="H178" s="17"/>
+    </row>
+    <row r="179" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B179" s="46"/>
+      <c r="C179" s="18"/>
+      <c r="D179" s="18"/>
+      <c r="E179" s="45"/>
+      <c r="F179" s="18"/>
+      <c r="G179" s="45"/>
+      <c r="H179" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H172" xr:uid="{40A518F1-E8D1-4EDA-B8FC-EAEFD9F39116}"/>
-  <conditionalFormatting sqref="B2:H457">
-    <cfRule type="expression" dxfId="12" priority="7">
+  <autoFilter ref="B2:H179" xr:uid="{40A518F1-E8D1-4EDA-B8FC-EAEFD9F39116}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:H179">
+      <sortCondition ref="B2:B179"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="B2:H500">
+    <cfRule type="expression" dxfId="12" priority="7" stopIfTrue="1">
       <formula>$C2=Saturday</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="8">
+    <cfRule type="expression" dxfId="14" priority="8">
       <formula>$C2="Monday"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="17" priority="9">
       <formula>$C2="Tuesday"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="16" priority="10" stopIfTrue="1">
       <formula>$C2="Wednesday"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="11">
+    <cfRule type="expression" dxfId="15" priority="11">
       <formula>$C2="Thursday"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="12">
+    <cfRule type="expression" dxfId="13" priority="12">
       <formula>$C2="Friday"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E33:E172 H33:H172" xr:uid="{F96E5036-0CE7-4348-B733-74DDF2C8E069}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E33:E179 H33:H179" xr:uid="{F96E5036-0CE7-4348-B733-74DDF2C8E069}">
       <formula1>45658</formula1>
       <formula2>46388</formula2>
     </dataValidation>
@@ -5702,6 +6027,9 @@
       </c>
       <c r="C3">
         <v>142</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6508,25 +6836,25 @@
     <mergeCell ref="B2:N2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:N28">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>LEFT($B4,1)="7"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>LEFT($B4,1)="1"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="34" priority="3">
       <formula>LEFT($B4,1)="2"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="33" priority="4">
       <formula>LEFT($B4,1)="3"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="32" priority="5">
       <formula>LEFT($B4,1)="4"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="31" priority="6">
       <formula>LEFT($B4,1)="5"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="30" priority="7">
       <formula>LEFT($B4,1)="6"</formula>
     </cfRule>
   </conditionalFormatting>
